--- a/tests/data/mock_drug_treatment_exp.xlsx
+++ b/tests/data/mock_drug_treatment_exp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabewilson/Desktop/worklist_generation/tests/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF1333D7-F093-5B4D-8CCF-E6FC4F928A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF92C99-6F98-8842-8BAE-67DE634C14BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14720" yWindow="700" windowWidth="14680" windowHeight="16940" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="700" windowWidth="14720" windowHeight="16920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="User" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="117">
   <si>
     <t>Name:</t>
   </si>
@@ -174,9 +174,6 @@
     <t>Number of sample to run:</t>
   </si>
   <si>
-    <t>Columns:</t>
-  </si>
-  <si>
     <t>QC</t>
   </si>
   <si>
@@ -237,9 +234,6 @@
     <t>lcmethodfile</t>
   </si>
   <si>
-    <t>After</t>
-  </si>
-  <si>
     <t>D1t0</t>
   </si>
   <si>
@@ -333,9 +327,6 @@
     <t>Nonsample between:</t>
   </si>
   <si>
-    <t>Library value placement:</t>
-  </si>
-  <si>
     <t>Frequency of system validation (#):</t>
   </si>
   <si>
@@ -348,17 +339,59 @@
     <t>This determines how the well location is denoted (RA1 vs R:A1)</t>
   </si>
   <si>
-    <t>1 column</t>
-  </si>
-  <si>
-    <t>UltiMate3000</t>
+    <t>Solvent Vials</t>
+  </si>
+  <si>
+    <t>Plate 4</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Injection volume:</t>
+  </si>
+  <si>
+    <t>System configuration:</t>
+  </si>
+  <si>
+    <t>Analytical Columns:</t>
+  </si>
+  <si>
+    <t>For 2 column, "ChannelA_" or "ChannelB_" is added before column K (LC method file name)</t>
+  </si>
+  <si>
+    <t>Library runs placement:</t>
+  </si>
+  <si>
+    <t>Do Library runs come before or after the experiment?</t>
+  </si>
+  <si>
+    <t>NonCondition Ordering: QC-&gt;Blank-&gt;Trueblank</t>
+  </si>
+  <si>
+    <t>What MS system are you using?</t>
+  </si>
+  <si>
+    <t>This determines if the run number is included at the end of each file name</t>
+  </si>
+  <si>
+    <t>Before</t>
+  </si>
+  <si>
+    <t>2 column</t>
+  </si>
+  <si>
+    <t>Vanquish Neo</t>
+  </si>
+  <si>
+    <t>Bruker</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -385,8 +418,20 @@
       <color theme="0"/>
       <name val="Aptos Narrow (Body)"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow (Body)"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -489,8 +534,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF44B3E1"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -658,11 +709,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyProtection="1">
@@ -708,7 +768,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -718,8 +777,6 @@
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
@@ -883,6 +940,41 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -892,21 +984,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1255,7 +1349,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AU63"/>
+  <dimension ref="A1:AU76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1284,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AD1" s="5" t="s">
         <v>1</v>
@@ -1299,17 +1393,17 @@
         <v>4</v>
       </c>
       <c r="AH1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM1" s="27"/>
-      <c r="AO1" s="26"/>
+        <v>89</v>
+      </c>
+      <c r="AM1" s="26"/>
+      <c r="AO1" s="25"/>
     </row>
     <row r="2" spans="1:47" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AD2" s="11">
         <v>1</v>
@@ -1317,19 +1411,19 @@
       <c r="AE2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AF2" s="74" t="s">
-        <v>68</v>
+      <c r="AF2" s="71" t="s">
+        <v>66</v>
       </c>
       <c r="AG2" s="24">
         <v>1</v>
       </c>
-      <c r="AI2" s="29"/>
-      <c r="AJ2" s="29"/>
-      <c r="AK2" s="29"/>
+      <c r="AI2" s="28"/>
+      <c r="AJ2" s="28"/>
+      <c r="AK2" s="28"/>
       <c r="AL2" s="9"/>
       <c r="AM2" s="9"/>
       <c r="AN2" s="9"/>
-      <c r="AO2" s="26"/>
+      <c r="AO2" s="25"/>
     </row>
     <row r="3" spans="1:47" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -1344,19 +1438,19 @@
       <c r="AE3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AF3" s="75" t="s">
-        <v>69</v>
+      <c r="AF3" s="72" t="s">
+        <v>67</v>
       </c>
       <c r="AG3" s="24">
         <v>1</v>
       </c>
-      <c r="AI3" s="29"/>
-      <c r="AJ3" s="29"/>
-      <c r="AK3" s="29"/>
+      <c r="AI3" s="28"/>
+      <c r="AJ3" s="28"/>
+      <c r="AK3" s="28"/>
       <c r="AL3" s="9"/>
       <c r="AM3" s="9"/>
       <c r="AN3" s="9"/>
-      <c r="AO3" s="26"/>
+      <c r="AO3" s="25"/>
       <c r="AU3" s="18"/>
     </row>
     <row r="4" spans="1:47" x14ac:dyDescent="0.2">
@@ -1393,8 +1487,8 @@
       <c r="AE4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AF4" s="76" t="s">
-        <v>70</v>
+      <c r="AF4" s="73" t="s">
+        <v>68</v>
       </c>
       <c r="AG4" s="24">
         <v>1</v>
@@ -1405,13 +1499,13 @@
       <c r="AJ4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AK4" s="87" t="s">
+      <c r="AK4" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="AL4" s="88"/>
+      <c r="AL4" s="100"/>
       <c r="AM4" s="9"/>
       <c r="AN4" s="9"/>
-      <c r="AO4" s="26"/>
+      <c r="AO4" s="25"/>
     </row>
     <row r="5" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
@@ -1501,104 +1595,104 @@
       <c r="AE5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AF5" s="77" t="s">
-        <v>71</v>
+      <c r="AF5" s="74" t="s">
+        <v>69</v>
       </c>
       <c r="AG5" s="24">
         <v>1</v>
       </c>
       <c r="AI5" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AJ5" s="6"/>
-      <c r="AK5" s="87" t="s">
-        <v>93</v>
-      </c>
-      <c r="AL5" s="88"/>
+      <c r="AK5" s="99" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL5" s="100"/>
       <c r="AM5" s="9"/>
       <c r="AN5" s="9"/>
-      <c r="AO5" s="26"/>
+      <c r="AO5" s="25"/>
     </row>
     <row r="6" spans="1:47" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="84" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="39">
+      <c r="E6" s="36">
         <v>13</v>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="37">
         <v>13</v>
       </c>
-      <c r="G6" s="58">
-        <v>1</v>
-      </c>
-      <c r="H6" s="58">
-        <v>1</v>
-      </c>
-      <c r="I6" s="58">
-        <v>1</v>
-      </c>
-      <c r="J6" s="58">
-        <v>1</v>
-      </c>
-      <c r="K6" s="58">
-        <v>1</v>
-      </c>
-      <c r="L6" s="60">
-        <v>2</v>
-      </c>
-      <c r="M6" s="60">
-        <v>2</v>
-      </c>
-      <c r="N6" s="60">
-        <v>2</v>
-      </c>
-      <c r="O6" s="60">
-        <v>2</v>
-      </c>
-      <c r="P6" s="60">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="62">
-        <v>3</v>
-      </c>
-      <c r="R6" s="62">
-        <v>3</v>
-      </c>
-      <c r="S6" s="62">
-        <v>3</v>
-      </c>
-      <c r="T6" s="62">
-        <v>3</v>
-      </c>
-      <c r="U6" s="62">
-        <v>3</v>
-      </c>
-      <c r="V6" s="64">
-        <v>4</v>
-      </c>
-      <c r="W6" s="64">
-        <v>4</v>
-      </c>
-      <c r="X6" s="64">
-        <v>4</v>
-      </c>
-      <c r="Y6" s="64">
-        <v>4</v>
-      </c>
-      <c r="Z6" s="64">
-        <v>4</v>
-      </c>
-      <c r="AA6" s="34">
+      <c r="G6" s="55">
+        <v>1</v>
+      </c>
+      <c r="H6" s="55">
+        <v>1</v>
+      </c>
+      <c r="I6" s="55">
+        <v>1</v>
+      </c>
+      <c r="J6" s="55">
+        <v>1</v>
+      </c>
+      <c r="K6" s="55">
+        <v>1</v>
+      </c>
+      <c r="L6" s="57">
+        <v>2</v>
+      </c>
+      <c r="M6" s="57">
+        <v>2</v>
+      </c>
+      <c r="N6" s="57">
+        <v>2</v>
+      </c>
+      <c r="O6" s="57">
+        <v>2</v>
+      </c>
+      <c r="P6" s="57">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="59">
+        <v>3</v>
+      </c>
+      <c r="R6" s="59">
+        <v>3</v>
+      </c>
+      <c r="S6" s="59">
+        <v>3</v>
+      </c>
+      <c r="T6" s="59">
+        <v>3</v>
+      </c>
+      <c r="U6" s="59">
+        <v>3</v>
+      </c>
+      <c r="V6" s="61">
+        <v>4</v>
+      </c>
+      <c r="W6" s="61">
+        <v>4</v>
+      </c>
+      <c r="X6" s="61">
+        <v>4</v>
+      </c>
+      <c r="Y6" s="61">
+        <v>4</v>
+      </c>
+      <c r="Z6" s="61">
+        <v>4</v>
+      </c>
+      <c r="AA6" s="31">
         <v>14</v>
       </c>
-      <c r="AB6" s="35">
+      <c r="AB6" s="32">
         <v>14</v>
       </c>
       <c r="AD6" s="11">
@@ -1607,8 +1701,8 @@
       <c r="AE6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AF6" s="78" t="s">
-        <v>72</v>
+      <c r="AF6" s="75" t="s">
+        <v>70</v>
       </c>
       <c r="AG6" s="24">
         <v>1</v>
@@ -1616,82 +1710,82 @@
       <c r="AK6" s="18"/>
       <c r="AM6" s="9"/>
       <c r="AN6" s="9"/>
-      <c r="AO6" s="26"/>
+      <c r="AO6" s="25"/>
     </row>
     <row r="7" spans="1:47" x14ac:dyDescent="0.2">
       <c r="D7" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="41">
+      <c r="E7" s="38">
         <v>13</v>
       </c>
-      <c r="F7" s="42">
+      <c r="F7" s="39">
         <v>13</v>
       </c>
-      <c r="G7" s="59">
-        <v>1</v>
-      </c>
-      <c r="H7" s="59">
-        <v>1</v>
-      </c>
-      <c r="I7" s="59">
-        <v>1</v>
-      </c>
-      <c r="J7" s="59">
-        <v>1</v>
-      </c>
-      <c r="K7" s="59">
-        <v>1</v>
-      </c>
-      <c r="L7" s="61">
-        <v>2</v>
-      </c>
-      <c r="M7" s="61">
-        <v>2</v>
-      </c>
-      <c r="N7" s="61">
-        <v>2</v>
-      </c>
-      <c r="O7" s="61">
-        <v>2</v>
-      </c>
-      <c r="P7" s="61">
-        <v>2</v>
-      </c>
-      <c r="Q7" s="63">
-        <v>3</v>
-      </c>
-      <c r="R7" s="63">
-        <v>3</v>
-      </c>
-      <c r="S7" s="63">
-        <v>3</v>
-      </c>
-      <c r="T7" s="63">
-        <v>3</v>
-      </c>
-      <c r="U7" s="63">
-        <v>3</v>
-      </c>
-      <c r="V7" s="65">
-        <v>4</v>
-      </c>
-      <c r="W7" s="65">
-        <v>4</v>
-      </c>
-      <c r="X7" s="65">
-        <v>4</v>
-      </c>
-      <c r="Y7" s="65">
-        <v>4</v>
-      </c>
-      <c r="Z7" s="65">
-        <v>4</v>
-      </c>
-      <c r="AA7" s="36">
+      <c r="G7" s="56">
+        <v>1</v>
+      </c>
+      <c r="H7" s="56">
+        <v>1</v>
+      </c>
+      <c r="I7" s="56">
+        <v>1</v>
+      </c>
+      <c r="J7" s="56">
+        <v>1</v>
+      </c>
+      <c r="K7" s="56">
+        <v>1</v>
+      </c>
+      <c r="L7" s="58">
+        <v>2</v>
+      </c>
+      <c r="M7" s="58">
+        <v>2</v>
+      </c>
+      <c r="N7" s="58">
+        <v>2</v>
+      </c>
+      <c r="O7" s="58">
+        <v>2</v>
+      </c>
+      <c r="P7" s="58">
+        <v>2</v>
+      </c>
+      <c r="Q7" s="60">
+        <v>3</v>
+      </c>
+      <c r="R7" s="60">
+        <v>3</v>
+      </c>
+      <c r="S7" s="60">
+        <v>3</v>
+      </c>
+      <c r="T7" s="60">
+        <v>3</v>
+      </c>
+      <c r="U7" s="60">
+        <v>3</v>
+      </c>
+      <c r="V7" s="62">
+        <v>4</v>
+      </c>
+      <c r="W7" s="62">
+        <v>4</v>
+      </c>
+      <c r="X7" s="62">
+        <v>4</v>
+      </c>
+      <c r="Y7" s="62">
+        <v>4</v>
+      </c>
+      <c r="Z7" s="62">
+        <v>4</v>
+      </c>
+      <c r="AA7" s="33">
         <v>14</v>
       </c>
-      <c r="AB7" s="36">
+      <c r="AB7" s="33">
         <v>14</v>
       </c>
       <c r="AD7" s="11">
@@ -1700,90 +1794,90 @@
       <c r="AE7" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AF7" s="79" t="s">
-        <v>73</v>
+      <c r="AF7" s="76" t="s">
+        <v>71</v>
       </c>
       <c r="AG7" s="24">
         <v>1</v>
       </c>
       <c r="AM7" s="9"/>
       <c r="AN7" s="9"/>
-      <c r="AO7" s="26"/>
+      <c r="AO7" s="25"/>
     </row>
     <row r="8" spans="1:47" x14ac:dyDescent="0.2">
       <c r="D8" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="41">
+      <c r="E8" s="38">
         <v>13</v>
       </c>
-      <c r="F8" s="42">
+      <c r="F8" s="39">
         <v>13</v>
       </c>
-      <c r="G8" s="59">
-        <v>1</v>
-      </c>
-      <c r="H8" s="59">
-        <v>1</v>
-      </c>
-      <c r="I8" s="59">
-        <v>1</v>
-      </c>
-      <c r="J8" s="59">
-        <v>1</v>
-      </c>
-      <c r="K8" s="59">
-        <v>1</v>
-      </c>
-      <c r="L8" s="61">
-        <v>2</v>
-      </c>
-      <c r="M8" s="61">
-        <v>2</v>
-      </c>
-      <c r="N8" s="61">
-        <v>2</v>
-      </c>
-      <c r="O8" s="61">
-        <v>2</v>
-      </c>
-      <c r="P8" s="61">
-        <v>2</v>
-      </c>
-      <c r="Q8" s="63">
-        <v>3</v>
-      </c>
-      <c r="R8" s="63">
-        <v>3</v>
-      </c>
-      <c r="S8" s="63">
-        <v>3</v>
-      </c>
-      <c r="T8" s="63">
-        <v>3</v>
-      </c>
-      <c r="U8" s="63">
-        <v>3</v>
-      </c>
-      <c r="V8" s="65">
-        <v>4</v>
-      </c>
-      <c r="W8" s="65">
-        <v>4</v>
-      </c>
-      <c r="X8" s="65">
-        <v>4</v>
-      </c>
-      <c r="Y8" s="65">
-        <v>4</v>
-      </c>
-      <c r="Z8" s="65">
-        <v>4</v>
-      </c>
-      <c r="AA8" s="36">
+      <c r="G8" s="56">
+        <v>1</v>
+      </c>
+      <c r="H8" s="56">
+        <v>1</v>
+      </c>
+      <c r="I8" s="56">
+        <v>1</v>
+      </c>
+      <c r="J8" s="56">
+        <v>1</v>
+      </c>
+      <c r="K8" s="56">
+        <v>1</v>
+      </c>
+      <c r="L8" s="58">
+        <v>2</v>
+      </c>
+      <c r="M8" s="58">
+        <v>2</v>
+      </c>
+      <c r="N8" s="58">
+        <v>2</v>
+      </c>
+      <c r="O8" s="58">
+        <v>2</v>
+      </c>
+      <c r="P8" s="58">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="60">
+        <v>3</v>
+      </c>
+      <c r="R8" s="60">
+        <v>3</v>
+      </c>
+      <c r="S8" s="60">
+        <v>3</v>
+      </c>
+      <c r="T8" s="60">
+        <v>3</v>
+      </c>
+      <c r="U8" s="60">
+        <v>3</v>
+      </c>
+      <c r="V8" s="62">
+        <v>4</v>
+      </c>
+      <c r="W8" s="62">
+        <v>4</v>
+      </c>
+      <c r="X8" s="62">
+        <v>4</v>
+      </c>
+      <c r="Y8" s="62">
+        <v>4</v>
+      </c>
+      <c r="Z8" s="62">
+        <v>4</v>
+      </c>
+      <c r="AA8" s="33">
         <v>14</v>
       </c>
-      <c r="AB8" s="37">
+      <c r="AB8" s="34">
         <v>14</v>
       </c>
       <c r="AD8" s="11">
@@ -1792,100 +1886,103 @@
       <c r="AE8" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AF8" s="80" t="s">
-        <v>74</v>
+      <c r="AF8" s="77" t="s">
+        <v>72</v>
       </c>
       <c r="AG8" s="24">
         <v>1</v>
       </c>
       <c r="AI8" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AJ8" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="AK8" s="87" t="s">
+      <c r="AK8" s="99" t="s">
         <v>34</v>
       </c>
-      <c r="AL8" s="88"/>
+      <c r="AL8" s="100"/>
       <c r="AM8" s="9"/>
       <c r="AN8" s="9"/>
-      <c r="AO8" s="26"/>
+      <c r="AO8" s="25"/>
     </row>
     <row r="9" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="B9" s="26" t="s">
+        <v>101</v>
+      </c>
       <c r="D9" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="38">
         <v>13</v>
       </c>
-      <c r="F9" s="42">
+      <c r="F9" s="39">
         <v>13</v>
       </c>
-      <c r="G9" s="59">
-        <v>1</v>
-      </c>
-      <c r="H9" s="59">
-        <v>1</v>
-      </c>
-      <c r="I9" s="59">
-        <v>1</v>
-      </c>
-      <c r="J9" s="59">
-        <v>1</v>
-      </c>
-      <c r="K9" s="59">
-        <v>1</v>
-      </c>
-      <c r="L9" s="61">
-        <v>2</v>
-      </c>
-      <c r="M9" s="61">
-        <v>2</v>
-      </c>
-      <c r="N9" s="61">
-        <v>2</v>
-      </c>
-      <c r="O9" s="61">
-        <v>2</v>
-      </c>
-      <c r="P9" s="61">
-        <v>2</v>
-      </c>
-      <c r="Q9" s="63">
-        <v>3</v>
-      </c>
-      <c r="R9" s="63">
-        <v>3</v>
-      </c>
-      <c r="S9" s="63">
-        <v>3</v>
-      </c>
-      <c r="T9" s="63">
-        <v>3</v>
-      </c>
-      <c r="U9" s="63">
-        <v>3</v>
-      </c>
-      <c r="V9" s="65">
-        <v>4</v>
-      </c>
-      <c r="W9" s="65">
-        <v>4</v>
-      </c>
-      <c r="X9" s="65">
-        <v>4</v>
-      </c>
-      <c r="Y9" s="65">
-        <v>4</v>
-      </c>
-      <c r="Z9" s="65">
-        <v>4</v>
-      </c>
-      <c r="AA9" s="36">
+      <c r="G9" s="56">
+        <v>1</v>
+      </c>
+      <c r="H9" s="56">
+        <v>1</v>
+      </c>
+      <c r="I9" s="56">
+        <v>1</v>
+      </c>
+      <c r="J9" s="56">
+        <v>1</v>
+      </c>
+      <c r="K9" s="56">
+        <v>1</v>
+      </c>
+      <c r="L9" s="58">
+        <v>2</v>
+      </c>
+      <c r="M9" s="58">
+        <v>2</v>
+      </c>
+      <c r="N9" s="58">
+        <v>2</v>
+      </c>
+      <c r="O9" s="58">
+        <v>2</v>
+      </c>
+      <c r="P9" s="58">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="60">
+        <v>3</v>
+      </c>
+      <c r="R9" s="60">
+        <v>3</v>
+      </c>
+      <c r="S9" s="60">
+        <v>3</v>
+      </c>
+      <c r="T9" s="60">
+        <v>3</v>
+      </c>
+      <c r="U9" s="60">
+        <v>3</v>
+      </c>
+      <c r="V9" s="62">
+        <v>4</v>
+      </c>
+      <c r="W9" s="62">
+        <v>4</v>
+      </c>
+      <c r="X9" s="62">
+        <v>4</v>
+      </c>
+      <c r="Y9" s="62">
+        <v>4</v>
+      </c>
+      <c r="Z9" s="62">
+        <v>4</v>
+      </c>
+      <c r="AA9" s="33">
         <v>14</v>
       </c>
-      <c r="AB9" s="37">
+      <c r="AB9" s="34">
         <v>14</v>
       </c>
       <c r="AD9" s="11">
@@ -1894,96 +1991,100 @@
       <c r="AE9" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AF9" s="81" t="s">
-        <v>75</v>
+      <c r="AF9" s="78" t="s">
+        <v>73</v>
       </c>
       <c r="AG9" s="24">
         <v>1</v>
       </c>
       <c r="AI9" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="AJ9" s="6"/>
-      <c r="AK9" s="87"/>
-      <c r="AL9" s="88"/>
+      <c r="AK9" s="99"/>
+      <c r="AL9" s="100"/>
       <c r="AM9" s="9"/>
       <c r="AN9" s="9"/>
-      <c r="AO9" s="26"/>
+      <c r="AO9" s="25"/>
     </row>
     <row r="10" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10" s="10"/>
       <c r="D10" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="38">
         <v>13</v>
       </c>
-      <c r="F10" s="42">
+      <c r="F10" s="39">
         <v>13</v>
       </c>
-      <c r="G10" s="59">
-        <v>1</v>
-      </c>
-      <c r="H10" s="59">
-        <v>1</v>
-      </c>
-      <c r="I10" s="59">
-        <v>1</v>
-      </c>
-      <c r="J10" s="59">
-        <v>1</v>
-      </c>
-      <c r="K10" s="59">
-        <v>1</v>
-      </c>
-      <c r="L10" s="61">
-        <v>2</v>
-      </c>
-      <c r="M10" s="61">
-        <v>2</v>
-      </c>
-      <c r="N10" s="61">
-        <v>2</v>
-      </c>
-      <c r="O10" s="61">
-        <v>2</v>
-      </c>
-      <c r="P10" s="61">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="63">
-        <v>3</v>
-      </c>
-      <c r="R10" s="63">
-        <v>3</v>
-      </c>
-      <c r="S10" s="63">
-        <v>3</v>
-      </c>
-      <c r="T10" s="63">
-        <v>3</v>
-      </c>
-      <c r="U10" s="63">
-        <v>3</v>
-      </c>
-      <c r="V10" s="65">
-        <v>4</v>
-      </c>
-      <c r="W10" s="65">
-        <v>4</v>
-      </c>
-      <c r="X10" s="65">
-        <v>4</v>
-      </c>
-      <c r="Y10" s="65">
-        <v>4</v>
-      </c>
-      <c r="Z10" s="65">
-        <v>4</v>
-      </c>
-      <c r="AA10" s="36">
+      <c r="G10" s="56">
+        <v>1</v>
+      </c>
+      <c r="H10" s="56">
+        <v>1</v>
+      </c>
+      <c r="I10" s="56">
+        <v>1</v>
+      </c>
+      <c r="J10" s="56">
+        <v>1</v>
+      </c>
+      <c r="K10" s="56">
+        <v>1</v>
+      </c>
+      <c r="L10" s="58">
+        <v>2</v>
+      </c>
+      <c r="M10" s="58">
+        <v>2</v>
+      </c>
+      <c r="N10" s="58">
+        <v>2</v>
+      </c>
+      <c r="O10" s="58">
+        <v>2</v>
+      </c>
+      <c r="P10" s="58">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="60">
+        <v>3</v>
+      </c>
+      <c r="R10" s="60">
+        <v>3</v>
+      </c>
+      <c r="S10" s="60">
+        <v>3</v>
+      </c>
+      <c r="T10" s="60">
+        <v>3</v>
+      </c>
+      <c r="U10" s="60">
+        <v>3</v>
+      </c>
+      <c r="V10" s="62">
+        <v>4</v>
+      </c>
+      <c r="W10" s="62">
+        <v>4</v>
+      </c>
+      <c r="X10" s="62">
+        <v>4</v>
+      </c>
+      <c r="Y10" s="62">
+        <v>4</v>
+      </c>
+      <c r="Z10" s="62">
+        <v>4</v>
+      </c>
+      <c r="AA10" s="33">
         <v>14</v>
       </c>
-      <c r="AB10" s="37">
+      <c r="AB10" s="34">
         <v>14</v>
       </c>
       <c r="AD10" s="11">
@@ -1992,98 +2093,102 @@
       <c r="AE10" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AF10" s="82" t="s">
-        <v>76</v>
+      <c r="AF10" s="79" t="s">
+        <v>74</v>
       </c>
       <c r="AG10" s="24">
         <v>1</v>
       </c>
-      <c r="AI10" s="89" t="s">
+      <c r="AI10" s="101" t="s">
         <v>35</v>
       </c>
-      <c r="AJ10" s="90" t="s">
+      <c r="AJ10" s="103" t="s">
         <v>31</v>
       </c>
-      <c r="AK10" s="87"/>
-      <c r="AL10" s="88"/>
+      <c r="AK10" s="99"/>
+      <c r="AL10" s="100"/>
       <c r="AM10" s="9"/>
       <c r="AN10" s="9"/>
-      <c r="AO10" s="26"/>
+      <c r="AO10" s="25"/>
     </row>
     <row r="11" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11" s="10"/>
       <c r="D11" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="38">
         <v>13</v>
       </c>
-      <c r="F11" s="42">
+      <c r="F11" s="39">
         <v>13</v>
       </c>
-      <c r="G11" s="59">
-        <v>1</v>
-      </c>
-      <c r="H11" s="59">
-        <v>1</v>
-      </c>
-      <c r="I11" s="59">
-        <v>1</v>
-      </c>
-      <c r="J11" s="59">
-        <v>1</v>
-      </c>
-      <c r="K11" s="59">
-        <v>1</v>
-      </c>
-      <c r="L11" s="61">
-        <v>2</v>
-      </c>
-      <c r="M11" s="61">
-        <v>2</v>
-      </c>
-      <c r="N11" s="61">
-        <v>2</v>
-      </c>
-      <c r="O11" s="61">
-        <v>2</v>
-      </c>
-      <c r="P11" s="61">
-        <v>2</v>
-      </c>
-      <c r="Q11" s="63">
-        <v>3</v>
-      </c>
-      <c r="R11" s="63">
-        <v>3</v>
-      </c>
-      <c r="S11" s="63">
-        <v>3</v>
-      </c>
-      <c r="T11" s="63">
-        <v>3</v>
-      </c>
-      <c r="U11" s="63">
-        <v>3</v>
-      </c>
-      <c r="V11" s="65">
-        <v>4</v>
-      </c>
-      <c r="W11" s="65">
-        <v>4</v>
-      </c>
-      <c r="X11" s="65">
-        <v>4</v>
-      </c>
-      <c r="Y11" s="65">
-        <v>4</v>
-      </c>
-      <c r="Z11" s="65">
-        <v>4</v>
-      </c>
-      <c r="AA11" s="36">
+      <c r="G11" s="56">
+        <v>1</v>
+      </c>
+      <c r="H11" s="56">
+        <v>1</v>
+      </c>
+      <c r="I11" s="56">
+        <v>1</v>
+      </c>
+      <c r="J11" s="56">
+        <v>1</v>
+      </c>
+      <c r="K11" s="56">
+        <v>1</v>
+      </c>
+      <c r="L11" s="58">
+        <v>2</v>
+      </c>
+      <c r="M11" s="58">
+        <v>2</v>
+      </c>
+      <c r="N11" s="58">
+        <v>2</v>
+      </c>
+      <c r="O11" s="58">
+        <v>2</v>
+      </c>
+      <c r="P11" s="58">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="60">
+        <v>3</v>
+      </c>
+      <c r="R11" s="60">
+        <v>3</v>
+      </c>
+      <c r="S11" s="60">
+        <v>3</v>
+      </c>
+      <c r="T11" s="60">
+        <v>3</v>
+      </c>
+      <c r="U11" s="60">
+        <v>3</v>
+      </c>
+      <c r="V11" s="62">
+        <v>4</v>
+      </c>
+      <c r="W11" s="62">
+        <v>4</v>
+      </c>
+      <c r="X11" s="62">
+        <v>4</v>
+      </c>
+      <c r="Y11" s="62">
+        <v>4</v>
+      </c>
+      <c r="Z11" s="62">
+        <v>4</v>
+      </c>
+      <c r="AA11" s="33">
         <v>14</v>
       </c>
-      <c r="AB11" s="37">
+      <c r="AB11" s="34">
         <v>14</v>
       </c>
       <c r="AD11" s="11">
@@ -2092,94 +2197,98 @@
       <c r="AE11" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AF11" s="83" t="s">
-        <v>77</v>
+      <c r="AF11" s="80" t="s">
+        <v>75</v>
       </c>
       <c r="AG11" s="24">
         <v>1</v>
       </c>
-      <c r="AI11" s="91"/>
-      <c r="AJ11" s="92"/>
-      <c r="AK11" s="28"/>
-      <c r="AL11" s="28"/>
+      <c r="AI11" s="102"/>
+      <c r="AJ11" s="104"/>
+      <c r="AK11" s="27"/>
+      <c r="AL11" s="27"/>
       <c r="AM11" s="9"/>
       <c r="AN11" s="9"/>
-      <c r="AO11" s="26"/>
+      <c r="AO11" s="25"/>
     </row>
     <row r="12" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>3</v>
+      </c>
+      <c r="B12" s="10"/>
       <c r="D12" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="38">
         <v>13</v>
       </c>
-      <c r="F12" s="42">
+      <c r="F12" s="39">
         <v>13</v>
       </c>
-      <c r="G12" s="59">
-        <v>1</v>
-      </c>
-      <c r="H12" s="59">
-        <v>1</v>
-      </c>
-      <c r="I12" s="59">
-        <v>1</v>
-      </c>
-      <c r="J12" s="59">
-        <v>1</v>
-      </c>
-      <c r="K12" s="59">
-        <v>1</v>
-      </c>
-      <c r="L12" s="61">
-        <v>2</v>
-      </c>
-      <c r="M12" s="61">
-        <v>2</v>
-      </c>
-      <c r="N12" s="61">
-        <v>2</v>
-      </c>
-      <c r="O12" s="61">
-        <v>2</v>
-      </c>
-      <c r="P12" s="61">
-        <v>2</v>
-      </c>
-      <c r="Q12" s="63">
-        <v>3</v>
-      </c>
-      <c r="R12" s="63">
-        <v>3</v>
-      </c>
-      <c r="S12" s="63">
-        <v>3</v>
-      </c>
-      <c r="T12" s="63">
-        <v>3</v>
-      </c>
-      <c r="U12" s="63">
-        <v>3</v>
-      </c>
-      <c r="V12" s="65">
-        <v>4</v>
-      </c>
-      <c r="W12" s="65">
-        <v>4</v>
-      </c>
-      <c r="X12" s="65">
-        <v>4</v>
-      </c>
-      <c r="Y12" s="65">
-        <v>4</v>
-      </c>
-      <c r="Z12" s="65">
-        <v>4</v>
-      </c>
-      <c r="AA12" s="36">
+      <c r="G12" s="56">
+        <v>1</v>
+      </c>
+      <c r="H12" s="56">
+        <v>1</v>
+      </c>
+      <c r="I12" s="56">
+        <v>1</v>
+      </c>
+      <c r="J12" s="56">
+        <v>1</v>
+      </c>
+      <c r="K12" s="56">
+        <v>1</v>
+      </c>
+      <c r="L12" s="58">
+        <v>2</v>
+      </c>
+      <c r="M12" s="58">
+        <v>2</v>
+      </c>
+      <c r="N12" s="58">
+        <v>2</v>
+      </c>
+      <c r="O12" s="58">
+        <v>2</v>
+      </c>
+      <c r="P12" s="58">
+        <v>2</v>
+      </c>
+      <c r="Q12" s="60">
+        <v>3</v>
+      </c>
+      <c r="R12" s="60">
+        <v>3</v>
+      </c>
+      <c r="S12" s="60">
+        <v>3</v>
+      </c>
+      <c r="T12" s="60">
+        <v>3</v>
+      </c>
+      <c r="U12" s="60">
+        <v>3</v>
+      </c>
+      <c r="V12" s="62">
+        <v>4</v>
+      </c>
+      <c r="W12" s="62">
+        <v>4</v>
+      </c>
+      <c r="X12" s="62">
+        <v>4</v>
+      </c>
+      <c r="Y12" s="62">
+        <v>4</v>
+      </c>
+      <c r="Z12" s="62">
+        <v>4</v>
+      </c>
+      <c r="AA12" s="33">
         <v>14</v>
       </c>
-      <c r="AB12" s="37">
+      <c r="AB12" s="34">
         <v>14</v>
       </c>
       <c r="AD12" s="11">
@@ -2188,94 +2297,98 @@
       <c r="AE12" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AF12" s="84" t="s">
-        <v>78</v>
+      <c r="AF12" s="81" t="s">
+        <v>76</v>
       </c>
       <c r="AG12" s="24">
         <v>1</v>
       </c>
-      <c r="AI12" s="29"/>
-      <c r="AJ12" s="29"/>
-      <c r="AK12" s="29"/>
+      <c r="AI12" s="28"/>
+      <c r="AJ12" s="28"/>
+      <c r="AK12" s="28"/>
       <c r="AL12" s="9"/>
       <c r="AM12" s="9"/>
       <c r="AN12" s="9"/>
-      <c r="AO12" s="26"/>
+      <c r="AO12" s="25"/>
     </row>
     <row r="13" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="B13" s="10"/>
       <c r="D13" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="38">
         <v>13</v>
       </c>
-      <c r="F13" s="42">
+      <c r="F13" s="39">
         <v>13</v>
       </c>
-      <c r="G13" s="59">
-        <v>1</v>
-      </c>
-      <c r="H13" s="59">
-        <v>1</v>
-      </c>
-      <c r="I13" s="59">
-        <v>1</v>
-      </c>
-      <c r="J13" s="59">
-        <v>1</v>
-      </c>
-      <c r="K13" s="59">
-        <v>1</v>
-      </c>
-      <c r="L13" s="61">
-        <v>2</v>
-      </c>
-      <c r="M13" s="61">
-        <v>2</v>
-      </c>
-      <c r="N13" s="61">
-        <v>2</v>
-      </c>
-      <c r="O13" s="61">
-        <v>2</v>
-      </c>
-      <c r="P13" s="61">
-        <v>2</v>
-      </c>
-      <c r="Q13" s="63">
-        <v>3</v>
-      </c>
-      <c r="R13" s="63">
-        <v>3</v>
-      </c>
-      <c r="S13" s="63">
-        <v>3</v>
-      </c>
-      <c r="T13" s="63">
-        <v>3</v>
-      </c>
-      <c r="U13" s="63">
-        <v>3</v>
-      </c>
-      <c r="V13" s="65">
-        <v>4</v>
-      </c>
-      <c r="W13" s="65">
-        <v>4</v>
-      </c>
-      <c r="X13" s="65">
-        <v>4</v>
-      </c>
-      <c r="Y13" s="65">
-        <v>4</v>
-      </c>
-      <c r="Z13" s="65">
-        <v>4</v>
-      </c>
-      <c r="AA13" s="36">
+      <c r="G13" s="56">
+        <v>1</v>
+      </c>
+      <c r="H13" s="56">
+        <v>1</v>
+      </c>
+      <c r="I13" s="56">
+        <v>1</v>
+      </c>
+      <c r="J13" s="56">
+        <v>1</v>
+      </c>
+      <c r="K13" s="56">
+        <v>1</v>
+      </c>
+      <c r="L13" s="58">
+        <v>2</v>
+      </c>
+      <c r="M13" s="58">
+        <v>2</v>
+      </c>
+      <c r="N13" s="58">
+        <v>2</v>
+      </c>
+      <c r="O13" s="58">
+        <v>2</v>
+      </c>
+      <c r="P13" s="58">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="60">
+        <v>3</v>
+      </c>
+      <c r="R13" s="60">
+        <v>3</v>
+      </c>
+      <c r="S13" s="60">
+        <v>3</v>
+      </c>
+      <c r="T13" s="60">
+        <v>3</v>
+      </c>
+      <c r="U13" s="60">
+        <v>3</v>
+      </c>
+      <c r="V13" s="62">
+        <v>4</v>
+      </c>
+      <c r="W13" s="62">
+        <v>4</v>
+      </c>
+      <c r="X13" s="62">
+        <v>4</v>
+      </c>
+      <c r="Y13" s="62">
+        <v>4</v>
+      </c>
+      <c r="Z13" s="62">
+        <v>4</v>
+      </c>
+      <c r="AA13" s="33">
         <v>14</v>
       </c>
-      <c r="AB13" s="37">
+      <c r="AB13" s="34">
         <v>14</v>
       </c>
       <c r="AD13" s="11">
@@ -2284,558 +2397,562 @@
       <c r="AE13" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AF13" s="85" t="s">
-        <v>79</v>
+      <c r="AF13" s="82" t="s">
+        <v>77</v>
       </c>
       <c r="AG13" s="24">
         <v>1</v>
       </c>
-      <c r="AI13" s="29"/>
-      <c r="AJ13" s="29"/>
-      <c r="AK13" s="29"/>
+      <c r="AI13" s="28"/>
+      <c r="AJ13" s="28"/>
+      <c r="AK13" s="28"/>
       <c r="AL13" s="9"/>
       <c r="AM13" s="9"/>
       <c r="AN13" s="9"/>
-      <c r="AO13" s="26"/>
+      <c r="AO13" s="25"/>
     </row>
     <row r="14" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>5</v>
+      </c>
+      <c r="B14" s="16"/>
       <c r="D14" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="38">
         <v>13</v>
       </c>
-      <c r="F14" s="42">
+      <c r="F14" s="39">
         <v>13</v>
       </c>
-      <c r="G14" s="59">
-        <v>1</v>
-      </c>
-      <c r="H14" s="59">
-        <v>1</v>
-      </c>
-      <c r="I14" s="59">
-        <v>1</v>
-      </c>
-      <c r="J14" s="59">
-        <v>1</v>
-      </c>
-      <c r="K14" s="59">
-        <v>1</v>
-      </c>
-      <c r="L14" s="61">
-        <v>2</v>
-      </c>
-      <c r="M14" s="61">
-        <v>2</v>
-      </c>
-      <c r="N14" s="61">
-        <v>2</v>
-      </c>
-      <c r="O14" s="61">
-        <v>2</v>
-      </c>
-      <c r="P14" s="61">
-        <v>2</v>
-      </c>
-      <c r="Q14" s="63">
-        <v>3</v>
-      </c>
-      <c r="R14" s="63">
-        <v>3</v>
-      </c>
-      <c r="S14" s="63">
-        <v>3</v>
-      </c>
-      <c r="T14" s="63">
-        <v>3</v>
-      </c>
-      <c r="U14" s="63">
-        <v>3</v>
-      </c>
-      <c r="V14" s="65">
-        <v>4</v>
-      </c>
-      <c r="W14" s="65">
-        <v>4</v>
-      </c>
-      <c r="X14" s="65">
-        <v>4</v>
-      </c>
-      <c r="Y14" s="65">
-        <v>4</v>
-      </c>
-      <c r="Z14" s="65">
-        <v>4</v>
-      </c>
-      <c r="AA14" s="36">
+      <c r="G14" s="56">
+        <v>1</v>
+      </c>
+      <c r="H14" s="56">
+        <v>1</v>
+      </c>
+      <c r="I14" s="56">
+        <v>1</v>
+      </c>
+      <c r="J14" s="56">
+        <v>1</v>
+      </c>
+      <c r="K14" s="56">
+        <v>1</v>
+      </c>
+      <c r="L14" s="58">
+        <v>2</v>
+      </c>
+      <c r="M14" s="58">
+        <v>2</v>
+      </c>
+      <c r="N14" s="58">
+        <v>2</v>
+      </c>
+      <c r="O14" s="58">
+        <v>2</v>
+      </c>
+      <c r="P14" s="58">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="60">
+        <v>3</v>
+      </c>
+      <c r="R14" s="60">
+        <v>3</v>
+      </c>
+      <c r="S14" s="60">
+        <v>3</v>
+      </c>
+      <c r="T14" s="60">
+        <v>3</v>
+      </c>
+      <c r="U14" s="60">
+        <v>3</v>
+      </c>
+      <c r="V14" s="62">
+        <v>4</v>
+      </c>
+      <c r="W14" s="62">
+        <v>4</v>
+      </c>
+      <c r="X14" s="62">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="62">
+        <v>4</v>
+      </c>
+      <c r="Z14" s="62">
+        <v>4</v>
+      </c>
+      <c r="AA14" s="33">
         <v>14</v>
       </c>
-      <c r="AB14" s="37">
+      <c r="AB14" s="34">
         <v>14</v>
       </c>
       <c r="AD14" s="11">
         <v>13</v>
       </c>
       <c r="AE14" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF14" s="38" t="s">
-        <v>47</v>
+        <v>46</v>
+      </c>
+      <c r="AF14" s="35" t="s">
+        <v>46</v>
       </c>
       <c r="AG14" s="24">
         <v>1</v>
       </c>
       <c r="AM14" s="9"/>
       <c r="AN14" s="9"/>
-      <c r="AO14" s="26"/>
+      <c r="AO14" s="25"/>
     </row>
     <row r="15" spans="1:47" x14ac:dyDescent="0.2">
       <c r="D15" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="41">
+      <c r="E15" s="38">
         <v>13</v>
       </c>
-      <c r="F15" s="42">
+      <c r="F15" s="39">
         <v>13</v>
       </c>
-      <c r="G15" s="59">
-        <v>1</v>
-      </c>
-      <c r="H15" s="59">
-        <v>1</v>
-      </c>
-      <c r="I15" s="59">
-        <v>1</v>
-      </c>
-      <c r="J15" s="59">
-        <v>1</v>
-      </c>
-      <c r="K15" s="59">
-        <v>1</v>
-      </c>
-      <c r="L15" s="61">
-        <v>2</v>
-      </c>
-      <c r="M15" s="61">
-        <v>2</v>
-      </c>
-      <c r="N15" s="61">
-        <v>2</v>
-      </c>
-      <c r="O15" s="61">
-        <v>2</v>
-      </c>
-      <c r="P15" s="61">
-        <v>2</v>
-      </c>
-      <c r="Q15" s="63">
-        <v>3</v>
-      </c>
-      <c r="R15" s="63">
-        <v>3</v>
-      </c>
-      <c r="S15" s="63">
-        <v>3</v>
-      </c>
-      <c r="T15" s="63">
-        <v>3</v>
-      </c>
-      <c r="U15" s="63">
-        <v>3</v>
-      </c>
-      <c r="V15" s="65">
-        <v>4</v>
-      </c>
-      <c r="W15" s="65">
-        <v>4</v>
-      </c>
-      <c r="X15" s="65">
-        <v>4</v>
-      </c>
-      <c r="Y15" s="65">
-        <v>4</v>
-      </c>
-      <c r="Z15" s="65">
-        <v>4</v>
-      </c>
-      <c r="AA15" s="36">
+      <c r="G15" s="56">
+        <v>1</v>
+      </c>
+      <c r="H15" s="56">
+        <v>1</v>
+      </c>
+      <c r="I15" s="56">
+        <v>1</v>
+      </c>
+      <c r="J15" s="56">
+        <v>1</v>
+      </c>
+      <c r="K15" s="56">
+        <v>1</v>
+      </c>
+      <c r="L15" s="58">
+        <v>2</v>
+      </c>
+      <c r="M15" s="58">
+        <v>2</v>
+      </c>
+      <c r="N15" s="58">
+        <v>2</v>
+      </c>
+      <c r="O15" s="58">
+        <v>2</v>
+      </c>
+      <c r="P15" s="58">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="60">
+        <v>3</v>
+      </c>
+      <c r="R15" s="60">
+        <v>3</v>
+      </c>
+      <c r="S15" s="60">
+        <v>3</v>
+      </c>
+      <c r="T15" s="60">
+        <v>3</v>
+      </c>
+      <c r="U15" s="60">
+        <v>3</v>
+      </c>
+      <c r="V15" s="62">
+        <v>4</v>
+      </c>
+      <c r="W15" s="62">
+        <v>4</v>
+      </c>
+      <c r="X15" s="62">
+        <v>4</v>
+      </c>
+      <c r="Y15" s="62">
+        <v>4</v>
+      </c>
+      <c r="Z15" s="62">
+        <v>4</v>
+      </c>
+      <c r="AA15" s="33">
         <v>14</v>
       </c>
-      <c r="AB15" s="37">
+      <c r="AB15" s="34">
         <v>14</v>
       </c>
       <c r="AD15" s="11">
         <v>14</v>
       </c>
       <c r="AE15" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF15" s="30" t="s">
         <v>48</v>
-      </c>
-      <c r="AF15" s="33" t="s">
-        <v>49</v>
       </c>
       <c r="AG15" s="24">
         <v>1</v>
       </c>
       <c r="AM15" s="9"/>
       <c r="AN15" s="9"/>
-      <c r="AO15" s="26"/>
+      <c r="AO15" s="25"/>
     </row>
     <row r="16" spans="1:47" x14ac:dyDescent="0.2">
       <c r="D16" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="38">
         <v>13</v>
       </c>
-      <c r="F16" s="42">
+      <c r="F16" s="39">
         <v>13</v>
       </c>
-      <c r="G16" s="59">
-        <v>1</v>
-      </c>
-      <c r="H16" s="59">
-        <v>1</v>
-      </c>
-      <c r="I16" s="59">
-        <v>1</v>
-      </c>
-      <c r="J16" s="59">
-        <v>1</v>
-      </c>
-      <c r="K16" s="59">
-        <v>1</v>
-      </c>
-      <c r="L16" s="61">
-        <v>2</v>
-      </c>
-      <c r="M16" s="61">
-        <v>2</v>
-      </c>
-      <c r="N16" s="61">
-        <v>2</v>
-      </c>
-      <c r="O16" s="61">
-        <v>2</v>
-      </c>
-      <c r="P16" s="61">
-        <v>2</v>
-      </c>
-      <c r="Q16" s="63">
-        <v>3</v>
-      </c>
-      <c r="R16" s="63">
-        <v>3</v>
-      </c>
-      <c r="S16" s="63">
-        <v>3</v>
-      </c>
-      <c r="T16" s="63">
-        <v>3</v>
-      </c>
-      <c r="U16" s="63">
-        <v>3</v>
-      </c>
-      <c r="V16" s="65">
-        <v>4</v>
-      </c>
-      <c r="W16" s="65">
-        <v>4</v>
-      </c>
-      <c r="X16" s="65">
-        <v>4</v>
-      </c>
-      <c r="Y16" s="65">
-        <v>4</v>
-      </c>
-      <c r="Z16" s="65">
-        <v>4</v>
-      </c>
-      <c r="AA16" s="36">
+      <c r="G16" s="56">
+        <v>1</v>
+      </c>
+      <c r="H16" s="56">
+        <v>1</v>
+      </c>
+      <c r="I16" s="56">
+        <v>1</v>
+      </c>
+      <c r="J16" s="56">
+        <v>1</v>
+      </c>
+      <c r="K16" s="56">
+        <v>1</v>
+      </c>
+      <c r="L16" s="58">
+        <v>2</v>
+      </c>
+      <c r="M16" s="58">
+        <v>2</v>
+      </c>
+      <c r="N16" s="58">
+        <v>2</v>
+      </c>
+      <c r="O16" s="58">
+        <v>2</v>
+      </c>
+      <c r="P16" s="58">
+        <v>2</v>
+      </c>
+      <c r="Q16" s="60">
+        <v>3</v>
+      </c>
+      <c r="R16" s="60">
+        <v>3</v>
+      </c>
+      <c r="S16" s="60">
+        <v>3</v>
+      </c>
+      <c r="T16" s="60">
+        <v>3</v>
+      </c>
+      <c r="U16" s="60">
+        <v>3</v>
+      </c>
+      <c r="V16" s="62">
+        <v>4</v>
+      </c>
+      <c r="W16" s="62">
+        <v>4</v>
+      </c>
+      <c r="X16" s="62">
+        <v>4</v>
+      </c>
+      <c r="Y16" s="62">
+        <v>4</v>
+      </c>
+      <c r="Z16" s="62">
+        <v>4</v>
+      </c>
+      <c r="AA16" s="33">
         <v>14</v>
       </c>
-      <c r="AB16" s="37">
+      <c r="AB16" s="34">
         <v>14</v>
       </c>
       <c r="AD16" s="11">
         <v>15</v>
       </c>
       <c r="AE16" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF16" s="44" t="s">
-        <v>50</v>
+        <v>49</v>
+      </c>
+      <c r="AF16" s="41" t="s">
+        <v>49</v>
       </c>
       <c r="AG16" s="24">
         <v>1</v>
       </c>
       <c r="AM16" s="9"/>
       <c r="AN16" s="9"/>
-      <c r="AO16" s="26"/>
+      <c r="AO16" s="25"/>
     </row>
     <row r="17" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D17" t="s">
         <v>24</v>
       </c>
-      <c r="E17" s="41">
+      <c r="E17" s="38">
         <v>13</v>
       </c>
-      <c r="F17" s="42">
+      <c r="F17" s="39">
         <v>13</v>
       </c>
-      <c r="G17" s="59">
-        <v>1</v>
-      </c>
-      <c r="H17" s="59">
-        <v>1</v>
-      </c>
-      <c r="I17" s="59">
-        <v>1</v>
-      </c>
-      <c r="J17" s="59">
-        <v>1</v>
-      </c>
-      <c r="K17" s="59">
-        <v>1</v>
-      </c>
-      <c r="L17" s="61">
-        <v>2</v>
-      </c>
-      <c r="M17" s="61">
-        <v>2</v>
-      </c>
-      <c r="N17" s="61">
-        <v>2</v>
-      </c>
-      <c r="O17" s="61">
-        <v>2</v>
-      </c>
-      <c r="P17" s="61">
-        <v>2</v>
-      </c>
-      <c r="Q17" s="63">
-        <v>3</v>
-      </c>
-      <c r="R17" s="63">
-        <v>3</v>
-      </c>
-      <c r="S17" s="63">
-        <v>3</v>
-      </c>
-      <c r="T17" s="63">
-        <v>3</v>
-      </c>
-      <c r="U17" s="63">
-        <v>3</v>
-      </c>
-      <c r="V17" s="65">
-        <v>4</v>
-      </c>
-      <c r="W17" s="65">
-        <v>4</v>
-      </c>
-      <c r="X17" s="65">
-        <v>4</v>
-      </c>
-      <c r="Y17" s="65">
-        <v>4</v>
-      </c>
-      <c r="Z17" s="65">
-        <v>4</v>
-      </c>
-      <c r="AA17" s="36">
+      <c r="G17" s="56">
+        <v>1</v>
+      </c>
+      <c r="H17" s="56">
+        <v>1</v>
+      </c>
+      <c r="I17" s="56">
+        <v>1</v>
+      </c>
+      <c r="J17" s="56">
+        <v>1</v>
+      </c>
+      <c r="K17" s="56">
+        <v>1</v>
+      </c>
+      <c r="L17" s="58">
+        <v>2</v>
+      </c>
+      <c r="M17" s="58">
+        <v>2</v>
+      </c>
+      <c r="N17" s="58">
+        <v>2</v>
+      </c>
+      <c r="O17" s="58">
+        <v>2</v>
+      </c>
+      <c r="P17" s="58">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="60">
+        <v>3</v>
+      </c>
+      <c r="R17" s="60">
+        <v>3</v>
+      </c>
+      <c r="S17" s="60">
+        <v>3</v>
+      </c>
+      <c r="T17" s="60">
+        <v>3</v>
+      </c>
+      <c r="U17" s="60">
+        <v>3</v>
+      </c>
+      <c r="V17" s="62">
+        <v>4</v>
+      </c>
+      <c r="W17" s="62">
+        <v>4</v>
+      </c>
+      <c r="X17" s="62">
+        <v>4</v>
+      </c>
+      <c r="Y17" s="62">
+        <v>4</v>
+      </c>
+      <c r="Z17" s="62">
+        <v>4</v>
+      </c>
+      <c r="AA17" s="33">
         <v>14</v>
       </c>
-      <c r="AB17" s="37">
+      <c r="AB17" s="34">
         <v>14</v>
       </c>
       <c r="AD17" s="11">
         <v>16</v>
       </c>
       <c r="AE17" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF17" s="49" t="s">
-        <v>53</v>
+        <v>50</v>
+      </c>
+      <c r="AF17" s="46" t="s">
+        <v>52</v>
       </c>
       <c r="AG17" s="24">
         <v>1</v>
       </c>
       <c r="AM17" s="9"/>
       <c r="AN17" s="9"/>
-      <c r="AO17" s="26"/>
+      <c r="AO17" s="25"/>
     </row>
     <row r="18" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D18" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="41">
+      <c r="E18" s="38">
         <v>13</v>
       </c>
-      <c r="F18" s="42">
+      <c r="F18" s="39">
         <v>13</v>
       </c>
-      <c r="G18" s="59">
-        <v>1</v>
-      </c>
-      <c r="H18" s="59">
-        <v>1</v>
-      </c>
-      <c r="I18" s="59">
-        <v>1</v>
-      </c>
-      <c r="J18" s="59">
-        <v>1</v>
-      </c>
-      <c r="K18" s="59">
-        <v>1</v>
-      </c>
-      <c r="L18" s="61">
-        <v>2</v>
-      </c>
-      <c r="M18" s="61">
-        <v>2</v>
-      </c>
-      <c r="N18" s="61">
-        <v>2</v>
-      </c>
-      <c r="O18" s="61">
-        <v>2</v>
-      </c>
-      <c r="P18" s="61">
-        <v>2</v>
-      </c>
-      <c r="Q18" s="63">
-        <v>3</v>
-      </c>
-      <c r="R18" s="63">
-        <v>3</v>
-      </c>
-      <c r="S18" s="63">
-        <v>3</v>
-      </c>
-      <c r="T18" s="63">
-        <v>3</v>
-      </c>
-      <c r="U18" s="63">
-        <v>3</v>
-      </c>
-      <c r="V18" s="65">
-        <v>4</v>
-      </c>
-      <c r="W18" s="65">
-        <v>4</v>
-      </c>
-      <c r="X18" s="65">
-        <v>4</v>
-      </c>
-      <c r="Y18" s="65">
-        <v>4</v>
-      </c>
-      <c r="Z18" s="65">
-        <v>4</v>
-      </c>
-      <c r="AA18" s="36">
+      <c r="G18" s="56">
+        <v>1</v>
+      </c>
+      <c r="H18" s="56">
+        <v>1</v>
+      </c>
+      <c r="I18" s="56">
+        <v>1</v>
+      </c>
+      <c r="J18" s="56">
+        <v>1</v>
+      </c>
+      <c r="K18" s="56">
+        <v>1</v>
+      </c>
+      <c r="L18" s="58">
+        <v>2</v>
+      </c>
+      <c r="M18" s="58">
+        <v>2</v>
+      </c>
+      <c r="N18" s="58">
+        <v>2</v>
+      </c>
+      <c r="O18" s="58">
+        <v>2</v>
+      </c>
+      <c r="P18" s="58">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="60">
+        <v>3</v>
+      </c>
+      <c r="R18" s="60">
+        <v>3</v>
+      </c>
+      <c r="S18" s="60">
+        <v>3</v>
+      </c>
+      <c r="T18" s="60">
+        <v>3</v>
+      </c>
+      <c r="U18" s="60">
+        <v>3</v>
+      </c>
+      <c r="V18" s="62">
+        <v>4</v>
+      </c>
+      <c r="W18" s="62">
+        <v>4</v>
+      </c>
+      <c r="X18" s="62">
+        <v>4</v>
+      </c>
+      <c r="Y18" s="62">
+        <v>4</v>
+      </c>
+      <c r="Z18" s="62">
+        <v>4</v>
+      </c>
+      <c r="AA18" s="33">
         <v>14</v>
       </c>
-      <c r="AB18" s="37">
+      <c r="AB18" s="34">
         <v>14</v>
       </c>
       <c r="AD18" s="11">
         <v>17</v>
       </c>
       <c r="AE18" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AF18" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AG18" s="24">
         <v>1</v>
       </c>
-      <c r="AI18" s="29"/>
-      <c r="AJ18" s="29"/>
-      <c r="AK18" s="29"/>
+      <c r="AI18" s="28"/>
+      <c r="AJ18" s="28"/>
+      <c r="AK18" s="28"/>
       <c r="AL18" s="9"/>
       <c r="AM18" s="9"/>
       <c r="AN18" s="9"/>
-      <c r="AO18" s="26"/>
+      <c r="AO18" s="25"/>
     </row>
     <row r="19" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D19" t="s">
         <v>26</v>
       </c>
-      <c r="E19" s="41">
+      <c r="E19" s="38">
         <v>13</v>
       </c>
-      <c r="F19" s="42">
+      <c r="F19" s="39">
         <v>13</v>
       </c>
-      <c r="G19" s="59">
-        <v>1</v>
-      </c>
-      <c r="H19" s="59">
-        <v>1</v>
-      </c>
-      <c r="I19" s="59">
-        <v>1</v>
-      </c>
-      <c r="J19" s="59">
-        <v>1</v>
-      </c>
-      <c r="K19" s="59">
-        <v>1</v>
-      </c>
-      <c r="L19" s="61">
-        <v>2</v>
-      </c>
-      <c r="M19" s="61">
-        <v>2</v>
-      </c>
-      <c r="N19" s="61">
-        <v>2</v>
-      </c>
-      <c r="O19" s="61">
-        <v>2</v>
-      </c>
-      <c r="P19" s="61">
-        <v>2</v>
-      </c>
-      <c r="Q19" s="63">
-        <v>3</v>
-      </c>
-      <c r="R19" s="63">
-        <v>3</v>
-      </c>
-      <c r="S19" s="63">
-        <v>3</v>
-      </c>
-      <c r="T19" s="63">
-        <v>3</v>
-      </c>
-      <c r="U19" s="63">
-        <v>3</v>
-      </c>
-      <c r="V19" s="65">
-        <v>4</v>
-      </c>
-      <c r="W19" s="65">
-        <v>4</v>
-      </c>
-      <c r="X19" s="65">
-        <v>4</v>
-      </c>
-      <c r="Y19" s="65">
-        <v>4</v>
-      </c>
-      <c r="Z19" s="65">
-        <v>4</v>
-      </c>
-      <c r="AA19" s="36">
+      <c r="G19" s="56">
+        <v>1</v>
+      </c>
+      <c r="H19" s="56">
+        <v>1</v>
+      </c>
+      <c r="I19" s="56">
+        <v>1</v>
+      </c>
+      <c r="J19" s="56">
+        <v>1</v>
+      </c>
+      <c r="K19" s="56">
+        <v>1</v>
+      </c>
+      <c r="L19" s="58">
+        <v>2</v>
+      </c>
+      <c r="M19" s="58">
+        <v>2</v>
+      </c>
+      <c r="N19" s="58">
+        <v>2</v>
+      </c>
+      <c r="O19" s="58">
+        <v>2</v>
+      </c>
+      <c r="P19" s="58">
+        <v>2</v>
+      </c>
+      <c r="Q19" s="60">
+        <v>3</v>
+      </c>
+      <c r="R19" s="60">
+        <v>3</v>
+      </c>
+      <c r="S19" s="60">
+        <v>3</v>
+      </c>
+      <c r="T19" s="60">
+        <v>3</v>
+      </c>
+      <c r="U19" s="60">
+        <v>3</v>
+      </c>
+      <c r="V19" s="62">
+        <v>4</v>
+      </c>
+      <c r="W19" s="62">
+        <v>4</v>
+      </c>
+      <c r="X19" s="62">
+        <v>4</v>
+      </c>
+      <c r="Y19" s="62">
+        <v>4</v>
+      </c>
+      <c r="Z19" s="62">
+        <v>4</v>
+      </c>
+      <c r="AA19" s="33">
         <v>14</v>
       </c>
-      <c r="AB19" s="37">
+      <c r="AB19" s="34">
         <v>14</v>
       </c>
       <c r="AD19" s="11">
@@ -2844,88 +2961,88 @@
       <c r="AE19" s="8"/>
       <c r="AF19" s="7"/>
       <c r="AG19" s="24"/>
-      <c r="AI19" s="29"/>
-      <c r="AJ19" s="29"/>
-      <c r="AK19" s="29"/>
+      <c r="AI19" s="28"/>
+      <c r="AJ19" s="28"/>
+      <c r="AK19" s="28"/>
       <c r="AL19" s="9"/>
       <c r="AM19" s="9"/>
       <c r="AN19" s="9"/>
-      <c r="AO19" s="26"/>
+      <c r="AO19" s="25"/>
     </row>
     <row r="20" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D20" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="41">
+      <c r="E20" s="38">
         <v>13</v>
       </c>
-      <c r="F20" s="42">
+      <c r="F20" s="39">
         <v>13</v>
       </c>
-      <c r="G20" s="59">
-        <v>1</v>
-      </c>
-      <c r="H20" s="59">
-        <v>1</v>
-      </c>
-      <c r="I20" s="59">
-        <v>1</v>
-      </c>
-      <c r="J20" s="59">
-        <v>1</v>
-      </c>
-      <c r="K20" s="59">
-        <v>1</v>
-      </c>
-      <c r="L20" s="61">
-        <v>2</v>
-      </c>
-      <c r="M20" s="61">
-        <v>2</v>
-      </c>
-      <c r="N20" s="61">
-        <v>2</v>
-      </c>
-      <c r="O20" s="61">
-        <v>2</v>
-      </c>
-      <c r="P20" s="61">
-        <v>2</v>
-      </c>
-      <c r="Q20" s="63">
-        <v>3</v>
-      </c>
-      <c r="R20" s="63">
-        <v>3</v>
-      </c>
-      <c r="S20" s="63">
-        <v>3</v>
-      </c>
-      <c r="T20" s="63">
-        <v>3</v>
-      </c>
-      <c r="U20" s="63">
-        <v>3</v>
-      </c>
-      <c r="V20" s="65">
-        <v>4</v>
-      </c>
-      <c r="W20" s="65">
-        <v>4</v>
-      </c>
-      <c r="X20" s="65">
-        <v>4</v>
-      </c>
-      <c r="Y20" s="65">
-        <v>4</v>
-      </c>
-      <c r="Z20" s="65">
-        <v>4</v>
-      </c>
-      <c r="AA20" s="36">
+      <c r="G20" s="56">
+        <v>1</v>
+      </c>
+      <c r="H20" s="56">
+        <v>1</v>
+      </c>
+      <c r="I20" s="56">
+        <v>1</v>
+      </c>
+      <c r="J20" s="56">
+        <v>1</v>
+      </c>
+      <c r="K20" s="56">
+        <v>1</v>
+      </c>
+      <c r="L20" s="58">
+        <v>2</v>
+      </c>
+      <c r="M20" s="58">
+        <v>2</v>
+      </c>
+      <c r="N20" s="58">
+        <v>2</v>
+      </c>
+      <c r="O20" s="58">
+        <v>2</v>
+      </c>
+      <c r="P20" s="58">
+        <v>2</v>
+      </c>
+      <c r="Q20" s="60">
+        <v>3</v>
+      </c>
+      <c r="R20" s="60">
+        <v>3</v>
+      </c>
+      <c r="S20" s="60">
+        <v>3</v>
+      </c>
+      <c r="T20" s="60">
+        <v>3</v>
+      </c>
+      <c r="U20" s="60">
+        <v>3</v>
+      </c>
+      <c r="V20" s="62">
+        <v>4</v>
+      </c>
+      <c r="W20" s="62">
+        <v>4</v>
+      </c>
+      <c r="X20" s="62">
+        <v>4</v>
+      </c>
+      <c r="Y20" s="62">
+        <v>4</v>
+      </c>
+      <c r="Z20" s="62">
+        <v>4</v>
+      </c>
+      <c r="AA20" s="33">
         <v>14</v>
       </c>
-      <c r="AB20" s="37">
+      <c r="AB20" s="34">
         <v>14</v>
       </c>
       <c r="AD20" s="11">
@@ -2934,88 +3051,88 @@
       <c r="AE20" s="8"/>
       <c r="AF20" s="7"/>
       <c r="AG20" s="24"/>
-      <c r="AI20" s="29"/>
-      <c r="AJ20" s="29"/>
-      <c r="AK20" s="29"/>
+      <c r="AI20" s="28"/>
+      <c r="AJ20" s="28"/>
+      <c r="AK20" s="28"/>
       <c r="AL20" s="9"/>
       <c r="AM20" s="9"/>
       <c r="AN20" s="9"/>
-      <c r="AO20" s="26"/>
+      <c r="AO20" s="25"/>
     </row>
     <row r="21" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D21" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="41">
+      <c r="E21" s="38">
         <v>13</v>
       </c>
-      <c r="F21" s="42">
+      <c r="F21" s="39">
         <v>13</v>
       </c>
-      <c r="G21" s="59">
-        <v>1</v>
-      </c>
-      <c r="H21" s="59">
-        <v>1</v>
-      </c>
-      <c r="I21" s="59">
-        <v>1</v>
-      </c>
-      <c r="J21" s="59">
-        <v>1</v>
-      </c>
-      <c r="K21" s="59">
-        <v>1</v>
-      </c>
-      <c r="L21" s="61">
-        <v>2</v>
-      </c>
-      <c r="M21" s="61">
-        <v>2</v>
-      </c>
-      <c r="N21" s="61">
-        <v>2</v>
-      </c>
-      <c r="O21" s="61">
-        <v>2</v>
-      </c>
-      <c r="P21" s="61">
-        <v>2</v>
-      </c>
-      <c r="Q21" s="63">
-        <v>3</v>
-      </c>
-      <c r="R21" s="63">
-        <v>3</v>
-      </c>
-      <c r="S21" s="63">
-        <v>3</v>
-      </c>
-      <c r="T21" s="63">
-        <v>3</v>
-      </c>
-      <c r="U21" s="63">
-        <v>3</v>
-      </c>
-      <c r="V21" s="65">
-        <v>4</v>
-      </c>
-      <c r="W21" s="65">
-        <v>4</v>
-      </c>
-      <c r="X21" s="65">
-        <v>4</v>
-      </c>
-      <c r="Y21" s="65">
-        <v>4</v>
-      </c>
-      <c r="Z21" s="65">
-        <v>4</v>
-      </c>
-      <c r="AA21" s="36">
+      <c r="G21" s="56">
+        <v>1</v>
+      </c>
+      <c r="H21" s="56">
+        <v>1</v>
+      </c>
+      <c r="I21" s="56">
+        <v>1</v>
+      </c>
+      <c r="J21" s="56">
+        <v>1</v>
+      </c>
+      <c r="K21" s="56">
+        <v>1</v>
+      </c>
+      <c r="L21" s="58">
+        <v>2</v>
+      </c>
+      <c r="M21" s="58">
+        <v>2</v>
+      </c>
+      <c r="N21" s="58">
+        <v>2</v>
+      </c>
+      <c r="O21" s="58">
+        <v>2</v>
+      </c>
+      <c r="P21" s="58">
+        <v>2</v>
+      </c>
+      <c r="Q21" s="60">
+        <v>3</v>
+      </c>
+      <c r="R21" s="60">
+        <v>3</v>
+      </c>
+      <c r="S21" s="60">
+        <v>3</v>
+      </c>
+      <c r="T21" s="60">
+        <v>3</v>
+      </c>
+      <c r="U21" s="60">
+        <v>3</v>
+      </c>
+      <c r="V21" s="62">
+        <v>4</v>
+      </c>
+      <c r="W21" s="62">
+        <v>4</v>
+      </c>
+      <c r="X21" s="62">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="62">
+        <v>4</v>
+      </c>
+      <c r="Z21" s="62">
+        <v>4</v>
+      </c>
+      <c r="AA21" s="33">
         <v>14</v>
       </c>
-      <c r="AB21" s="37">
+      <c r="AB21" s="34">
         <v>14</v>
       </c>
       <c r="AD21" s="11">
@@ -3024,13 +3141,13 @@
       <c r="AE21" s="8"/>
       <c r="AF21" s="7"/>
       <c r="AG21" s="24"/>
-      <c r="AI21" s="29"/>
-      <c r="AJ21" s="29"/>
-      <c r="AK21" s="29"/>
+      <c r="AI21" s="28"/>
+      <c r="AJ21" s="28"/>
+      <c r="AK21" s="28"/>
       <c r="AL21" s="9"/>
       <c r="AM21" s="9"/>
       <c r="AN21" s="9"/>
-      <c r="AO21" s="26"/>
+      <c r="AO21" s="25"/>
     </row>
     <row r="22" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A22" s="3"/>
@@ -3066,19 +3183,19 @@
       <c r="AE22" s="8"/>
       <c r="AF22" s="7"/>
       <c r="AG22" s="24"/>
-      <c r="AI22" s="29"/>
-      <c r="AJ22" s="29"/>
-      <c r="AK22" s="29"/>
+      <c r="AI22" s="28"/>
+      <c r="AJ22" s="28"/>
+      <c r="AK22" s="28"/>
       <c r="AL22" s="9"/>
       <c r="AM22" s="9"/>
       <c r="AN22" s="9"/>
-      <c r="AO22" s="26"/>
+      <c r="AO22" s="25"/>
     </row>
     <row r="23" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A23" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="4" t="s">
+      <c r="A23" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="85" t="s">
         <v>10</v>
       </c>
       <c r="D23" t="s">
@@ -3162,94 +3279,94 @@
       <c r="AE23" s="8"/>
       <c r="AF23" s="7"/>
       <c r="AG23" s="24"/>
-      <c r="AI23" s="29"/>
-      <c r="AJ23" s="29"/>
-      <c r="AK23" s="29"/>
+      <c r="AI23" s="28"/>
+      <c r="AJ23" s="28"/>
+      <c r="AK23" s="28"/>
       <c r="AL23" s="9"/>
       <c r="AM23" s="9"/>
       <c r="AN23" s="9"/>
-      <c r="AO23" s="26"/>
+      <c r="AO23" s="25"/>
     </row>
     <row r="24" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="12" t="s">
-        <v>81</v>
+      <c r="B24" s="87" t="s">
+        <v>79</v>
       </c>
       <c r="D24" t="s">
         <v>13</v>
       </c>
-      <c r="E24" s="39">
+      <c r="E24" s="36">
         <v>13</v>
       </c>
-      <c r="F24" s="40">
+      <c r="F24" s="37">
         <v>13</v>
       </c>
-      <c r="G24" s="50">
-        <v>5</v>
-      </c>
-      <c r="H24" s="50">
-        <v>5</v>
-      </c>
-      <c r="I24" s="50">
-        <v>5</v>
-      </c>
-      <c r="J24" s="50">
-        <v>5</v>
-      </c>
-      <c r="K24" s="50">
-        <v>5</v>
-      </c>
-      <c r="L24" s="52">
-        <v>6</v>
-      </c>
-      <c r="M24" s="52">
-        <v>6</v>
-      </c>
-      <c r="N24" s="52">
-        <v>6</v>
-      </c>
-      <c r="O24" s="52">
-        <v>6</v>
-      </c>
-      <c r="P24" s="52">
-        <v>6</v>
-      </c>
-      <c r="Q24" s="54">
+      <c r="G24" s="47">
+        <v>5</v>
+      </c>
+      <c r="H24" s="47">
+        <v>5</v>
+      </c>
+      <c r="I24" s="47">
+        <v>5</v>
+      </c>
+      <c r="J24" s="47">
+        <v>5</v>
+      </c>
+      <c r="K24" s="47">
+        <v>5</v>
+      </c>
+      <c r="L24" s="49">
+        <v>6</v>
+      </c>
+      <c r="M24" s="49">
+        <v>6</v>
+      </c>
+      <c r="N24" s="49">
+        <v>6</v>
+      </c>
+      <c r="O24" s="49">
+        <v>6</v>
+      </c>
+      <c r="P24" s="49">
+        <v>6</v>
+      </c>
+      <c r="Q24" s="51">
         <v>7</v>
       </c>
-      <c r="R24" s="54">
+      <c r="R24" s="51">
         <v>7</v>
       </c>
-      <c r="S24" s="54">
+      <c r="S24" s="51">
         <v>7</v>
       </c>
-      <c r="T24" s="54">
+      <c r="T24" s="51">
         <v>7</v>
       </c>
-      <c r="U24" s="54">
+      <c r="U24" s="51">
         <v>7</v>
       </c>
-      <c r="V24" s="56">
+      <c r="V24" s="53">
         <v>8</v>
       </c>
-      <c r="W24" s="56">
+      <c r="W24" s="53">
         <v>8</v>
       </c>
-      <c r="X24" s="56">
+      <c r="X24" s="53">
         <v>8</v>
       </c>
-      <c r="Y24" s="56">
+      <c r="Y24" s="53">
         <v>8</v>
       </c>
-      <c r="Z24" s="56">
+      <c r="Z24" s="53">
         <v>8</v>
       </c>
-      <c r="AA24" s="34">
+      <c r="AA24" s="31">
         <v>14</v>
       </c>
-      <c r="AB24" s="35">
+      <c r="AB24" s="32">
         <v>14</v>
       </c>
       <c r="AD24" s="11">
@@ -3258,88 +3375,90 @@
       <c r="AE24" s="8"/>
       <c r="AF24" s="7"/>
       <c r="AG24" s="24"/>
-      <c r="AI24" s="29"/>
-      <c r="AJ24" s="29"/>
-      <c r="AK24" s="29"/>
+      <c r="AI24" s="28"/>
+      <c r="AJ24" s="28"/>
+      <c r="AK24" s="28"/>
       <c r="AL24" s="9"/>
       <c r="AM24" s="9"/>
       <c r="AN24" s="9"/>
-      <c r="AO24" s="26"/>
+      <c r="AO24" s="25"/>
     </row>
     <row r="25" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A25" s="25"/>
+      <c r="B25" s="25"/>
       <c r="D25" t="s">
         <v>14</v>
       </c>
-      <c r="E25" s="41">
+      <c r="E25" s="38">
         <v>13</v>
       </c>
-      <c r="F25" s="42">
+      <c r="F25" s="39">
         <v>13</v>
       </c>
-      <c r="G25" s="51">
-        <v>5</v>
-      </c>
-      <c r="H25" s="51">
-        <v>5</v>
-      </c>
-      <c r="I25" s="51">
-        <v>5</v>
-      </c>
-      <c r="J25" s="51">
-        <v>5</v>
-      </c>
-      <c r="K25" s="51">
-        <v>5</v>
-      </c>
-      <c r="L25" s="53">
-        <v>6</v>
-      </c>
-      <c r="M25" s="53">
-        <v>6</v>
-      </c>
-      <c r="N25" s="53">
-        <v>6</v>
-      </c>
-      <c r="O25" s="53">
-        <v>6</v>
-      </c>
-      <c r="P25" s="53">
-        <v>6</v>
-      </c>
-      <c r="Q25" s="55">
+      <c r="G25" s="48">
+        <v>5</v>
+      </c>
+      <c r="H25" s="48">
+        <v>5</v>
+      </c>
+      <c r="I25" s="48">
+        <v>5</v>
+      </c>
+      <c r="J25" s="48">
+        <v>5</v>
+      </c>
+      <c r="K25" s="48">
+        <v>5</v>
+      </c>
+      <c r="L25" s="50">
+        <v>6</v>
+      </c>
+      <c r="M25" s="50">
+        <v>6</v>
+      </c>
+      <c r="N25" s="50">
+        <v>6</v>
+      </c>
+      <c r="O25" s="50">
+        <v>6</v>
+      </c>
+      <c r="P25" s="50">
+        <v>6</v>
+      </c>
+      <c r="Q25" s="52">
         <v>7</v>
       </c>
-      <c r="R25" s="55">
+      <c r="R25" s="52">
         <v>7</v>
       </c>
-      <c r="S25" s="55">
+      <c r="S25" s="52">
         <v>7</v>
       </c>
-      <c r="T25" s="55">
+      <c r="T25" s="52">
         <v>7</v>
       </c>
-      <c r="U25" s="55">
+      <c r="U25" s="52">
         <v>7</v>
       </c>
-      <c r="V25" s="57">
+      <c r="V25" s="54">
         <v>8</v>
       </c>
-      <c r="W25" s="57">
+      <c r="W25" s="54">
         <v>8</v>
       </c>
-      <c r="X25" s="57">
+      <c r="X25" s="54">
         <v>8</v>
       </c>
-      <c r="Y25" s="57">
+      <c r="Y25" s="54">
         <v>8</v>
       </c>
-      <c r="Z25" s="57">
+      <c r="Z25" s="54">
         <v>8</v>
       </c>
-      <c r="AA25" s="36">
+      <c r="AA25" s="33">
         <v>14</v>
       </c>
-      <c r="AB25" s="37">
+      <c r="AB25" s="34">
         <v>14</v>
       </c>
       <c r="AD25" s="11">
@@ -3348,88 +3467,90 @@
       <c r="AE25" s="8"/>
       <c r="AF25" s="7"/>
       <c r="AG25" s="24"/>
-      <c r="AI25" s="29"/>
-      <c r="AJ25" s="29"/>
-      <c r="AK25" s="29"/>
+      <c r="AI25" s="28"/>
+      <c r="AJ25" s="28"/>
+      <c r="AK25" s="28"/>
       <c r="AL25" s="9"/>
       <c r="AM25" s="9"/>
       <c r="AN25" s="9"/>
-      <c r="AO25" s="26"/>
+      <c r="AO25" s="25"/>
     </row>
     <row r="26" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A26" s="25"/>
+      <c r="B26" s="25"/>
       <c r="D26" t="s">
         <v>15</v>
       </c>
-      <c r="E26" s="41">
+      <c r="E26" s="38">
         <v>13</v>
       </c>
-      <c r="F26" s="42">
+      <c r="F26" s="39">
         <v>13</v>
       </c>
-      <c r="G26" s="51">
-        <v>5</v>
-      </c>
-      <c r="H26" s="51">
-        <v>5</v>
-      </c>
-      <c r="I26" s="51">
-        <v>5</v>
-      </c>
-      <c r="J26" s="51">
-        <v>5</v>
-      </c>
-      <c r="K26" s="51">
-        <v>5</v>
-      </c>
-      <c r="L26" s="53">
-        <v>6</v>
-      </c>
-      <c r="M26" s="53">
-        <v>6</v>
-      </c>
-      <c r="N26" s="53">
-        <v>6</v>
-      </c>
-      <c r="O26" s="53">
-        <v>6</v>
-      </c>
-      <c r="P26" s="53">
-        <v>6</v>
-      </c>
-      <c r="Q26" s="55">
+      <c r="G26" s="48">
+        <v>5</v>
+      </c>
+      <c r="H26" s="48">
+        <v>5</v>
+      </c>
+      <c r="I26" s="48">
+        <v>5</v>
+      </c>
+      <c r="J26" s="48">
+        <v>5</v>
+      </c>
+      <c r="K26" s="48">
+        <v>5</v>
+      </c>
+      <c r="L26" s="50">
+        <v>6</v>
+      </c>
+      <c r="M26" s="50">
+        <v>6</v>
+      </c>
+      <c r="N26" s="50">
+        <v>6</v>
+      </c>
+      <c r="O26" s="50">
+        <v>6</v>
+      </c>
+      <c r="P26" s="50">
+        <v>6</v>
+      </c>
+      <c r="Q26" s="52">
         <v>7</v>
       </c>
-      <c r="R26" s="55">
+      <c r="R26" s="52">
         <v>7</v>
       </c>
-      <c r="S26" s="55">
+      <c r="S26" s="52">
         <v>7</v>
       </c>
-      <c r="T26" s="55">
+      <c r="T26" s="52">
         <v>7</v>
       </c>
-      <c r="U26" s="55">
+      <c r="U26" s="52">
         <v>7</v>
       </c>
-      <c r="V26" s="57">
+      <c r="V26" s="54">
         <v>8</v>
       </c>
-      <c r="W26" s="57">
+      <c r="W26" s="54">
         <v>8</v>
       </c>
-      <c r="X26" s="57">
+      <c r="X26" s="54">
         <v>8</v>
       </c>
-      <c r="Y26" s="57">
+      <c r="Y26" s="54">
         <v>8</v>
       </c>
-      <c r="Z26" s="57">
+      <c r="Z26" s="54">
         <v>8</v>
       </c>
-      <c r="AA26" s="36">
+      <c r="AA26" s="33">
         <v>14</v>
       </c>
-      <c r="AB26" s="37">
+      <c r="AB26" s="34">
         <v>14</v>
       </c>
       <c r="AD26" s="11">
@@ -3438,88 +3559,92 @@
       <c r="AE26" s="8"/>
       <c r="AF26" s="7"/>
       <c r="AG26" s="24"/>
-      <c r="AI26" s="29"/>
-      <c r="AJ26" s="29"/>
-      <c r="AK26" s="29"/>
+      <c r="AI26" s="28"/>
+      <c r="AJ26" s="28"/>
+      <c r="AK26" s="28"/>
       <c r="AL26" s="9"/>
       <c r="AM26" s="9"/>
       <c r="AN26" s="9"/>
-      <c r="AO26" s="26"/>
+      <c r="AO26" s="25"/>
     </row>
     <row r="27" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A27" s="25"/>
+      <c r="B27" s="88" t="s">
+        <v>101</v>
+      </c>
       <c r="D27" t="s">
         <v>16</v>
       </c>
-      <c r="E27" s="41">
+      <c r="E27" s="38">
         <v>13</v>
       </c>
-      <c r="F27" s="42">
+      <c r="F27" s="39">
         <v>13</v>
       </c>
-      <c r="G27" s="51">
-        <v>5</v>
-      </c>
-      <c r="H27" s="51">
-        <v>5</v>
-      </c>
-      <c r="I27" s="51">
-        <v>5</v>
-      </c>
-      <c r="J27" s="51">
-        <v>5</v>
-      </c>
-      <c r="K27" s="51">
-        <v>5</v>
-      </c>
-      <c r="L27" s="53">
-        <v>6</v>
-      </c>
-      <c r="M27" s="53">
-        <v>6</v>
-      </c>
-      <c r="N27" s="53">
-        <v>6</v>
-      </c>
-      <c r="O27" s="53">
-        <v>6</v>
-      </c>
-      <c r="P27" s="53">
-        <v>6</v>
-      </c>
-      <c r="Q27" s="55">
+      <c r="G27" s="48">
+        <v>5</v>
+      </c>
+      <c r="H27" s="48">
+        <v>5</v>
+      </c>
+      <c r="I27" s="48">
+        <v>5</v>
+      </c>
+      <c r="J27" s="48">
+        <v>5</v>
+      </c>
+      <c r="K27" s="48">
+        <v>5</v>
+      </c>
+      <c r="L27" s="50">
+        <v>6</v>
+      </c>
+      <c r="M27" s="50">
+        <v>6</v>
+      </c>
+      <c r="N27" s="50">
+        <v>6</v>
+      </c>
+      <c r="O27" s="50">
+        <v>6</v>
+      </c>
+      <c r="P27" s="50">
+        <v>6</v>
+      </c>
+      <c r="Q27" s="52">
         <v>7</v>
       </c>
-      <c r="R27" s="55">
+      <c r="R27" s="52">
         <v>7</v>
       </c>
-      <c r="S27" s="55">
+      <c r="S27" s="52">
         <v>7</v>
       </c>
-      <c r="T27" s="55">
+      <c r="T27" s="52">
         <v>7</v>
       </c>
-      <c r="U27" s="55">
+      <c r="U27" s="52">
         <v>7</v>
       </c>
-      <c r="V27" s="57">
+      <c r="V27" s="54">
         <v>8</v>
       </c>
-      <c r="W27" s="57">
+      <c r="W27" s="54">
         <v>8</v>
       </c>
-      <c r="X27" s="57">
+      <c r="X27" s="54">
         <v>8</v>
       </c>
-      <c r="Y27" s="57">
+      <c r="Y27" s="54">
         <v>8</v>
       </c>
-      <c r="Z27" s="57">
+      <c r="Z27" s="54">
         <v>8</v>
       </c>
-      <c r="AA27" s="36">
+      <c r="AA27" s="33">
         <v>14</v>
       </c>
-      <c r="AB27" s="37">
+      <c r="AB27" s="34">
         <v>14</v>
       </c>
       <c r="AD27" s="11">
@@ -3528,88 +3653,92 @@
       <c r="AE27" s="8"/>
       <c r="AF27" s="7"/>
       <c r="AG27" s="24"/>
-      <c r="AI27" s="29"/>
-      <c r="AJ27" s="29"/>
-      <c r="AK27" s="29"/>
+      <c r="AI27" s="28"/>
+      <c r="AJ27" s="28"/>
+      <c r="AK27" s="28"/>
       <c r="AL27" s="9"/>
       <c r="AM27" s="9"/>
       <c r="AN27" s="9"/>
-      <c r="AO27" s="26"/>
+      <c r="AO27" s="25"/>
     </row>
     <row r="28" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A28" s="25">
+        <v>1</v>
+      </c>
+      <c r="B28" s="24"/>
       <c r="D28" t="s">
         <v>17</v>
       </c>
-      <c r="E28" s="41">
+      <c r="E28" s="38">
         <v>13</v>
       </c>
-      <c r="F28" s="42">
+      <c r="F28" s="39">
         <v>13</v>
       </c>
-      <c r="G28" s="51">
-        <v>5</v>
-      </c>
-      <c r="H28" s="51">
-        <v>5</v>
-      </c>
-      <c r="I28" s="51">
-        <v>5</v>
-      </c>
-      <c r="J28" s="51">
-        <v>5</v>
-      </c>
-      <c r="K28" s="51">
-        <v>5</v>
-      </c>
-      <c r="L28" s="53">
-        <v>6</v>
-      </c>
-      <c r="M28" s="53">
-        <v>6</v>
-      </c>
-      <c r="N28" s="53">
-        <v>6</v>
-      </c>
-      <c r="O28" s="53">
-        <v>6</v>
-      </c>
-      <c r="P28" s="53">
-        <v>6</v>
-      </c>
-      <c r="Q28" s="55">
+      <c r="G28" s="48">
+        <v>5</v>
+      </c>
+      <c r="H28" s="48">
+        <v>5</v>
+      </c>
+      <c r="I28" s="48">
+        <v>5</v>
+      </c>
+      <c r="J28" s="48">
+        <v>5</v>
+      </c>
+      <c r="K28" s="48">
+        <v>5</v>
+      </c>
+      <c r="L28" s="50">
+        <v>6</v>
+      </c>
+      <c r="M28" s="50">
+        <v>6</v>
+      </c>
+      <c r="N28" s="50">
+        <v>6</v>
+      </c>
+      <c r="O28" s="50">
+        <v>6</v>
+      </c>
+      <c r="P28" s="50">
+        <v>6</v>
+      </c>
+      <c r="Q28" s="52">
         <v>7</v>
       </c>
-      <c r="R28" s="55">
+      <c r="R28" s="52">
         <v>7</v>
       </c>
-      <c r="S28" s="55">
+      <c r="S28" s="52">
         <v>7</v>
       </c>
-      <c r="T28" s="55">
+      <c r="T28" s="52">
         <v>7</v>
       </c>
-      <c r="U28" s="55">
+      <c r="U28" s="52">
         <v>7</v>
       </c>
-      <c r="V28" s="57">
+      <c r="V28" s="54">
         <v>8</v>
       </c>
-      <c r="W28" s="57">
+      <c r="W28" s="54">
         <v>8</v>
       </c>
-      <c r="X28" s="57">
+      <c r="X28" s="54">
         <v>8</v>
       </c>
-      <c r="Y28" s="57">
+      <c r="Y28" s="54">
         <v>8</v>
       </c>
-      <c r="Z28" s="57">
+      <c r="Z28" s="54">
         <v>8</v>
       </c>
-      <c r="AA28" s="36">
+      <c r="AA28" s="33">
         <v>14</v>
       </c>
-      <c r="AB28" s="37">
+      <c r="AB28" s="34">
         <v>14</v>
       </c>
       <c r="AD28" s="11">
@@ -3618,88 +3747,92 @@
       <c r="AE28" s="8"/>
       <c r="AF28" s="7"/>
       <c r="AG28" s="24"/>
-      <c r="AI28" s="29"/>
-      <c r="AJ28" s="29"/>
-      <c r="AK28" s="29"/>
+      <c r="AI28" s="28"/>
+      <c r="AJ28" s="28"/>
+      <c r="AK28" s="28"/>
       <c r="AL28" s="9"/>
       <c r="AM28" s="9"/>
       <c r="AN28" s="9"/>
-      <c r="AO28" s="26"/>
+      <c r="AO28" s="25"/>
     </row>
     <row r="29" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A29" s="25">
+        <v>2</v>
+      </c>
+      <c r="B29" s="24"/>
       <c r="D29" t="s">
         <v>18</v>
       </c>
-      <c r="E29" s="41">
+      <c r="E29" s="38">
         <v>13</v>
       </c>
-      <c r="F29" s="42">
+      <c r="F29" s="39">
         <v>13</v>
       </c>
-      <c r="G29" s="51">
-        <v>5</v>
-      </c>
-      <c r="H29" s="51">
-        <v>5</v>
-      </c>
-      <c r="I29" s="51">
-        <v>5</v>
-      </c>
-      <c r="J29" s="51">
-        <v>5</v>
-      </c>
-      <c r="K29" s="51">
-        <v>5</v>
-      </c>
-      <c r="L29" s="53">
-        <v>6</v>
-      </c>
-      <c r="M29" s="53">
-        <v>6</v>
-      </c>
-      <c r="N29" s="53">
-        <v>6</v>
-      </c>
-      <c r="O29" s="53">
-        <v>6</v>
-      </c>
-      <c r="P29" s="53">
-        <v>6</v>
-      </c>
-      <c r="Q29" s="55">
+      <c r="G29" s="48">
+        <v>5</v>
+      </c>
+      <c r="H29" s="48">
+        <v>5</v>
+      </c>
+      <c r="I29" s="48">
+        <v>5</v>
+      </c>
+      <c r="J29" s="48">
+        <v>5</v>
+      </c>
+      <c r="K29" s="48">
+        <v>5</v>
+      </c>
+      <c r="L29" s="50">
+        <v>6</v>
+      </c>
+      <c r="M29" s="50">
+        <v>6</v>
+      </c>
+      <c r="N29" s="50">
+        <v>6</v>
+      </c>
+      <c r="O29" s="50">
+        <v>6</v>
+      </c>
+      <c r="P29" s="50">
+        <v>6</v>
+      </c>
+      <c r="Q29" s="52">
         <v>7</v>
       </c>
-      <c r="R29" s="55">
+      <c r="R29" s="52">
         <v>7</v>
       </c>
-      <c r="S29" s="55">
+      <c r="S29" s="52">
         <v>7</v>
       </c>
-      <c r="T29" s="55">
+      <c r="T29" s="52">
         <v>7</v>
       </c>
-      <c r="U29" s="55">
+      <c r="U29" s="52">
         <v>7</v>
       </c>
-      <c r="V29" s="57">
+      <c r="V29" s="54">
         <v>8</v>
       </c>
-      <c r="W29" s="57">
+      <c r="W29" s="54">
         <v>8</v>
       </c>
-      <c r="X29" s="57">
+      <c r="X29" s="54">
         <v>8</v>
       </c>
-      <c r="Y29" s="57">
+      <c r="Y29" s="54">
         <v>8</v>
       </c>
-      <c r="Z29" s="57">
+      <c r="Z29" s="54">
         <v>8</v>
       </c>
-      <c r="AA29" s="36">
+      <c r="AA29" s="33">
         <v>14</v>
       </c>
-      <c r="AB29" s="37">
+      <c r="AB29" s="34">
         <v>14</v>
       </c>
       <c r="AD29" s="11">
@@ -3708,88 +3841,92 @@
       <c r="AE29" s="8"/>
       <c r="AF29" s="7"/>
       <c r="AG29" s="24"/>
-      <c r="AI29" s="29"/>
-      <c r="AJ29" s="29"/>
-      <c r="AK29" s="29"/>
+      <c r="AI29" s="28"/>
+      <c r="AJ29" s="28"/>
+      <c r="AK29" s="28"/>
       <c r="AL29" s="9"/>
       <c r="AM29" s="9"/>
       <c r="AN29" s="9"/>
-      <c r="AO29" s="26"/>
+      <c r="AO29" s="25"/>
     </row>
     <row r="30" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A30" s="25">
+        <v>3</v>
+      </c>
+      <c r="B30" s="24"/>
       <c r="D30" t="s">
         <v>19</v>
       </c>
-      <c r="E30" s="41">
+      <c r="E30" s="38">
         <v>13</v>
       </c>
-      <c r="F30" s="42">
+      <c r="F30" s="39">
         <v>13</v>
       </c>
-      <c r="G30" s="51">
-        <v>5</v>
-      </c>
-      <c r="H30" s="51">
-        <v>5</v>
-      </c>
-      <c r="I30" s="51">
-        <v>5</v>
-      </c>
-      <c r="J30" s="51">
-        <v>5</v>
-      </c>
-      <c r="K30" s="51">
-        <v>5</v>
-      </c>
-      <c r="L30" s="53">
-        <v>6</v>
-      </c>
-      <c r="M30" s="53">
-        <v>6</v>
-      </c>
-      <c r="N30" s="53">
-        <v>6</v>
-      </c>
-      <c r="O30" s="53">
-        <v>6</v>
-      </c>
-      <c r="P30" s="53">
-        <v>6</v>
-      </c>
-      <c r="Q30" s="55">
+      <c r="G30" s="48">
+        <v>5</v>
+      </c>
+      <c r="H30" s="48">
+        <v>5</v>
+      </c>
+      <c r="I30" s="48">
+        <v>5</v>
+      </c>
+      <c r="J30" s="48">
+        <v>5</v>
+      </c>
+      <c r="K30" s="48">
+        <v>5</v>
+      </c>
+      <c r="L30" s="50">
+        <v>6</v>
+      </c>
+      <c r="M30" s="50">
+        <v>6</v>
+      </c>
+      <c r="N30" s="50">
+        <v>6</v>
+      </c>
+      <c r="O30" s="50">
+        <v>6</v>
+      </c>
+      <c r="P30" s="50">
+        <v>6</v>
+      </c>
+      <c r="Q30" s="52">
         <v>7</v>
       </c>
-      <c r="R30" s="55">
+      <c r="R30" s="52">
         <v>7</v>
       </c>
-      <c r="S30" s="55">
+      <c r="S30" s="52">
         <v>7</v>
       </c>
-      <c r="T30" s="55">
+      <c r="T30" s="52">
         <v>7</v>
       </c>
-      <c r="U30" s="55">
+      <c r="U30" s="52">
         <v>7</v>
       </c>
-      <c r="V30" s="57">
+      <c r="V30" s="54">
         <v>8</v>
       </c>
-      <c r="W30" s="57">
+      <c r="W30" s="54">
         <v>8</v>
       </c>
-      <c r="X30" s="57">
+      <c r="X30" s="54">
         <v>8</v>
       </c>
-      <c r="Y30" s="57">
+      <c r="Y30" s="54">
         <v>8</v>
       </c>
-      <c r="Z30" s="57">
+      <c r="Z30" s="54">
         <v>8</v>
       </c>
-      <c r="AA30" s="36">
+      <c r="AA30" s="33">
         <v>14</v>
       </c>
-      <c r="AB30" s="37">
+      <c r="AB30" s="34">
         <v>14</v>
       </c>
       <c r="AD30" s="11">
@@ -3798,88 +3935,92 @@
       <c r="AE30" s="8"/>
       <c r="AF30" s="7"/>
       <c r="AG30" s="24"/>
-      <c r="AI30" s="29"/>
-      <c r="AJ30" s="29"/>
-      <c r="AK30" s="29"/>
+      <c r="AI30" s="28"/>
+      <c r="AJ30" s="28"/>
+      <c r="AK30" s="28"/>
       <c r="AL30" s="9"/>
       <c r="AM30" s="9"/>
       <c r="AN30" s="9"/>
-      <c r="AO30" s="26"/>
+      <c r="AO30" s="25"/>
     </row>
     <row r="31" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A31" s="25">
+        <v>4</v>
+      </c>
+      <c r="B31" s="24"/>
       <c r="D31" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="41">
+      <c r="E31" s="38">
         <v>13</v>
       </c>
-      <c r="F31" s="42">
+      <c r="F31" s="39">
         <v>13</v>
       </c>
-      <c r="G31" s="51">
-        <v>5</v>
-      </c>
-      <c r="H31" s="51">
-        <v>5</v>
-      </c>
-      <c r="I31" s="51">
-        <v>5</v>
-      </c>
-      <c r="J31" s="51">
-        <v>5</v>
-      </c>
-      <c r="K31" s="51">
-        <v>5</v>
-      </c>
-      <c r="L31" s="53">
-        <v>6</v>
-      </c>
-      <c r="M31" s="53">
-        <v>6</v>
-      </c>
-      <c r="N31" s="53">
-        <v>6</v>
-      </c>
-      <c r="O31" s="53">
-        <v>6</v>
-      </c>
-      <c r="P31" s="53">
-        <v>6</v>
-      </c>
-      <c r="Q31" s="55">
+      <c r="G31" s="48">
+        <v>5</v>
+      </c>
+      <c r="H31" s="48">
+        <v>5</v>
+      </c>
+      <c r="I31" s="48">
+        <v>5</v>
+      </c>
+      <c r="J31" s="48">
+        <v>5</v>
+      </c>
+      <c r="K31" s="48">
+        <v>5</v>
+      </c>
+      <c r="L31" s="50">
+        <v>6</v>
+      </c>
+      <c r="M31" s="50">
+        <v>6</v>
+      </c>
+      <c r="N31" s="50">
+        <v>6</v>
+      </c>
+      <c r="O31" s="50">
+        <v>6</v>
+      </c>
+      <c r="P31" s="50">
+        <v>6</v>
+      </c>
+      <c r="Q31" s="52">
         <v>7</v>
       </c>
-      <c r="R31" s="55">
+      <c r="R31" s="52">
         <v>7</v>
       </c>
-      <c r="S31" s="55">
+      <c r="S31" s="52">
         <v>7</v>
       </c>
-      <c r="T31" s="55">
+      <c r="T31" s="52">
         <v>7</v>
       </c>
-      <c r="U31" s="55">
+      <c r="U31" s="52">
         <v>7</v>
       </c>
-      <c r="V31" s="57">
+      <c r="V31" s="54">
         <v>8</v>
       </c>
-      <c r="W31" s="57">
+      <c r="W31" s="54">
         <v>8</v>
       </c>
-      <c r="X31" s="57">
+      <c r="X31" s="54">
         <v>8</v>
       </c>
-      <c r="Y31" s="57">
+      <c r="Y31" s="54">
         <v>8</v>
       </c>
-      <c r="Z31" s="57">
+      <c r="Z31" s="54">
         <v>8</v>
       </c>
-      <c r="AA31" s="36">
+      <c r="AA31" s="33">
         <v>14</v>
       </c>
-      <c r="AB31" s="37">
+      <c r="AB31" s="34">
         <v>14</v>
       </c>
       <c r="AD31" s="11">
@@ -3888,88 +4029,92 @@
       <c r="AE31" s="8"/>
       <c r="AF31" s="7"/>
       <c r="AG31" s="24"/>
-      <c r="AI31" s="29"/>
-      <c r="AJ31" s="29"/>
-      <c r="AK31" s="29"/>
+      <c r="AI31" s="28"/>
+      <c r="AJ31" s="28"/>
+      <c r="AK31" s="28"/>
       <c r="AL31" s="9"/>
       <c r="AM31" s="9"/>
       <c r="AN31" s="9"/>
-      <c r="AO31" s="26"/>
+      <c r="AO31" s="25"/>
     </row>
     <row r="32" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A32" s="25">
+        <v>5</v>
+      </c>
+      <c r="B32" s="29"/>
       <c r="D32" t="s">
         <v>21</v>
       </c>
-      <c r="E32" s="41">
+      <c r="E32" s="38">
         <v>13</v>
       </c>
-      <c r="F32" s="42">
+      <c r="F32" s="39">
         <v>13</v>
       </c>
-      <c r="G32" s="51">
-        <v>5</v>
-      </c>
-      <c r="H32" s="51">
-        <v>5</v>
-      </c>
-      <c r="I32" s="51">
-        <v>5</v>
-      </c>
-      <c r="J32" s="51">
-        <v>5</v>
-      </c>
-      <c r="K32" s="51">
-        <v>5</v>
-      </c>
-      <c r="L32" s="53">
-        <v>6</v>
-      </c>
-      <c r="M32" s="53">
-        <v>6</v>
-      </c>
-      <c r="N32" s="53">
-        <v>6</v>
-      </c>
-      <c r="O32" s="53">
-        <v>6</v>
-      </c>
-      <c r="P32" s="53">
-        <v>6</v>
-      </c>
-      <c r="Q32" s="55">
+      <c r="G32" s="48">
+        <v>5</v>
+      </c>
+      <c r="H32" s="48">
+        <v>5</v>
+      </c>
+      <c r="I32" s="48">
+        <v>5</v>
+      </c>
+      <c r="J32" s="48">
+        <v>5</v>
+      </c>
+      <c r="K32" s="48">
+        <v>5</v>
+      </c>
+      <c r="L32" s="50">
+        <v>6</v>
+      </c>
+      <c r="M32" s="50">
+        <v>6</v>
+      </c>
+      <c r="N32" s="50">
+        <v>6</v>
+      </c>
+      <c r="O32" s="50">
+        <v>6</v>
+      </c>
+      <c r="P32" s="50">
+        <v>6</v>
+      </c>
+      <c r="Q32" s="52">
         <v>7</v>
       </c>
-      <c r="R32" s="55">
+      <c r="R32" s="52">
         <v>7</v>
       </c>
-      <c r="S32" s="55">
+      <c r="S32" s="52">
         <v>7</v>
       </c>
-      <c r="T32" s="55">
+      <c r="T32" s="52">
         <v>7</v>
       </c>
-      <c r="U32" s="55">
+      <c r="U32" s="52">
         <v>7</v>
       </c>
-      <c r="V32" s="57">
+      <c r="V32" s="54">
         <v>8</v>
       </c>
-      <c r="W32" s="57">
+      <c r="W32" s="54">
         <v>8</v>
       </c>
-      <c r="X32" s="57">
+      <c r="X32" s="54">
         <v>8</v>
       </c>
-      <c r="Y32" s="57">
+      <c r="Y32" s="54">
         <v>8</v>
       </c>
-      <c r="Z32" s="57">
+      <c r="Z32" s="54">
         <v>8</v>
       </c>
-      <c r="AA32" s="36">
+      <c r="AA32" s="33">
         <v>14</v>
       </c>
-      <c r="AB32" s="37">
+      <c r="AB32" s="34">
         <v>14</v>
       </c>
       <c r="AD32" s="11">
@@ -3984,82 +4129,84 @@
       <c r="AL32" s="9"/>
       <c r="AM32" s="9"/>
       <c r="AN32" s="9"/>
-      <c r="AO32" s="26"/>
+      <c r="AO32" s="25"/>
     </row>
     <row r="33" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="25"/>
+      <c r="B33" s="25"/>
       <c r="D33" t="s">
         <v>22</v>
       </c>
-      <c r="E33" s="41">
+      <c r="E33" s="38">
         <v>13</v>
       </c>
-      <c r="F33" s="42">
+      <c r="F33" s="39">
         <v>13</v>
       </c>
-      <c r="G33" s="51">
-        <v>5</v>
-      </c>
-      <c r="H33" s="51">
-        <v>5</v>
-      </c>
-      <c r="I33" s="51">
-        <v>5</v>
-      </c>
-      <c r="J33" s="51">
-        <v>5</v>
-      </c>
-      <c r="K33" s="51">
-        <v>5</v>
-      </c>
-      <c r="L33" s="53">
-        <v>6</v>
-      </c>
-      <c r="M33" s="53">
-        <v>6</v>
-      </c>
-      <c r="N33" s="53">
-        <v>6</v>
-      </c>
-      <c r="O33" s="53">
-        <v>6</v>
-      </c>
-      <c r="P33" s="53">
-        <v>6</v>
-      </c>
-      <c r="Q33" s="55">
+      <c r="G33" s="48">
+        <v>5</v>
+      </c>
+      <c r="H33" s="48">
+        <v>5</v>
+      </c>
+      <c r="I33" s="48">
+        <v>5</v>
+      </c>
+      <c r="J33" s="48">
+        <v>5</v>
+      </c>
+      <c r="K33" s="48">
+        <v>5</v>
+      </c>
+      <c r="L33" s="50">
+        <v>6</v>
+      </c>
+      <c r="M33" s="50">
+        <v>6</v>
+      </c>
+      <c r="N33" s="50">
+        <v>6</v>
+      </c>
+      <c r="O33" s="50">
+        <v>6</v>
+      </c>
+      <c r="P33" s="50">
+        <v>6</v>
+      </c>
+      <c r="Q33" s="52">
         <v>7</v>
       </c>
-      <c r="R33" s="55">
+      <c r="R33" s="52">
         <v>7</v>
       </c>
-      <c r="S33" s="55">
+      <c r="S33" s="52">
         <v>7</v>
       </c>
-      <c r="T33" s="55">
+      <c r="T33" s="52">
         <v>7</v>
       </c>
-      <c r="U33" s="55">
+      <c r="U33" s="52">
         <v>7</v>
       </c>
-      <c r="V33" s="57">
+      <c r="V33" s="54">
         <v>8</v>
       </c>
-      <c r="W33" s="57">
+      <c r="W33" s="54">
         <v>8</v>
       </c>
-      <c r="X33" s="57">
+      <c r="X33" s="54">
         <v>8</v>
       </c>
-      <c r="Y33" s="57">
+      <c r="Y33" s="54">
         <v>8</v>
       </c>
-      <c r="Z33" s="57">
+      <c r="Z33" s="54">
         <v>8</v>
       </c>
-      <c r="AA33" s="36">
+      <c r="AA33" s="33">
         <v>14</v>
       </c>
-      <c r="AB33" s="37">
+      <c r="AB33" s="34">
         <v>14</v>
       </c>
       <c r="AD33" s="11">
@@ -4070,82 +4217,82 @@
       <c r="AG33" s="24"/>
       <c r="AM33" s="9"/>
       <c r="AN33" s="9"/>
-      <c r="AO33" s="26"/>
+      <c r="AO33" s="25"/>
     </row>
     <row r="34" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D34" t="s">
         <v>23</v>
       </c>
-      <c r="E34" s="41">
+      <c r="E34" s="38">
         <v>13</v>
       </c>
-      <c r="F34" s="42">
+      <c r="F34" s="39">
         <v>13</v>
       </c>
-      <c r="G34" s="51">
-        <v>5</v>
-      </c>
-      <c r="H34" s="51">
-        <v>5</v>
-      </c>
-      <c r="I34" s="51">
-        <v>5</v>
-      </c>
-      <c r="J34" s="51">
-        <v>5</v>
-      </c>
-      <c r="K34" s="51">
-        <v>5</v>
-      </c>
-      <c r="L34" s="53">
-        <v>6</v>
-      </c>
-      <c r="M34" s="53">
-        <v>6</v>
-      </c>
-      <c r="N34" s="53">
-        <v>6</v>
-      </c>
-      <c r="O34" s="53">
-        <v>6</v>
-      </c>
-      <c r="P34" s="53">
-        <v>6</v>
-      </c>
-      <c r="Q34" s="55">
+      <c r="G34" s="48">
+        <v>5</v>
+      </c>
+      <c r="H34" s="48">
+        <v>5</v>
+      </c>
+      <c r="I34" s="48">
+        <v>5</v>
+      </c>
+      <c r="J34" s="48">
+        <v>5</v>
+      </c>
+      <c r="K34" s="48">
+        <v>5</v>
+      </c>
+      <c r="L34" s="50">
+        <v>6</v>
+      </c>
+      <c r="M34" s="50">
+        <v>6</v>
+      </c>
+      <c r="N34" s="50">
+        <v>6</v>
+      </c>
+      <c r="O34" s="50">
+        <v>6</v>
+      </c>
+      <c r="P34" s="50">
+        <v>6</v>
+      </c>
+      <c r="Q34" s="52">
         <v>7</v>
       </c>
-      <c r="R34" s="55">
+      <c r="R34" s="52">
         <v>7</v>
       </c>
-      <c r="S34" s="55">
+      <c r="S34" s="52">
         <v>7</v>
       </c>
-      <c r="T34" s="55">
+      <c r="T34" s="52">
         <v>7</v>
       </c>
-      <c r="U34" s="55">
+      <c r="U34" s="52">
         <v>7</v>
       </c>
-      <c r="V34" s="57">
+      <c r="V34" s="54">
         <v>8</v>
       </c>
-      <c r="W34" s="57">
+      <c r="W34" s="54">
         <v>8</v>
       </c>
-      <c r="X34" s="57">
+      <c r="X34" s="54">
         <v>8</v>
       </c>
-      <c r="Y34" s="57">
+      <c r="Y34" s="54">
         <v>8</v>
       </c>
-      <c r="Z34" s="57">
+      <c r="Z34" s="54">
         <v>8</v>
       </c>
-      <c r="AA34" s="36">
+      <c r="AA34" s="33">
         <v>14</v>
       </c>
-      <c r="AB34" s="37">
+      <c r="AB34" s="34">
         <v>14</v>
       </c>
       <c r="AD34" s="11">
@@ -4159,76 +4306,76 @@
       <c r="D35" t="s">
         <v>24</v>
       </c>
-      <c r="E35" s="41">
+      <c r="E35" s="38">
         <v>13</v>
       </c>
-      <c r="F35" s="42">
+      <c r="F35" s="39">
         <v>13</v>
       </c>
-      <c r="G35" s="51">
-        <v>5</v>
-      </c>
-      <c r="H35" s="51">
-        <v>5</v>
-      </c>
-      <c r="I35" s="51">
-        <v>5</v>
-      </c>
-      <c r="J35" s="51">
-        <v>5</v>
-      </c>
-      <c r="K35" s="51">
-        <v>5</v>
-      </c>
-      <c r="L35" s="53">
-        <v>6</v>
-      </c>
-      <c r="M35" s="53">
-        <v>6</v>
-      </c>
-      <c r="N35" s="53">
-        <v>6</v>
-      </c>
-      <c r="O35" s="53">
-        <v>6</v>
-      </c>
-      <c r="P35" s="53">
-        <v>6</v>
-      </c>
-      <c r="Q35" s="55">
+      <c r="G35" s="48">
+        <v>5</v>
+      </c>
+      <c r="H35" s="48">
+        <v>5</v>
+      </c>
+      <c r="I35" s="48">
+        <v>5</v>
+      </c>
+      <c r="J35" s="48">
+        <v>5</v>
+      </c>
+      <c r="K35" s="48">
+        <v>5</v>
+      </c>
+      <c r="L35" s="50">
+        <v>6</v>
+      </c>
+      <c r="M35" s="50">
+        <v>6</v>
+      </c>
+      <c r="N35" s="50">
+        <v>6</v>
+      </c>
+      <c r="O35" s="50">
+        <v>6</v>
+      </c>
+      <c r="P35" s="50">
+        <v>6</v>
+      </c>
+      <c r="Q35" s="52">
         <v>7</v>
       </c>
-      <c r="R35" s="55">
+      <c r="R35" s="52">
         <v>7</v>
       </c>
-      <c r="S35" s="55">
+      <c r="S35" s="52">
         <v>7</v>
       </c>
-      <c r="T35" s="55">
+      <c r="T35" s="52">
         <v>7</v>
       </c>
-      <c r="U35" s="55">
+      <c r="U35" s="52">
         <v>7</v>
       </c>
-      <c r="V35" s="57">
+      <c r="V35" s="54">
         <v>8</v>
       </c>
-      <c r="W35" s="57">
+      <c r="W35" s="54">
         <v>8</v>
       </c>
-      <c r="X35" s="57">
+      <c r="X35" s="54">
         <v>8</v>
       </c>
-      <c r="Y35" s="57">
+      <c r="Y35" s="54">
         <v>8</v>
       </c>
-      <c r="Z35" s="57">
+      <c r="Z35" s="54">
         <v>8</v>
       </c>
-      <c r="AA35" s="36">
+      <c r="AA35" s="33">
         <v>14</v>
       </c>
-      <c r="AB35" s="37">
+      <c r="AB35" s="34">
         <v>14</v>
       </c>
       <c r="AD35" s="11">
@@ -4242,76 +4389,76 @@
       <c r="D36" t="s">
         <v>25</v>
       </c>
-      <c r="E36" s="41">
+      <c r="E36" s="38">
         <v>13</v>
       </c>
-      <c r="F36" s="42">
+      <c r="F36" s="39">
         <v>13</v>
       </c>
-      <c r="G36" s="51">
-        <v>5</v>
-      </c>
-      <c r="H36" s="51">
-        <v>5</v>
-      </c>
-      <c r="I36" s="51">
-        <v>5</v>
-      </c>
-      <c r="J36" s="51">
-        <v>5</v>
-      </c>
-      <c r="K36" s="51">
-        <v>5</v>
-      </c>
-      <c r="L36" s="53">
-        <v>6</v>
-      </c>
-      <c r="M36" s="53">
-        <v>6</v>
-      </c>
-      <c r="N36" s="53">
-        <v>6</v>
-      </c>
-      <c r="O36" s="53">
-        <v>6</v>
-      </c>
-      <c r="P36" s="53">
-        <v>6</v>
-      </c>
-      <c r="Q36" s="55">
+      <c r="G36" s="48">
+        <v>5</v>
+      </c>
+      <c r="H36" s="48">
+        <v>5</v>
+      </c>
+      <c r="I36" s="48">
+        <v>5</v>
+      </c>
+      <c r="J36" s="48">
+        <v>5</v>
+      </c>
+      <c r="K36" s="48">
+        <v>5</v>
+      </c>
+      <c r="L36" s="50">
+        <v>6</v>
+      </c>
+      <c r="M36" s="50">
+        <v>6</v>
+      </c>
+      <c r="N36" s="50">
+        <v>6</v>
+      </c>
+      <c r="O36" s="50">
+        <v>6</v>
+      </c>
+      <c r="P36" s="50">
+        <v>6</v>
+      </c>
+      <c r="Q36" s="52">
         <v>7</v>
       </c>
-      <c r="R36" s="55">
+      <c r="R36" s="52">
         <v>7</v>
       </c>
-      <c r="S36" s="55">
+      <c r="S36" s="52">
         <v>7</v>
       </c>
-      <c r="T36" s="55">
+      <c r="T36" s="52">
         <v>7</v>
       </c>
-      <c r="U36" s="55">
+      <c r="U36" s="52">
         <v>7</v>
       </c>
-      <c r="V36" s="57">
+      <c r="V36" s="54">
         <v>8</v>
       </c>
-      <c r="W36" s="57">
+      <c r="W36" s="54">
         <v>8</v>
       </c>
-      <c r="X36" s="57">
+      <c r="X36" s="54">
         <v>8</v>
       </c>
-      <c r="Y36" s="57">
+      <c r="Y36" s="54">
         <v>8</v>
       </c>
-      <c r="Z36" s="57">
+      <c r="Z36" s="54">
         <v>8</v>
       </c>
-      <c r="AA36" s="36">
+      <c r="AA36" s="33">
         <v>14</v>
       </c>
-      <c r="AB36" s="37">
+      <c r="AB36" s="34">
         <v>14</v>
       </c>
       <c r="AD36" s="11">
@@ -4325,76 +4472,76 @@
       <c r="D37" t="s">
         <v>26</v>
       </c>
-      <c r="E37" s="41">
+      <c r="E37" s="38">
         <v>13</v>
       </c>
-      <c r="F37" s="42">
+      <c r="F37" s="39">
         <v>13</v>
       </c>
-      <c r="G37" s="51">
-        <v>5</v>
-      </c>
-      <c r="H37" s="51">
-        <v>5</v>
-      </c>
-      <c r="I37" s="51">
-        <v>5</v>
-      </c>
-      <c r="J37" s="51">
-        <v>5</v>
-      </c>
-      <c r="K37" s="51">
-        <v>5</v>
-      </c>
-      <c r="L37" s="53">
-        <v>6</v>
-      </c>
-      <c r="M37" s="53">
-        <v>6</v>
-      </c>
-      <c r="N37" s="53">
-        <v>6</v>
-      </c>
-      <c r="O37" s="53">
-        <v>6</v>
-      </c>
-      <c r="P37" s="53">
-        <v>6</v>
-      </c>
-      <c r="Q37" s="55">
+      <c r="G37" s="48">
+        <v>5</v>
+      </c>
+      <c r="H37" s="48">
+        <v>5</v>
+      </c>
+      <c r="I37" s="48">
+        <v>5</v>
+      </c>
+      <c r="J37" s="48">
+        <v>5</v>
+      </c>
+      <c r="K37" s="48">
+        <v>5</v>
+      </c>
+      <c r="L37" s="50">
+        <v>6</v>
+      </c>
+      <c r="M37" s="50">
+        <v>6</v>
+      </c>
+      <c r="N37" s="50">
+        <v>6</v>
+      </c>
+      <c r="O37" s="50">
+        <v>6</v>
+      </c>
+      <c r="P37" s="50">
+        <v>6</v>
+      </c>
+      <c r="Q37" s="52">
         <v>7</v>
       </c>
-      <c r="R37" s="55">
+      <c r="R37" s="52">
         <v>7</v>
       </c>
-      <c r="S37" s="55">
+      <c r="S37" s="52">
         <v>7</v>
       </c>
-      <c r="T37" s="55">
+      <c r="T37" s="52">
         <v>7</v>
       </c>
-      <c r="U37" s="55">
+      <c r="U37" s="52">
         <v>7</v>
       </c>
-      <c r="V37" s="57">
+      <c r="V37" s="54">
         <v>8</v>
       </c>
-      <c r="W37" s="57">
+      <c r="W37" s="54">
         <v>8</v>
       </c>
-      <c r="X37" s="57">
+      <c r="X37" s="54">
         <v>8</v>
       </c>
-      <c r="Y37" s="57">
+      <c r="Y37" s="54">
         <v>8</v>
       </c>
-      <c r="Z37" s="57">
+      <c r="Z37" s="54">
         <v>8</v>
       </c>
-      <c r="AA37" s="36">
+      <c r="AA37" s="33">
         <v>14</v>
       </c>
-      <c r="AB37" s="37">
+      <c r="AB37" s="34">
         <v>14</v>
       </c>
       <c r="AD37" s="11">
@@ -4408,76 +4555,76 @@
       <c r="D38" t="s">
         <v>27</v>
       </c>
-      <c r="E38" s="41">
+      <c r="E38" s="38">
         <v>13</v>
       </c>
-      <c r="F38" s="42">
+      <c r="F38" s="39">
         <v>13</v>
       </c>
-      <c r="G38" s="51">
-        <v>5</v>
-      </c>
-      <c r="H38" s="51">
-        <v>5</v>
-      </c>
-      <c r="I38" s="51">
-        <v>5</v>
-      </c>
-      <c r="J38" s="51">
-        <v>5</v>
-      </c>
-      <c r="K38" s="51">
-        <v>5</v>
-      </c>
-      <c r="L38" s="53">
-        <v>6</v>
-      </c>
-      <c r="M38" s="53">
-        <v>6</v>
-      </c>
-      <c r="N38" s="53">
-        <v>6</v>
-      </c>
-      <c r="O38" s="53">
-        <v>6</v>
-      </c>
-      <c r="P38" s="53">
-        <v>6</v>
-      </c>
-      <c r="Q38" s="55">
+      <c r="G38" s="48">
+        <v>5</v>
+      </c>
+      <c r="H38" s="48">
+        <v>5</v>
+      </c>
+      <c r="I38" s="48">
+        <v>5</v>
+      </c>
+      <c r="J38" s="48">
+        <v>5</v>
+      </c>
+      <c r="K38" s="48">
+        <v>5</v>
+      </c>
+      <c r="L38" s="50">
+        <v>6</v>
+      </c>
+      <c r="M38" s="50">
+        <v>6</v>
+      </c>
+      <c r="N38" s="50">
+        <v>6</v>
+      </c>
+      <c r="O38" s="50">
+        <v>6</v>
+      </c>
+      <c r="P38" s="50">
+        <v>6</v>
+      </c>
+      <c r="Q38" s="52">
         <v>7</v>
       </c>
-      <c r="R38" s="55">
+      <c r="R38" s="52">
         <v>7</v>
       </c>
-      <c r="S38" s="55">
+      <c r="S38" s="52">
         <v>7</v>
       </c>
-      <c r="T38" s="55">
+      <c r="T38" s="52">
         <v>7</v>
       </c>
-      <c r="U38" s="55">
+      <c r="U38" s="52">
         <v>7</v>
       </c>
-      <c r="V38" s="57">
+      <c r="V38" s="54">
         <v>8</v>
       </c>
-      <c r="W38" s="57">
+      <c r="W38" s="54">
         <v>8</v>
       </c>
-      <c r="X38" s="57">
+      <c r="X38" s="54">
         <v>8</v>
       </c>
-      <c r="Y38" s="57">
+      <c r="Y38" s="54">
         <v>8</v>
       </c>
-      <c r="Z38" s="57">
+      <c r="Z38" s="54">
         <v>8</v>
       </c>
-      <c r="AA38" s="36">
+      <c r="AA38" s="33">
         <v>14</v>
       </c>
-      <c r="AB38" s="37">
+      <c r="AB38" s="34">
         <v>14</v>
       </c>
       <c r="AD38" s="11">
@@ -4491,76 +4638,76 @@
       <c r="D39" t="s">
         <v>28</v>
       </c>
-      <c r="E39" s="41">
+      <c r="E39" s="38">
         <v>13</v>
       </c>
-      <c r="F39" s="42">
+      <c r="F39" s="39">
         <v>13</v>
       </c>
-      <c r="G39" s="51">
-        <v>5</v>
-      </c>
-      <c r="H39" s="51">
-        <v>5</v>
-      </c>
-      <c r="I39" s="51">
-        <v>5</v>
-      </c>
-      <c r="J39" s="51">
-        <v>5</v>
-      </c>
-      <c r="K39" s="51">
-        <v>5</v>
-      </c>
-      <c r="L39" s="53">
-        <v>6</v>
-      </c>
-      <c r="M39" s="53">
-        <v>6</v>
-      </c>
-      <c r="N39" s="53">
-        <v>6</v>
-      </c>
-      <c r="O39" s="53">
-        <v>6</v>
-      </c>
-      <c r="P39" s="53">
-        <v>6</v>
-      </c>
-      <c r="Q39" s="55">
+      <c r="G39" s="48">
+        <v>5</v>
+      </c>
+      <c r="H39" s="48">
+        <v>5</v>
+      </c>
+      <c r="I39" s="48">
+        <v>5</v>
+      </c>
+      <c r="J39" s="48">
+        <v>5</v>
+      </c>
+      <c r="K39" s="48">
+        <v>5</v>
+      </c>
+      <c r="L39" s="50">
+        <v>6</v>
+      </c>
+      <c r="M39" s="50">
+        <v>6</v>
+      </c>
+      <c r="N39" s="50">
+        <v>6</v>
+      </c>
+      <c r="O39" s="50">
+        <v>6</v>
+      </c>
+      <c r="P39" s="50">
+        <v>6</v>
+      </c>
+      <c r="Q39" s="52">
         <v>7</v>
       </c>
-      <c r="R39" s="55">
+      <c r="R39" s="52">
         <v>7</v>
       </c>
-      <c r="S39" s="55">
+      <c r="S39" s="52">
         <v>7</v>
       </c>
-      <c r="T39" s="55">
+      <c r="T39" s="52">
         <v>7</v>
       </c>
-      <c r="U39" s="55">
+      <c r="U39" s="52">
         <v>7</v>
       </c>
-      <c r="V39" s="57">
+      <c r="V39" s="54">
         <v>8</v>
       </c>
-      <c r="W39" s="57">
+      <c r="W39" s="54">
         <v>8</v>
       </c>
-      <c r="X39" s="57">
+      <c r="X39" s="54">
         <v>8</v>
       </c>
-      <c r="Y39" s="57">
+      <c r="Y39" s="54">
         <v>8</v>
       </c>
-      <c r="Z39" s="57">
+      <c r="Z39" s="54">
         <v>8</v>
       </c>
-      <c r="AA39" s="36">
+      <c r="AA39" s="33">
         <v>14</v>
       </c>
-      <c r="AB39" s="37">
+      <c r="AB39" s="34">
         <v>14</v>
       </c>
       <c r="AD39" s="11">
@@ -4604,14 +4751,14 @@
       <c r="AE40" s="11"/>
       <c r="AF40" s="10"/>
       <c r="AG40" s="10"/>
-      <c r="AJ40" s="28"/>
-      <c r="AK40" s="28"/>
+      <c r="AJ40" s="27"/>
+      <c r="AK40" s="27"/>
     </row>
     <row r="41" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A41" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B41" s="4" t="s">
+      <c r="A41" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="85" t="s">
         <v>10</v>
       </c>
       <c r="D41" t="s">
@@ -4695,15 +4842,15 @@
       <c r="AE41" s="11"/>
       <c r="AF41" s="10"/>
       <c r="AG41" s="10"/>
-      <c r="AJ41" s="28"/>
-      <c r="AK41" s="28"/>
+      <c r="AJ41" s="27"/>
+      <c r="AK41" s="27"/>
     </row>
     <row r="42" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="B42" s="12" t="s">
-        <v>82</v>
+      <c r="B42" s="87" t="s">
+        <v>80</v>
       </c>
       <c r="D42" t="s">
         <v>13</v>
@@ -4711,73 +4858,73 @@
       <c r="E42" s="13">
         <v>17</v>
       </c>
-      <c r="F42" s="45">
+      <c r="F42" s="42">
         <v>16</v>
       </c>
-      <c r="G42" s="66">
-        <v>9</v>
-      </c>
-      <c r="H42" s="66">
-        <v>9</v>
-      </c>
-      <c r="I42" s="66">
-        <v>9</v>
-      </c>
-      <c r="J42" s="66">
-        <v>9</v>
-      </c>
-      <c r="K42" s="66">
-        <v>9</v>
-      </c>
-      <c r="L42" s="68">
-        <v>10</v>
-      </c>
-      <c r="M42" s="68">
-        <v>10</v>
-      </c>
-      <c r="N42" s="68">
-        <v>10</v>
-      </c>
-      <c r="O42" s="68">
-        <v>10</v>
-      </c>
-      <c r="P42" s="68">
-        <v>10</v>
-      </c>
-      <c r="Q42" s="70">
+      <c r="G42" s="63">
+        <v>9</v>
+      </c>
+      <c r="H42" s="63">
+        <v>9</v>
+      </c>
+      <c r="I42" s="63">
+        <v>9</v>
+      </c>
+      <c r="J42" s="63">
+        <v>9</v>
+      </c>
+      <c r="K42" s="63">
+        <v>9</v>
+      </c>
+      <c r="L42" s="65">
+        <v>10</v>
+      </c>
+      <c r="M42" s="65">
+        <v>10</v>
+      </c>
+      <c r="N42" s="65">
+        <v>10</v>
+      </c>
+      <c r="O42" s="65">
+        <v>10</v>
+      </c>
+      <c r="P42" s="65">
+        <v>10</v>
+      </c>
+      <c r="Q42" s="67">
         <v>11</v>
       </c>
-      <c r="R42" s="70">
+      <c r="R42" s="67">
         <v>11</v>
       </c>
-      <c r="S42" s="70">
+      <c r="S42" s="67">
         <v>11</v>
       </c>
-      <c r="T42" s="70">
+      <c r="T42" s="67">
         <v>11</v>
       </c>
-      <c r="U42" s="70">
+      <c r="U42" s="67">
         <v>11</v>
       </c>
-      <c r="V42" s="72">
+      <c r="V42" s="69">
         <v>12</v>
       </c>
-      <c r="W42" s="72">
+      <c r="W42" s="69">
         <v>12</v>
       </c>
-      <c r="X42" s="72">
+      <c r="X42" s="69">
         <v>12</v>
       </c>
-      <c r="Y42" s="72">
+      <c r="Y42" s="69">
         <v>12</v>
       </c>
-      <c r="Z42" s="72">
+      <c r="Z42" s="69">
         <v>12</v>
       </c>
-      <c r="AA42" s="45">
+      <c r="AA42" s="42">
         <v>16</v>
       </c>
-      <c r="AB42" s="46">
+      <c r="AB42" s="43">
         <v>16</v>
       </c>
       <c r="AD42" s="11">
@@ -4788,79 +4935,81 @@
       <c r="AG42" s="10"/>
     </row>
     <row r="43" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A43" s="25"/>
+      <c r="B43" s="25"/>
       <c r="D43" t="s">
         <v>14</v>
       </c>
-      <c r="E43" s="43">
+      <c r="E43" s="40">
         <v>15</v>
       </c>
-      <c r="F43" s="47">
+      <c r="F43" s="44">
         <v>16</v>
       </c>
-      <c r="G43" s="67">
-        <v>9</v>
-      </c>
-      <c r="H43" s="67">
-        <v>9</v>
-      </c>
-      <c r="I43" s="67">
-        <v>9</v>
-      </c>
-      <c r="J43" s="67">
-        <v>9</v>
-      </c>
-      <c r="K43" s="67">
-        <v>9</v>
-      </c>
-      <c r="L43" s="69">
-        <v>10</v>
-      </c>
-      <c r="M43" s="69">
-        <v>10</v>
-      </c>
-      <c r="N43" s="69">
-        <v>10</v>
-      </c>
-      <c r="O43" s="69">
-        <v>10</v>
-      </c>
-      <c r="P43" s="69">
-        <v>10</v>
-      </c>
-      <c r="Q43" s="71">
+      <c r="G43" s="64">
+        <v>9</v>
+      </c>
+      <c r="H43" s="64">
+        <v>9</v>
+      </c>
+      <c r="I43" s="64">
+        <v>9</v>
+      </c>
+      <c r="J43" s="64">
+        <v>9</v>
+      </c>
+      <c r="K43" s="64">
+        <v>9</v>
+      </c>
+      <c r="L43" s="66">
+        <v>10</v>
+      </c>
+      <c r="M43" s="66">
+        <v>10</v>
+      </c>
+      <c r="N43" s="66">
+        <v>10</v>
+      </c>
+      <c r="O43" s="66">
+        <v>10</v>
+      </c>
+      <c r="P43" s="66">
+        <v>10</v>
+      </c>
+      <c r="Q43" s="68">
         <v>11</v>
       </c>
-      <c r="R43" s="71">
+      <c r="R43" s="68">
         <v>11</v>
       </c>
-      <c r="S43" s="71">
+      <c r="S43" s="68">
         <v>11</v>
       </c>
-      <c r="T43" s="71">
+      <c r="T43" s="68">
         <v>11</v>
       </c>
-      <c r="U43" s="71">
+      <c r="U43" s="68">
         <v>11</v>
       </c>
-      <c r="V43" s="73">
+      <c r="V43" s="70">
         <v>12</v>
       </c>
-      <c r="W43" s="73">
+      <c r="W43" s="70">
         <v>12</v>
       </c>
-      <c r="X43" s="73">
+      <c r="X43" s="70">
         <v>12</v>
       </c>
-      <c r="Y43" s="73">
+      <c r="Y43" s="70">
         <v>12</v>
       </c>
-      <c r="Z43" s="73">
+      <c r="Z43" s="70">
         <v>12</v>
       </c>
-      <c r="AA43" s="47">
+      <c r="AA43" s="44">
         <v>16</v>
       </c>
-      <c r="AB43" s="48">
+      <c r="AB43" s="45">
         <v>16</v>
       </c>
       <c r="AD43" s="11">
@@ -4871,79 +5020,81 @@
       <c r="AG43" s="10"/>
     </row>
     <row r="44" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A44" s="25"/>
+      <c r="B44" s="25"/>
       <c r="D44" t="s">
         <v>15</v>
       </c>
-      <c r="E44" s="43">
+      <c r="E44" s="40">
         <v>15</v>
       </c>
-      <c r="F44" s="47">
+      <c r="F44" s="44">
         <v>16</v>
       </c>
-      <c r="G44" s="67">
-        <v>9</v>
-      </c>
-      <c r="H44" s="67">
-        <v>9</v>
-      </c>
-      <c r="I44" s="67">
-        <v>9</v>
-      </c>
-      <c r="J44" s="67">
-        <v>9</v>
-      </c>
-      <c r="K44" s="67">
-        <v>9</v>
-      </c>
-      <c r="L44" s="69">
-        <v>10</v>
-      </c>
-      <c r="M44" s="69">
-        <v>10</v>
-      </c>
-      <c r="N44" s="69">
-        <v>10</v>
-      </c>
-      <c r="O44" s="69">
-        <v>10</v>
-      </c>
-      <c r="P44" s="69">
-        <v>10</v>
-      </c>
-      <c r="Q44" s="71">
+      <c r="G44" s="64">
+        <v>9</v>
+      </c>
+      <c r="H44" s="64">
+        <v>9</v>
+      </c>
+      <c r="I44" s="64">
+        <v>9</v>
+      </c>
+      <c r="J44" s="64">
+        <v>9</v>
+      </c>
+      <c r="K44" s="64">
+        <v>9</v>
+      </c>
+      <c r="L44" s="66">
+        <v>10</v>
+      </c>
+      <c r="M44" s="66">
+        <v>10</v>
+      </c>
+      <c r="N44" s="66">
+        <v>10</v>
+      </c>
+      <c r="O44" s="66">
+        <v>10</v>
+      </c>
+      <c r="P44" s="66">
+        <v>10</v>
+      </c>
+      <c r="Q44" s="68">
         <v>11</v>
       </c>
-      <c r="R44" s="71">
+      <c r="R44" s="68">
         <v>11</v>
       </c>
-      <c r="S44" s="71">
+      <c r="S44" s="68">
         <v>11</v>
       </c>
-      <c r="T44" s="71">
+      <c r="T44" s="68">
         <v>11</v>
       </c>
-      <c r="U44" s="71">
+      <c r="U44" s="68">
         <v>11</v>
       </c>
-      <c r="V44" s="73">
+      <c r="V44" s="70">
         <v>12</v>
       </c>
-      <c r="W44" s="73">
+      <c r="W44" s="70">
         <v>12</v>
       </c>
-      <c r="X44" s="73">
+      <c r="X44" s="70">
         <v>12</v>
       </c>
-      <c r="Y44" s="73">
+      <c r="Y44" s="70">
         <v>12</v>
       </c>
-      <c r="Z44" s="73">
+      <c r="Z44" s="70">
         <v>12</v>
       </c>
-      <c r="AA44" s="47">
+      <c r="AA44" s="44">
         <v>16</v>
       </c>
-      <c r="AB44" s="48">
+      <c r="AB44" s="45">
         <v>16</v>
       </c>
       <c r="AD44" s="11">
@@ -4954,79 +5105,83 @@
       <c r="AG44" s="10"/>
     </row>
     <row r="45" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="25"/>
+      <c r="B45" s="88" t="s">
+        <v>101</v>
+      </c>
       <c r="D45" t="s">
         <v>16</v>
       </c>
-      <c r="E45" s="43">
+      <c r="E45" s="40">
         <v>15</v>
       </c>
-      <c r="F45" s="47">
+      <c r="F45" s="44">
         <v>16</v>
       </c>
-      <c r="G45" s="67">
-        <v>9</v>
-      </c>
-      <c r="H45" s="67">
-        <v>9</v>
-      </c>
-      <c r="I45" s="67">
-        <v>9</v>
-      </c>
-      <c r="J45" s="67">
-        <v>9</v>
-      </c>
-      <c r="K45" s="67">
-        <v>9</v>
-      </c>
-      <c r="L45" s="69">
-        <v>10</v>
-      </c>
-      <c r="M45" s="69">
-        <v>10</v>
-      </c>
-      <c r="N45" s="69">
-        <v>10</v>
-      </c>
-      <c r="O45" s="69">
-        <v>10</v>
-      </c>
-      <c r="P45" s="69">
-        <v>10</v>
-      </c>
-      <c r="Q45" s="71">
+      <c r="G45" s="64">
+        <v>9</v>
+      </c>
+      <c r="H45" s="64">
+        <v>9</v>
+      </c>
+      <c r="I45" s="64">
+        <v>9</v>
+      </c>
+      <c r="J45" s="64">
+        <v>9</v>
+      </c>
+      <c r="K45" s="64">
+        <v>9</v>
+      </c>
+      <c r="L45" s="66">
+        <v>10</v>
+      </c>
+      <c r="M45" s="66">
+        <v>10</v>
+      </c>
+      <c r="N45" s="66">
+        <v>10</v>
+      </c>
+      <c r="O45" s="66">
+        <v>10</v>
+      </c>
+      <c r="P45" s="66">
+        <v>10</v>
+      </c>
+      <c r="Q45" s="68">
         <v>11</v>
       </c>
-      <c r="R45" s="71">
+      <c r="R45" s="68">
         <v>11</v>
       </c>
-      <c r="S45" s="71">
+      <c r="S45" s="68">
         <v>11</v>
       </c>
-      <c r="T45" s="71">
+      <c r="T45" s="68">
         <v>11</v>
       </c>
-      <c r="U45" s="71">
+      <c r="U45" s="68">
         <v>11</v>
       </c>
-      <c r="V45" s="73">
+      <c r="V45" s="70">
         <v>12</v>
       </c>
-      <c r="W45" s="73">
+      <c r="W45" s="70">
         <v>12</v>
       </c>
-      <c r="X45" s="73">
+      <c r="X45" s="70">
         <v>12</v>
       </c>
-      <c r="Y45" s="73">
+      <c r="Y45" s="70">
         <v>12</v>
       </c>
-      <c r="Z45" s="73">
+      <c r="Z45" s="70">
         <v>12</v>
       </c>
-      <c r="AA45" s="47">
+      <c r="AA45" s="44">
         <v>16</v>
       </c>
-      <c r="AB45" s="48">
+      <c r="AB45" s="45">
         <v>16</v>
       </c>
       <c r="AD45" s="11">
@@ -5037,79 +5192,83 @@
       <c r="AG45" s="10"/>
     </row>
     <row r="46" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A46" s="25">
+        <v>1</v>
+      </c>
+      <c r="B46" s="24"/>
       <c r="D46" t="s">
         <v>17</v>
       </c>
-      <c r="E46" s="43">
+      <c r="E46" s="40">
         <v>15</v>
       </c>
-      <c r="F46" s="47">
+      <c r="F46" s="44">
         <v>16</v>
       </c>
-      <c r="G46" s="67">
-        <v>9</v>
-      </c>
-      <c r="H46" s="67">
-        <v>9</v>
-      </c>
-      <c r="I46" s="67">
-        <v>9</v>
-      </c>
-      <c r="J46" s="67">
-        <v>9</v>
-      </c>
-      <c r="K46" s="67">
-        <v>9</v>
-      </c>
-      <c r="L46" s="69">
-        <v>10</v>
-      </c>
-      <c r="M46" s="69">
-        <v>10</v>
-      </c>
-      <c r="N46" s="69">
-        <v>10</v>
-      </c>
-      <c r="O46" s="69">
-        <v>10</v>
-      </c>
-      <c r="P46" s="69">
-        <v>10</v>
-      </c>
-      <c r="Q46" s="71">
+      <c r="G46" s="64">
+        <v>9</v>
+      </c>
+      <c r="H46" s="64">
+        <v>9</v>
+      </c>
+      <c r="I46" s="64">
+        <v>9</v>
+      </c>
+      <c r="J46" s="64">
+        <v>9</v>
+      </c>
+      <c r="K46" s="64">
+        <v>9</v>
+      </c>
+      <c r="L46" s="66">
+        <v>10</v>
+      </c>
+      <c r="M46" s="66">
+        <v>10</v>
+      </c>
+      <c r="N46" s="66">
+        <v>10</v>
+      </c>
+      <c r="O46" s="66">
+        <v>10</v>
+      </c>
+      <c r="P46" s="66">
+        <v>10</v>
+      </c>
+      <c r="Q46" s="68">
         <v>11</v>
       </c>
-      <c r="R46" s="71">
+      <c r="R46" s="68">
         <v>11</v>
       </c>
-      <c r="S46" s="71">
+      <c r="S46" s="68">
         <v>11</v>
       </c>
-      <c r="T46" s="71">
+      <c r="T46" s="68">
         <v>11</v>
       </c>
-      <c r="U46" s="71">
+      <c r="U46" s="68">
         <v>11</v>
       </c>
-      <c r="V46" s="73">
+      <c r="V46" s="70">
         <v>12</v>
       </c>
-      <c r="W46" s="73">
+      <c r="W46" s="70">
         <v>12</v>
       </c>
-      <c r="X46" s="73">
+      <c r="X46" s="70">
         <v>12</v>
       </c>
-      <c r="Y46" s="73">
+      <c r="Y46" s="70">
         <v>12</v>
       </c>
-      <c r="Z46" s="73">
+      <c r="Z46" s="70">
         <v>12</v>
       </c>
-      <c r="AA46" s="47">
+      <c r="AA46" s="44">
         <v>16</v>
       </c>
-      <c r="AB46" s="48">
+      <c r="AB46" s="45">
         <v>16</v>
       </c>
       <c r="AD46" s="11">
@@ -5120,79 +5279,83 @@
       <c r="AG46" s="10"/>
     </row>
     <row r="47" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A47" s="25">
+        <v>2</v>
+      </c>
+      <c r="B47" s="24"/>
       <c r="D47" t="s">
         <v>18</v>
       </c>
-      <c r="E47" s="43">
+      <c r="E47" s="40">
         <v>15</v>
       </c>
-      <c r="F47" s="47">
+      <c r="F47" s="44">
         <v>16</v>
       </c>
-      <c r="G47" s="67">
-        <v>9</v>
-      </c>
-      <c r="H47" s="67">
-        <v>9</v>
-      </c>
-      <c r="I47" s="67">
-        <v>9</v>
-      </c>
-      <c r="J47" s="67">
-        <v>9</v>
-      </c>
-      <c r="K47" s="67">
-        <v>9</v>
-      </c>
-      <c r="L47" s="69">
-        <v>10</v>
-      </c>
-      <c r="M47" s="69">
-        <v>10</v>
-      </c>
-      <c r="N47" s="69">
-        <v>10</v>
-      </c>
-      <c r="O47" s="69">
-        <v>10</v>
-      </c>
-      <c r="P47" s="69">
-        <v>10</v>
-      </c>
-      <c r="Q47" s="71">
+      <c r="G47" s="64">
+        <v>9</v>
+      </c>
+      <c r="H47" s="64">
+        <v>9</v>
+      </c>
+      <c r="I47" s="64">
+        <v>9</v>
+      </c>
+      <c r="J47" s="64">
+        <v>9</v>
+      </c>
+      <c r="K47" s="64">
+        <v>9</v>
+      </c>
+      <c r="L47" s="66">
+        <v>10</v>
+      </c>
+      <c r="M47" s="66">
+        <v>10</v>
+      </c>
+      <c r="N47" s="66">
+        <v>10</v>
+      </c>
+      <c r="O47" s="66">
+        <v>10</v>
+      </c>
+      <c r="P47" s="66">
+        <v>10</v>
+      </c>
+      <c r="Q47" s="68">
         <v>11</v>
       </c>
-      <c r="R47" s="71">
+      <c r="R47" s="68">
         <v>11</v>
       </c>
-      <c r="S47" s="71">
+      <c r="S47" s="68">
         <v>11</v>
       </c>
-      <c r="T47" s="71">
+      <c r="T47" s="68">
         <v>11</v>
       </c>
-      <c r="U47" s="71">
+      <c r="U47" s="68">
         <v>11</v>
       </c>
-      <c r="V47" s="73">
+      <c r="V47" s="70">
         <v>12</v>
       </c>
-      <c r="W47" s="73">
+      <c r="W47" s="70">
         <v>12</v>
       </c>
-      <c r="X47" s="73">
+      <c r="X47" s="70">
         <v>12</v>
       </c>
-      <c r="Y47" s="73">
+      <c r="Y47" s="70">
         <v>12</v>
       </c>
-      <c r="Z47" s="73">
+      <c r="Z47" s="70">
         <v>12</v>
       </c>
-      <c r="AA47" s="47">
+      <c r="AA47" s="44">
         <v>16</v>
       </c>
-      <c r="AB47" s="48">
+      <c r="AB47" s="45">
         <v>16</v>
       </c>
       <c r="AD47" s="11">
@@ -5203,79 +5366,83 @@
       <c r="AG47" s="10"/>
     </row>
     <row r="48" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A48" s="25">
+        <v>3</v>
+      </c>
+      <c r="B48" s="24"/>
       <c r="D48" t="s">
         <v>19</v>
       </c>
-      <c r="E48" s="43">
+      <c r="E48" s="40">
         <v>15</v>
       </c>
-      <c r="F48" s="47">
+      <c r="F48" s="44">
         <v>16</v>
       </c>
-      <c r="G48" s="67">
-        <v>9</v>
-      </c>
-      <c r="H48" s="67">
-        <v>9</v>
-      </c>
-      <c r="I48" s="67">
-        <v>9</v>
-      </c>
-      <c r="J48" s="67">
-        <v>9</v>
-      </c>
-      <c r="K48" s="67">
-        <v>9</v>
-      </c>
-      <c r="L48" s="69">
-        <v>10</v>
-      </c>
-      <c r="M48" s="69">
-        <v>10</v>
-      </c>
-      <c r="N48" s="69">
-        <v>10</v>
-      </c>
-      <c r="O48" s="69">
-        <v>10</v>
-      </c>
-      <c r="P48" s="69">
-        <v>10</v>
-      </c>
-      <c r="Q48" s="71">
+      <c r="G48" s="64">
+        <v>9</v>
+      </c>
+      <c r="H48" s="64">
+        <v>9</v>
+      </c>
+      <c r="I48" s="64">
+        <v>9</v>
+      </c>
+      <c r="J48" s="64">
+        <v>9</v>
+      </c>
+      <c r="K48" s="64">
+        <v>9</v>
+      </c>
+      <c r="L48" s="66">
+        <v>10</v>
+      </c>
+      <c r="M48" s="66">
+        <v>10</v>
+      </c>
+      <c r="N48" s="66">
+        <v>10</v>
+      </c>
+      <c r="O48" s="66">
+        <v>10</v>
+      </c>
+      <c r="P48" s="66">
+        <v>10</v>
+      </c>
+      <c r="Q48" s="68">
         <v>11</v>
       </c>
-      <c r="R48" s="71">
+      <c r="R48" s="68">
         <v>11</v>
       </c>
-      <c r="S48" s="71">
+      <c r="S48" s="68">
         <v>11</v>
       </c>
-      <c r="T48" s="71">
+      <c r="T48" s="68">
         <v>11</v>
       </c>
-      <c r="U48" s="71">
+      <c r="U48" s="68">
         <v>11</v>
       </c>
-      <c r="V48" s="73">
+      <c r="V48" s="70">
         <v>12</v>
       </c>
-      <c r="W48" s="73">
+      <c r="W48" s="70">
         <v>12</v>
       </c>
-      <c r="X48" s="73">
+      <c r="X48" s="70">
         <v>12</v>
       </c>
-      <c r="Y48" s="73">
+      <c r="Y48" s="70">
         <v>12</v>
       </c>
-      <c r="Z48" s="73">
+      <c r="Z48" s="70">
         <v>12</v>
       </c>
-      <c r="AA48" s="47">
+      <c r="AA48" s="44">
         <v>16</v>
       </c>
-      <c r="AB48" s="48">
+      <c r="AB48" s="45">
         <v>16</v>
       </c>
       <c r="AD48" s="11">
@@ -5286,79 +5453,83 @@
       <c r="AG48" s="10"/>
     </row>
     <row r="49" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A49" s="25">
+        <v>4</v>
+      </c>
+      <c r="B49" s="24"/>
       <c r="D49" t="s">
         <v>20</v>
       </c>
-      <c r="E49" s="43">
+      <c r="E49" s="40">
         <v>15</v>
       </c>
-      <c r="F49" s="47">
+      <c r="F49" s="44">
         <v>16</v>
       </c>
-      <c r="G49" s="67">
-        <v>9</v>
-      </c>
-      <c r="H49" s="67">
-        <v>9</v>
-      </c>
-      <c r="I49" s="67">
-        <v>9</v>
-      </c>
-      <c r="J49" s="67">
-        <v>9</v>
-      </c>
-      <c r="K49" s="67">
-        <v>9</v>
-      </c>
-      <c r="L49" s="69">
-        <v>10</v>
-      </c>
-      <c r="M49" s="69">
-        <v>10</v>
-      </c>
-      <c r="N49" s="69">
-        <v>10</v>
-      </c>
-      <c r="O49" s="69">
-        <v>10</v>
-      </c>
-      <c r="P49" s="69">
-        <v>10</v>
-      </c>
-      <c r="Q49" s="71">
+      <c r="G49" s="64">
+        <v>9</v>
+      </c>
+      <c r="H49" s="64">
+        <v>9</v>
+      </c>
+      <c r="I49" s="64">
+        <v>9</v>
+      </c>
+      <c r="J49" s="64">
+        <v>9</v>
+      </c>
+      <c r="K49" s="64">
+        <v>9</v>
+      </c>
+      <c r="L49" s="66">
+        <v>10</v>
+      </c>
+      <c r="M49" s="66">
+        <v>10</v>
+      </c>
+      <c r="N49" s="66">
+        <v>10</v>
+      </c>
+      <c r="O49" s="66">
+        <v>10</v>
+      </c>
+      <c r="P49" s="66">
+        <v>10</v>
+      </c>
+      <c r="Q49" s="68">
         <v>11</v>
       </c>
-      <c r="R49" s="71">
+      <c r="R49" s="68">
         <v>11</v>
       </c>
-      <c r="S49" s="71">
+      <c r="S49" s="68">
         <v>11</v>
       </c>
-      <c r="T49" s="71">
+      <c r="T49" s="68">
         <v>11</v>
       </c>
-      <c r="U49" s="71">
+      <c r="U49" s="68">
         <v>11</v>
       </c>
-      <c r="V49" s="73">
+      <c r="V49" s="70">
         <v>12</v>
       </c>
-      <c r="W49" s="73">
+      <c r="W49" s="70">
         <v>12</v>
       </c>
-      <c r="X49" s="73">
+      <c r="X49" s="70">
         <v>12</v>
       </c>
-      <c r="Y49" s="73">
+      <c r="Y49" s="70">
         <v>12</v>
       </c>
-      <c r="Z49" s="73">
+      <c r="Z49" s="70">
         <v>12</v>
       </c>
-      <c r="AA49" s="47">
+      <c r="AA49" s="44">
         <v>16</v>
       </c>
-      <c r="AB49" s="48">
+      <c r="AB49" s="45">
         <v>16</v>
       </c>
       <c r="AD49" s="11">
@@ -5369,79 +5540,83 @@
       <c r="AG49" s="10"/>
     </row>
     <row r="50" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A50" s="25">
+        <v>5</v>
+      </c>
+      <c r="B50" s="29"/>
       <c r="D50" t="s">
         <v>21</v>
       </c>
-      <c r="E50" s="86">
+      <c r="E50" s="83">
         <v>16</v>
       </c>
-      <c r="F50" s="47">
+      <c r="F50" s="44">
         <v>16</v>
       </c>
-      <c r="G50" s="67">
-        <v>9</v>
-      </c>
-      <c r="H50" s="67">
-        <v>9</v>
-      </c>
-      <c r="I50" s="67">
-        <v>9</v>
-      </c>
-      <c r="J50" s="67">
-        <v>9</v>
-      </c>
-      <c r="K50" s="67">
-        <v>9</v>
-      </c>
-      <c r="L50" s="69">
-        <v>10</v>
-      </c>
-      <c r="M50" s="69">
-        <v>10</v>
-      </c>
-      <c r="N50" s="69">
-        <v>10</v>
-      </c>
-      <c r="O50" s="69">
-        <v>10</v>
-      </c>
-      <c r="P50" s="69">
-        <v>10</v>
-      </c>
-      <c r="Q50" s="71">
+      <c r="G50" s="64">
+        <v>9</v>
+      </c>
+      <c r="H50" s="64">
+        <v>9</v>
+      </c>
+      <c r="I50" s="64">
+        <v>9</v>
+      </c>
+      <c r="J50" s="64">
+        <v>9</v>
+      </c>
+      <c r="K50" s="64">
+        <v>9</v>
+      </c>
+      <c r="L50" s="66">
+        <v>10</v>
+      </c>
+      <c r="M50" s="66">
+        <v>10</v>
+      </c>
+      <c r="N50" s="66">
+        <v>10</v>
+      </c>
+      <c r="O50" s="66">
+        <v>10</v>
+      </c>
+      <c r="P50" s="66">
+        <v>10</v>
+      </c>
+      <c r="Q50" s="68">
         <v>11</v>
       </c>
-      <c r="R50" s="71">
+      <c r="R50" s="68">
         <v>11</v>
       </c>
-      <c r="S50" s="71">
+      <c r="S50" s="68">
         <v>11</v>
       </c>
-      <c r="T50" s="71">
+      <c r="T50" s="68">
         <v>11</v>
       </c>
-      <c r="U50" s="71">
+      <c r="U50" s="68">
         <v>11</v>
       </c>
-      <c r="V50" s="73">
+      <c r="V50" s="70">
         <v>12</v>
       </c>
-      <c r="W50" s="73">
+      <c r="W50" s="70">
         <v>12</v>
       </c>
-      <c r="X50" s="73">
+      <c r="X50" s="70">
         <v>12</v>
       </c>
-      <c r="Y50" s="73">
+      <c r="Y50" s="70">
         <v>12</v>
       </c>
-      <c r="Z50" s="73">
+      <c r="Z50" s="70">
         <v>12</v>
       </c>
-      <c r="AA50" s="47">
+      <c r="AA50" s="44">
         <v>16</v>
       </c>
-      <c r="AB50" s="48">
+      <c r="AB50" s="45">
         <v>16</v>
       </c>
       <c r="AD50" s="11">
@@ -5452,79 +5627,81 @@
       <c r="AG50" s="10"/>
     </row>
     <row r="51" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A51" s="25"/>
+      <c r="B51" s="25"/>
       <c r="D51" t="s">
         <v>22</v>
       </c>
-      <c r="E51" s="86">
+      <c r="E51" s="83">
         <v>16</v>
       </c>
-      <c r="F51" s="47">
+      <c r="F51" s="44">
         <v>16</v>
       </c>
-      <c r="G51" s="67">
-        <v>9</v>
-      </c>
-      <c r="H51" s="67">
-        <v>9</v>
-      </c>
-      <c r="I51" s="67">
-        <v>9</v>
-      </c>
-      <c r="J51" s="67">
-        <v>9</v>
-      </c>
-      <c r="K51" s="67">
-        <v>9</v>
-      </c>
-      <c r="L51" s="69">
-        <v>10</v>
-      </c>
-      <c r="M51" s="69">
-        <v>10</v>
-      </c>
-      <c r="N51" s="69">
-        <v>10</v>
-      </c>
-      <c r="O51" s="69">
-        <v>10</v>
-      </c>
-      <c r="P51" s="69">
-        <v>10</v>
-      </c>
-      <c r="Q51" s="71">
+      <c r="G51" s="64">
+        <v>9</v>
+      </c>
+      <c r="H51" s="64">
+        <v>9</v>
+      </c>
+      <c r="I51" s="64">
+        <v>9</v>
+      </c>
+      <c r="J51" s="64">
+        <v>9</v>
+      </c>
+      <c r="K51" s="64">
+        <v>9</v>
+      </c>
+      <c r="L51" s="66">
+        <v>10</v>
+      </c>
+      <c r="M51" s="66">
+        <v>10</v>
+      </c>
+      <c r="N51" s="66">
+        <v>10</v>
+      </c>
+      <c r="O51" s="66">
+        <v>10</v>
+      </c>
+      <c r="P51" s="66">
+        <v>10</v>
+      </c>
+      <c r="Q51" s="68">
         <v>11</v>
       </c>
-      <c r="R51" s="71">
+      <c r="R51" s="68">
         <v>11</v>
       </c>
-      <c r="S51" s="71">
+      <c r="S51" s="68">
         <v>11</v>
       </c>
-      <c r="T51" s="71">
+      <c r="T51" s="68">
         <v>11</v>
       </c>
-      <c r="U51" s="71">
+      <c r="U51" s="68">
         <v>11</v>
       </c>
-      <c r="V51" s="73">
+      <c r="V51" s="70">
         <v>12</v>
       </c>
-      <c r="W51" s="73">
+      <c r="W51" s="70">
         <v>12</v>
       </c>
-      <c r="X51" s="73">
+      <c r="X51" s="70">
         <v>12</v>
       </c>
-      <c r="Y51" s="73">
+      <c r="Y51" s="70">
         <v>12</v>
       </c>
-      <c r="Z51" s="73">
+      <c r="Z51" s="70">
         <v>12</v>
       </c>
-      <c r="AA51" s="47">
+      <c r="AA51" s="44">
         <v>16</v>
       </c>
-      <c r="AB51" s="48">
+      <c r="AB51" s="45">
         <v>16</v>
       </c>
       <c r="AD51" s="15">
@@ -5538,76 +5715,76 @@
       <c r="D52" t="s">
         <v>23</v>
       </c>
-      <c r="E52" s="86">
+      <c r="E52" s="83">
         <v>16</v>
       </c>
-      <c r="F52" s="47">
+      <c r="F52" s="44">
         <v>16</v>
       </c>
-      <c r="G52" s="67">
-        <v>9</v>
-      </c>
-      <c r="H52" s="67">
-        <v>9</v>
-      </c>
-      <c r="I52" s="67">
-        <v>9</v>
-      </c>
-      <c r="J52" s="67">
-        <v>9</v>
-      </c>
-      <c r="K52" s="67">
-        <v>9</v>
-      </c>
-      <c r="L52" s="69">
-        <v>10</v>
-      </c>
-      <c r="M52" s="69">
-        <v>10</v>
-      </c>
-      <c r="N52" s="69">
-        <v>10</v>
-      </c>
-      <c r="O52" s="69">
-        <v>10</v>
-      </c>
-      <c r="P52" s="69">
-        <v>10</v>
-      </c>
-      <c r="Q52" s="71">
+      <c r="G52" s="64">
+        <v>9</v>
+      </c>
+      <c r="H52" s="64">
+        <v>9</v>
+      </c>
+      <c r="I52" s="64">
+        <v>9</v>
+      </c>
+      <c r="J52" s="64">
+        <v>9</v>
+      </c>
+      <c r="K52" s="64">
+        <v>9</v>
+      </c>
+      <c r="L52" s="66">
+        <v>10</v>
+      </c>
+      <c r="M52" s="66">
+        <v>10</v>
+      </c>
+      <c r="N52" s="66">
+        <v>10</v>
+      </c>
+      <c r="O52" s="66">
+        <v>10</v>
+      </c>
+      <c r="P52" s="66">
+        <v>10</v>
+      </c>
+      <c r="Q52" s="68">
         <v>11</v>
       </c>
-      <c r="R52" s="71">
+      <c r="R52" s="68">
         <v>11</v>
       </c>
-      <c r="S52" s="71">
+      <c r="S52" s="68">
         <v>11</v>
       </c>
-      <c r="T52" s="71">
+      <c r="T52" s="68">
         <v>11</v>
       </c>
-      <c r="U52" s="71">
+      <c r="U52" s="68">
         <v>11</v>
       </c>
-      <c r="V52" s="73">
+      <c r="V52" s="70">
         <v>12</v>
       </c>
-      <c r="W52" s="73">
+      <c r="W52" s="70">
         <v>12</v>
       </c>
-      <c r="X52" s="73">
+      <c r="X52" s="70">
         <v>12</v>
       </c>
-      <c r="Y52" s="73">
+      <c r="Y52" s="70">
         <v>12</v>
       </c>
-      <c r="Z52" s="73">
+      <c r="Z52" s="70">
         <v>12</v>
       </c>
-      <c r="AA52" s="47">
+      <c r="AA52" s="44">
         <v>16</v>
       </c>
-      <c r="AB52" s="48">
+      <c r="AB52" s="45">
         <v>16</v>
       </c>
     </row>
@@ -5615,76 +5792,76 @@
       <c r="D53" t="s">
         <v>24</v>
       </c>
-      <c r="E53" s="86">
+      <c r="E53" s="83">
         <v>16</v>
       </c>
-      <c r="F53" s="47">
+      <c r="F53" s="44">
         <v>16</v>
       </c>
-      <c r="G53" s="67">
-        <v>9</v>
-      </c>
-      <c r="H53" s="67">
-        <v>9</v>
-      </c>
-      <c r="I53" s="67">
-        <v>9</v>
-      </c>
-      <c r="J53" s="67">
-        <v>9</v>
-      </c>
-      <c r="K53" s="67">
-        <v>9</v>
-      </c>
-      <c r="L53" s="69">
-        <v>10</v>
-      </c>
-      <c r="M53" s="69">
-        <v>10</v>
-      </c>
-      <c r="N53" s="69">
-        <v>10</v>
-      </c>
-      <c r="O53" s="69">
-        <v>10</v>
-      </c>
-      <c r="P53" s="69">
-        <v>10</v>
-      </c>
-      <c r="Q53" s="71">
+      <c r="G53" s="64">
+        <v>9</v>
+      </c>
+      <c r="H53" s="64">
+        <v>9</v>
+      </c>
+      <c r="I53" s="64">
+        <v>9</v>
+      </c>
+      <c r="J53" s="64">
+        <v>9</v>
+      </c>
+      <c r="K53" s="64">
+        <v>9</v>
+      </c>
+      <c r="L53" s="66">
+        <v>10</v>
+      </c>
+      <c r="M53" s="66">
+        <v>10</v>
+      </c>
+      <c r="N53" s="66">
+        <v>10</v>
+      </c>
+      <c r="O53" s="66">
+        <v>10</v>
+      </c>
+      <c r="P53" s="66">
+        <v>10</v>
+      </c>
+      <c r="Q53" s="68">
         <v>11</v>
       </c>
-      <c r="R53" s="71">
+      <c r="R53" s="68">
         <v>11</v>
       </c>
-      <c r="S53" s="71">
+      <c r="S53" s="68">
         <v>11</v>
       </c>
-      <c r="T53" s="71">
+      <c r="T53" s="68">
         <v>11</v>
       </c>
-      <c r="U53" s="71">
+      <c r="U53" s="68">
         <v>11</v>
       </c>
-      <c r="V53" s="73">
+      <c r="V53" s="70">
         <v>12</v>
       </c>
-      <c r="W53" s="73">
+      <c r="W53" s="70">
         <v>12</v>
       </c>
-      <c r="X53" s="73">
+      <c r="X53" s="70">
         <v>12</v>
       </c>
-      <c r="Y53" s="73">
+      <c r="Y53" s="70">
         <v>12</v>
       </c>
-      <c r="Z53" s="73">
+      <c r="Z53" s="70">
         <v>12</v>
       </c>
-      <c r="AA53" s="47">
+      <c r="AA53" s="44">
         <v>16</v>
       </c>
-      <c r="AB53" s="48">
+      <c r="AB53" s="45">
         <v>16</v>
       </c>
       <c r="AE53" s="18"/>
@@ -5696,76 +5873,76 @@
       <c r="D54" t="s">
         <v>25</v>
       </c>
-      <c r="E54" s="86">
+      <c r="E54" s="83">
         <v>16</v>
       </c>
-      <c r="F54" s="47">
+      <c r="F54" s="44">
         <v>16</v>
       </c>
-      <c r="G54" s="67">
-        <v>9</v>
-      </c>
-      <c r="H54" s="67">
-        <v>9</v>
-      </c>
-      <c r="I54" s="67">
-        <v>9</v>
-      </c>
-      <c r="J54" s="67">
-        <v>9</v>
-      </c>
-      <c r="K54" s="67">
-        <v>9</v>
-      </c>
-      <c r="L54" s="69">
-        <v>10</v>
-      </c>
-      <c r="M54" s="69">
-        <v>10</v>
-      </c>
-      <c r="N54" s="69">
-        <v>10</v>
-      </c>
-      <c r="O54" s="69">
-        <v>10</v>
-      </c>
-      <c r="P54" s="69">
-        <v>10</v>
-      </c>
-      <c r="Q54" s="71">
+      <c r="G54" s="64">
+        <v>9</v>
+      </c>
+      <c r="H54" s="64">
+        <v>9</v>
+      </c>
+      <c r="I54" s="64">
+        <v>9</v>
+      </c>
+      <c r="J54" s="64">
+        <v>9</v>
+      </c>
+      <c r="K54" s="64">
+        <v>9</v>
+      </c>
+      <c r="L54" s="66">
+        <v>10</v>
+      </c>
+      <c r="M54" s="66">
+        <v>10</v>
+      </c>
+      <c r="N54" s="66">
+        <v>10</v>
+      </c>
+      <c r="O54" s="66">
+        <v>10</v>
+      </c>
+      <c r="P54" s="66">
+        <v>10</v>
+      </c>
+      <c r="Q54" s="68">
         <v>11</v>
       </c>
-      <c r="R54" s="71">
+      <c r="R54" s="68">
         <v>11</v>
       </c>
-      <c r="S54" s="71">
+      <c r="S54" s="68">
         <v>11</v>
       </c>
-      <c r="T54" s="71">
+      <c r="T54" s="68">
         <v>11</v>
       </c>
-      <c r="U54" s="71">
+      <c r="U54" s="68">
         <v>11</v>
       </c>
-      <c r="V54" s="73">
+      <c r="V54" s="70">
         <v>12</v>
       </c>
-      <c r="W54" s="73">
+      <c r="W54" s="70">
         <v>12</v>
       </c>
-      <c r="X54" s="73">
+      <c r="X54" s="70">
         <v>12</v>
       </c>
-      <c r="Y54" s="73">
+      <c r="Y54" s="70">
         <v>12</v>
       </c>
-      <c r="Z54" s="73">
+      <c r="Z54" s="70">
         <v>12</v>
       </c>
-      <c r="AA54" s="47">
+      <c r="AA54" s="44">
         <v>16</v>
       </c>
-      <c r="AB54" s="48">
+      <c r="AB54" s="45">
         <v>16</v>
       </c>
       <c r="AE54" s="18"/>
@@ -5777,76 +5954,76 @@
       <c r="D55" t="s">
         <v>26</v>
       </c>
-      <c r="E55" s="86">
+      <c r="E55" s="83">
         <v>16</v>
       </c>
-      <c r="F55" s="47">
+      <c r="F55" s="44">
         <v>16</v>
       </c>
-      <c r="G55" s="67">
-        <v>9</v>
-      </c>
-      <c r="H55" s="67">
-        <v>9</v>
-      </c>
-      <c r="I55" s="67">
-        <v>9</v>
-      </c>
-      <c r="J55" s="67">
-        <v>9</v>
-      </c>
-      <c r="K55" s="67">
-        <v>9</v>
-      </c>
-      <c r="L55" s="69">
-        <v>10</v>
-      </c>
-      <c r="M55" s="69">
-        <v>10</v>
-      </c>
-      <c r="N55" s="69">
-        <v>10</v>
-      </c>
-      <c r="O55" s="69">
-        <v>10</v>
-      </c>
-      <c r="P55" s="69">
-        <v>10</v>
-      </c>
-      <c r="Q55" s="71">
+      <c r="G55" s="64">
+        <v>9</v>
+      </c>
+      <c r="H55" s="64">
+        <v>9</v>
+      </c>
+      <c r="I55" s="64">
+        <v>9</v>
+      </c>
+      <c r="J55" s="64">
+        <v>9</v>
+      </c>
+      <c r="K55" s="64">
+        <v>9</v>
+      </c>
+      <c r="L55" s="66">
+        <v>10</v>
+      </c>
+      <c r="M55" s="66">
+        <v>10</v>
+      </c>
+      <c r="N55" s="66">
+        <v>10</v>
+      </c>
+      <c r="O55" s="66">
+        <v>10</v>
+      </c>
+      <c r="P55" s="66">
+        <v>10</v>
+      </c>
+      <c r="Q55" s="68">
         <v>11</v>
       </c>
-      <c r="R55" s="71">
+      <c r="R55" s="68">
         <v>11</v>
       </c>
-      <c r="S55" s="71">
+      <c r="S55" s="68">
         <v>11</v>
       </c>
-      <c r="T55" s="71">
+      <c r="T55" s="68">
         <v>11</v>
       </c>
-      <c r="U55" s="71">
+      <c r="U55" s="68">
         <v>11</v>
       </c>
-      <c r="V55" s="73">
+      <c r="V55" s="70">
         <v>12</v>
       </c>
-      <c r="W55" s="73">
+      <c r="W55" s="70">
         <v>12</v>
       </c>
-      <c r="X55" s="73">
+      <c r="X55" s="70">
         <v>12</v>
       </c>
-      <c r="Y55" s="73">
+      <c r="Y55" s="70">
         <v>12</v>
       </c>
-      <c r="Z55" s="73">
+      <c r="Z55" s="70">
         <v>12</v>
       </c>
-      <c r="AA55" s="47">
+      <c r="AA55" s="44">
         <v>16</v>
       </c>
-      <c r="AB55" s="48">
+      <c r="AB55" s="45">
         <v>16</v>
       </c>
       <c r="AE55" s="18"/>
@@ -5858,76 +6035,76 @@
       <c r="D56" t="s">
         <v>27</v>
       </c>
-      <c r="E56" s="86">
+      <c r="E56" s="83">
         <v>16</v>
       </c>
-      <c r="F56" s="47">
+      <c r="F56" s="44">
         <v>16</v>
       </c>
-      <c r="G56" s="67">
-        <v>9</v>
-      </c>
-      <c r="H56" s="67">
-        <v>9</v>
-      </c>
-      <c r="I56" s="67">
-        <v>9</v>
-      </c>
-      <c r="J56" s="67">
-        <v>9</v>
-      </c>
-      <c r="K56" s="67">
-        <v>9</v>
-      </c>
-      <c r="L56" s="69">
-        <v>10</v>
-      </c>
-      <c r="M56" s="69">
-        <v>10</v>
-      </c>
-      <c r="N56" s="69">
-        <v>10</v>
-      </c>
-      <c r="O56" s="69">
-        <v>10</v>
-      </c>
-      <c r="P56" s="69">
-        <v>10</v>
-      </c>
-      <c r="Q56" s="71">
+      <c r="G56" s="64">
+        <v>9</v>
+      </c>
+      <c r="H56" s="64">
+        <v>9</v>
+      </c>
+      <c r="I56" s="64">
+        <v>9</v>
+      </c>
+      <c r="J56" s="64">
+        <v>9</v>
+      </c>
+      <c r="K56" s="64">
+        <v>9</v>
+      </c>
+      <c r="L56" s="66">
+        <v>10</v>
+      </c>
+      <c r="M56" s="66">
+        <v>10</v>
+      </c>
+      <c r="N56" s="66">
+        <v>10</v>
+      </c>
+      <c r="O56" s="66">
+        <v>10</v>
+      </c>
+      <c r="P56" s="66">
+        <v>10</v>
+      </c>
+      <c r="Q56" s="68">
         <v>11</v>
       </c>
-      <c r="R56" s="71">
+      <c r="R56" s="68">
         <v>11</v>
       </c>
-      <c r="S56" s="71">
+      <c r="S56" s="68">
         <v>11</v>
       </c>
-      <c r="T56" s="71">
+      <c r="T56" s="68">
         <v>11</v>
       </c>
-      <c r="U56" s="71">
+      <c r="U56" s="68">
         <v>11</v>
       </c>
-      <c r="V56" s="73">
+      <c r="V56" s="70">
         <v>12</v>
       </c>
-      <c r="W56" s="73">
+      <c r="W56" s="70">
         <v>12</v>
       </c>
-      <c r="X56" s="73">
+      <c r="X56" s="70">
         <v>12</v>
       </c>
-      <c r="Y56" s="73">
+      <c r="Y56" s="70">
         <v>12</v>
       </c>
-      <c r="Z56" s="73">
+      <c r="Z56" s="70">
         <v>12</v>
       </c>
-      <c r="AA56" s="47">
+      <c r="AA56" s="44">
         <v>16</v>
       </c>
-      <c r="AB56" s="48">
+      <c r="AB56" s="45">
         <v>16</v>
       </c>
       <c r="AE56" s="9"/>
@@ -5936,76 +6113,76 @@
       <c r="D57" t="s">
         <v>28</v>
       </c>
-      <c r="E57" s="86">
+      <c r="E57" s="83">
         <v>16</v>
       </c>
-      <c r="F57" s="47">
+      <c r="F57" s="44">
         <v>16</v>
       </c>
-      <c r="G57" s="67">
-        <v>9</v>
-      </c>
-      <c r="H57" s="67">
-        <v>9</v>
-      </c>
-      <c r="I57" s="67">
-        <v>9</v>
-      </c>
-      <c r="J57" s="67">
-        <v>9</v>
-      </c>
-      <c r="K57" s="67">
-        <v>9</v>
-      </c>
-      <c r="L57" s="69">
-        <v>10</v>
-      </c>
-      <c r="M57" s="69">
-        <v>10</v>
-      </c>
-      <c r="N57" s="69">
-        <v>10</v>
-      </c>
-      <c r="O57" s="69">
-        <v>10</v>
-      </c>
-      <c r="P57" s="69">
-        <v>10</v>
-      </c>
-      <c r="Q57" s="71">
+      <c r="G57" s="64">
+        <v>9</v>
+      </c>
+      <c r="H57" s="64">
+        <v>9</v>
+      </c>
+      <c r="I57" s="64">
+        <v>9</v>
+      </c>
+      <c r="J57" s="64">
+        <v>9</v>
+      </c>
+      <c r="K57" s="64">
+        <v>9</v>
+      </c>
+      <c r="L57" s="66">
+        <v>10</v>
+      </c>
+      <c r="M57" s="66">
+        <v>10</v>
+      </c>
+      <c r="N57" s="66">
+        <v>10</v>
+      </c>
+      <c r="O57" s="66">
+        <v>10</v>
+      </c>
+      <c r="P57" s="66">
+        <v>10</v>
+      </c>
+      <c r="Q57" s="68">
         <v>11</v>
       </c>
-      <c r="R57" s="71">
+      <c r="R57" s="68">
         <v>11</v>
       </c>
-      <c r="S57" s="71">
+      <c r="S57" s="68">
         <v>11</v>
       </c>
-      <c r="T57" s="71">
+      <c r="T57" s="68">
         <v>11</v>
       </c>
-      <c r="U57" s="71">
+      <c r="U57" s="68">
         <v>11</v>
       </c>
-      <c r="V57" s="73">
+      <c r="V57" s="70">
         <v>12</v>
       </c>
-      <c r="W57" s="73">
+      <c r="W57" s="70">
         <v>12</v>
       </c>
-      <c r="X57" s="73">
+      <c r="X57" s="70">
         <v>12</v>
       </c>
-      <c r="Y57" s="73">
+      <c r="Y57" s="70">
         <v>12</v>
       </c>
-      <c r="Z57" s="73">
+      <c r="Z57" s="70">
         <v>12</v>
       </c>
-      <c r="AA57" s="47">
+      <c r="AA57" s="44">
         <v>16</v>
       </c>
-      <c r="AB57" s="48">
+      <c r="AB57" s="45">
         <v>16</v>
       </c>
       <c r="AE57" s="9"/>
@@ -6049,6 +6226,87 @@
       <c r="AN58" s="18"/>
     </row>
     <row r="59" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" t="s">
+        <v>102</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59">
+        <v>2</v>
+      </c>
+      <c r="G59">
+        <v>3</v>
+      </c>
+      <c r="H59">
+        <v>4</v>
+      </c>
+      <c r="I59">
+        <v>5</v>
+      </c>
+      <c r="J59">
+        <v>6</v>
+      </c>
+      <c r="K59">
+        <v>7</v>
+      </c>
+      <c r="L59">
+        <v>8</v>
+      </c>
+      <c r="M59">
+        <v>9</v>
+      </c>
+      <c r="N59">
+        <v>10</v>
+      </c>
+      <c r="O59">
+        <v>11</v>
+      </c>
+      <c r="P59">
+        <v>12</v>
+      </c>
+      <c r="Q59">
+        <v>13</v>
+      </c>
+      <c r="R59">
+        <v>14</v>
+      </c>
+      <c r="S59">
+        <v>15</v>
+      </c>
+      <c r="T59">
+        <v>16</v>
+      </c>
+      <c r="U59">
+        <v>17</v>
+      </c>
+      <c r="V59">
+        <v>18</v>
+      </c>
+      <c r="W59">
+        <v>19</v>
+      </c>
+      <c r="X59">
+        <v>20</v>
+      </c>
+      <c r="Y59">
+        <v>21</v>
+      </c>
+      <c r="Z59">
+        <v>22</v>
+      </c>
+      <c r="AA59">
+        <v>23</v>
+      </c>
+      <c r="AB59">
+        <v>24</v>
+      </c>
       <c r="AE59" s="9"/>
       <c r="AK59" s="18"/>
       <c r="AL59" s="19"/>
@@ -6056,16 +6314,528 @@
       <c r="AN59" s="18"/>
     </row>
     <row r="60" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A60" s="84" t="s">
+        <v>103</v>
+      </c>
+      <c r="B60" s="12"/>
+      <c r="D60" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" s="13"/>
+      <c r="F60" s="89"/>
+      <c r="G60" s="89"/>
+      <c r="H60" s="89"/>
+      <c r="I60" s="89"/>
+      <c r="J60" s="89"/>
+      <c r="K60" s="89"/>
+      <c r="L60" s="89"/>
+      <c r="M60" s="89"/>
+      <c r="N60" s="89"/>
+      <c r="O60" s="89"/>
+      <c r="P60" s="89"/>
+      <c r="Q60" s="89"/>
+      <c r="R60" s="89"/>
+      <c r="S60" s="89"/>
+      <c r="T60" s="89"/>
+      <c r="U60" s="89"/>
+      <c r="V60" s="89"/>
+      <c r="W60" s="89"/>
+      <c r="X60" s="89"/>
+      <c r="Y60" s="89"/>
+      <c r="Z60" s="89"/>
+      <c r="AA60" s="89"/>
+      <c r="AB60" s="90"/>
       <c r="AE60" s="9"/>
     </row>
     <row r="61" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="D61" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="8"/>
+      <c r="F61" s="9"/>
+      <c r="G61" s="9"/>
+      <c r="H61" s="9"/>
+      <c r="I61" s="9"/>
+      <c r="J61" s="9"/>
+      <c r="K61" s="9"/>
+      <c r="L61" s="9"/>
+      <c r="M61" s="9"/>
+      <c r="N61" s="9"/>
+      <c r="O61" s="9"/>
+      <c r="P61" s="9"/>
+      <c r="Q61" s="9"/>
+      <c r="R61" s="9"/>
+      <c r="S61" s="9"/>
+      <c r="T61" s="9"/>
+      <c r="U61" s="9"/>
+      <c r="V61" s="9"/>
+      <c r="W61" s="9"/>
+      <c r="X61" s="9"/>
+      <c r="Y61" s="9"/>
+      <c r="Z61" s="9"/>
+      <c r="AA61" s="9"/>
+      <c r="AB61" s="91"/>
       <c r="AE61" s="9"/>
     </row>
     <row r="62" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="D62" t="s">
+        <v>15</v>
+      </c>
+      <c r="E62" s="8"/>
+      <c r="F62" s="9"/>
+      <c r="G62" s="9"/>
+      <c r="H62" s="9"/>
+      <c r="I62" s="9"/>
+      <c r="J62" s="9"/>
+      <c r="K62" s="9"/>
+      <c r="L62" s="9"/>
+      <c r="M62" s="9"/>
+      <c r="N62" s="9"/>
+      <c r="O62" s="9"/>
+      <c r="P62" s="9"/>
+      <c r="Q62" s="9"/>
+      <c r="R62" s="9"/>
+      <c r="S62" s="9"/>
+      <c r="T62" s="9"/>
+      <c r="U62" s="9"/>
+      <c r="V62" s="9"/>
+      <c r="W62" s="9"/>
+      <c r="X62" s="9"/>
+      <c r="Y62" s="9"/>
+      <c r="Z62" s="9"/>
+      <c r="AA62" s="9"/>
+      <c r="AB62" s="91"/>
       <c r="AE62" s="9"/>
     </row>
     <row r="63" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="B63" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="D63" t="s">
+        <v>16</v>
+      </c>
+      <c r="E63" s="8"/>
+      <c r="F63" s="9"/>
+      <c r="G63" s="9"/>
+      <c r="H63" s="9"/>
+      <c r="I63" s="9"/>
+      <c r="J63" s="9"/>
+      <c r="K63" s="9"/>
+      <c r="L63" s="9"/>
+      <c r="M63" s="9"/>
+      <c r="N63" s="9"/>
+      <c r="O63" s="9"/>
+      <c r="P63" s="9"/>
+      <c r="Q63" s="9"/>
+      <c r="R63" s="9"/>
+      <c r="S63" s="9"/>
+      <c r="T63" s="9"/>
+      <c r="U63" s="9"/>
+      <c r="V63" s="9"/>
+      <c r="W63" s="9"/>
+      <c r="X63" s="9"/>
+      <c r="Y63" s="9"/>
+      <c r="Z63" s="9"/>
+      <c r="AA63" s="9"/>
+      <c r="AB63" s="91"/>
       <c r="AE63" s="9"/>
+    </row>
+    <row r="64" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>1</v>
+      </c>
+      <c r="B64" s="10"/>
+      <c r="D64" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64" s="8"/>
+      <c r="F64" s="9"/>
+      <c r="G64" s="9"/>
+      <c r="H64" s="9"/>
+      <c r="I64" s="9"/>
+      <c r="J64" s="9"/>
+      <c r="K64" s="9"/>
+      <c r="L64" s="9"/>
+      <c r="M64" s="9"/>
+      <c r="N64" s="9"/>
+      <c r="O64" s="9"/>
+      <c r="P64" s="9"/>
+      <c r="Q64" s="9"/>
+      <c r="R64" s="9"/>
+      <c r="S64" s="9"/>
+      <c r="T64" s="9"/>
+      <c r="U64" s="9"/>
+      <c r="V64" s="9"/>
+      <c r="W64" s="9"/>
+      <c r="X64" s="9"/>
+      <c r="Y64" s="9"/>
+      <c r="Z64" s="9"/>
+      <c r="AA64" s="9"/>
+      <c r="AB64" s="91"/>
+    </row>
+    <row r="65" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>2</v>
+      </c>
+      <c r="B65" s="10"/>
+      <c r="D65" t="s">
+        <v>18</v>
+      </c>
+      <c r="E65" s="8"/>
+      <c r="F65" s="9"/>
+      <c r="G65" s="9"/>
+      <c r="H65" s="9"/>
+      <c r="I65" s="9"/>
+      <c r="J65" s="9"/>
+      <c r="K65" s="9"/>
+      <c r="L65" s="9"/>
+      <c r="M65" s="9"/>
+      <c r="N65" s="9"/>
+      <c r="O65" s="9"/>
+      <c r="P65" s="9"/>
+      <c r="Q65" s="9"/>
+      <c r="R65" s="9"/>
+      <c r="S65" s="9"/>
+      <c r="T65" s="9"/>
+      <c r="U65" s="9"/>
+      <c r="V65" s="9"/>
+      <c r="W65" s="9"/>
+      <c r="X65" s="9"/>
+      <c r="Y65" s="9"/>
+      <c r="Z65" s="9"/>
+      <c r="AA65" s="9"/>
+      <c r="AB65" s="91"/>
+    </row>
+    <row r="66" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>3</v>
+      </c>
+      <c r="B66" s="10"/>
+      <c r="D66" t="s">
+        <v>19</v>
+      </c>
+      <c r="E66" s="8"/>
+      <c r="F66" s="9"/>
+      <c r="G66" s="9"/>
+      <c r="H66" s="9"/>
+      <c r="I66" s="9"/>
+      <c r="J66" s="9"/>
+      <c r="K66" s="9"/>
+      <c r="L66" s="9"/>
+      <c r="M66" s="9"/>
+      <c r="N66" s="9"/>
+      <c r="O66" s="9"/>
+      <c r="P66" s="9"/>
+      <c r="Q66" s="9"/>
+      <c r="R66" s="9"/>
+      <c r="S66" s="9"/>
+      <c r="T66" s="9"/>
+      <c r="U66" s="9"/>
+      <c r="V66" s="9"/>
+      <c r="W66" s="9"/>
+      <c r="X66" s="9"/>
+      <c r="Y66" s="9"/>
+      <c r="Z66" s="9"/>
+      <c r="AA66" s="9"/>
+      <c r="AB66" s="91"/>
+    </row>
+    <row r="67" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>4</v>
+      </c>
+      <c r="B67" s="10"/>
+      <c r="D67" t="s">
+        <v>20</v>
+      </c>
+      <c r="E67" s="8"/>
+      <c r="F67" s="9"/>
+      <c r="G67" s="9"/>
+      <c r="H67" s="9"/>
+      <c r="I67" s="9"/>
+      <c r="J67" s="9"/>
+      <c r="K67" s="9"/>
+      <c r="L67" s="9"/>
+      <c r="M67" s="9"/>
+      <c r="N67" s="9"/>
+      <c r="O67" s="9"/>
+      <c r="P67" s="9"/>
+      <c r="Q67" s="9"/>
+      <c r="R67" s="9"/>
+      <c r="S67" s="9"/>
+      <c r="T67" s="9"/>
+      <c r="U67" s="9"/>
+      <c r="V67" s="9"/>
+      <c r="W67" s="9"/>
+      <c r="X67" s="9"/>
+      <c r="Y67" s="9"/>
+      <c r="Z67" s="9"/>
+      <c r="AA67" s="9"/>
+      <c r="AB67" s="91"/>
+    </row>
+    <row r="68" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>5</v>
+      </c>
+      <c r="B68" s="16"/>
+      <c r="D68" t="s">
+        <v>21</v>
+      </c>
+      <c r="E68" s="8"/>
+      <c r="F68" s="9"/>
+      <c r="G68" s="9"/>
+      <c r="H68" s="9"/>
+      <c r="I68" s="9"/>
+      <c r="J68" s="9"/>
+      <c r="K68" s="9"/>
+      <c r="L68" s="9"/>
+      <c r="M68" s="9"/>
+      <c r="N68" s="9"/>
+      <c r="O68" s="9"/>
+      <c r="P68" s="9"/>
+      <c r="Q68" s="9"/>
+      <c r="R68" s="9"/>
+      <c r="S68" s="9"/>
+      <c r="T68" s="9"/>
+      <c r="U68" s="9"/>
+      <c r="V68" s="9"/>
+      <c r="W68" s="9"/>
+      <c r="X68" s="9"/>
+      <c r="Y68" s="9"/>
+      <c r="Z68" s="9"/>
+      <c r="AA68" s="9"/>
+      <c r="AB68" s="91"/>
+    </row>
+    <row r="69" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="D69" t="s">
+        <v>22</v>
+      </c>
+      <c r="E69" s="8"/>
+      <c r="F69" s="9"/>
+      <c r="G69" s="9"/>
+      <c r="H69" s="9"/>
+      <c r="I69" s="9"/>
+      <c r="J69" s="9"/>
+      <c r="K69" s="9"/>
+      <c r="L69" s="9"/>
+      <c r="M69" s="9"/>
+      <c r="N69" s="9"/>
+      <c r="O69" s="9"/>
+      <c r="P69" s="9"/>
+      <c r="Q69" s="9"/>
+      <c r="R69" s="9"/>
+      <c r="S69" s="9"/>
+      <c r="T69" s="9"/>
+      <c r="U69" s="9"/>
+      <c r="V69" s="9"/>
+      <c r="W69" s="9"/>
+      <c r="X69" s="9"/>
+      <c r="Y69" s="9"/>
+      <c r="Z69" s="9"/>
+      <c r="AA69" s="9"/>
+      <c r="AB69" s="91"/>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="D70" t="s">
+        <v>23</v>
+      </c>
+      <c r="E70" s="8"/>
+      <c r="F70" s="9"/>
+      <c r="G70" s="9"/>
+      <c r="H70" s="9"/>
+      <c r="I70" s="9"/>
+      <c r="J70" s="9"/>
+      <c r="K70" s="9"/>
+      <c r="L70" s="9"/>
+      <c r="M70" s="9"/>
+      <c r="N70" s="9"/>
+      <c r="O70" s="9"/>
+      <c r="P70" s="9"/>
+      <c r="Q70" s="9"/>
+      <c r="R70" s="9"/>
+      <c r="S70" s="9"/>
+      <c r="T70" s="9"/>
+      <c r="U70" s="9"/>
+      <c r="V70" s="9"/>
+      <c r="W70" s="9"/>
+      <c r="X70" s="9"/>
+      <c r="Y70" s="9"/>
+      <c r="Z70" s="9"/>
+      <c r="AA70" s="9"/>
+      <c r="AB70" s="91"/>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="D71" t="s">
+        <v>24</v>
+      </c>
+      <c r="E71" s="8"/>
+      <c r="F71" s="9"/>
+      <c r="G71" s="9"/>
+      <c r="H71" s="9"/>
+      <c r="I71" s="9"/>
+      <c r="J71" s="9"/>
+      <c r="K71" s="9"/>
+      <c r="L71" s="9"/>
+      <c r="M71" s="9"/>
+      <c r="N71" s="9"/>
+      <c r="O71" s="9"/>
+      <c r="P71" s="9"/>
+      <c r="Q71" s="9"/>
+      <c r="R71" s="9"/>
+      <c r="S71" s="9"/>
+      <c r="T71" s="9"/>
+      <c r="U71" s="9"/>
+      <c r="V71" s="9"/>
+      <c r="W71" s="9"/>
+      <c r="X71" s="9"/>
+      <c r="Y71" s="9"/>
+      <c r="Z71" s="9"/>
+      <c r="AA71" s="9"/>
+      <c r="AB71" s="91"/>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="D72" t="s">
+        <v>25</v>
+      </c>
+      <c r="E72" s="8"/>
+      <c r="F72" s="9"/>
+      <c r="G72" s="9"/>
+      <c r="H72" s="9"/>
+      <c r="I72" s="9"/>
+      <c r="J72" s="9"/>
+      <c r="K72" s="9"/>
+      <c r="L72" s="9"/>
+      <c r="M72" s="9"/>
+      <c r="N72" s="9"/>
+      <c r="O72" s="9"/>
+      <c r="P72" s="9"/>
+      <c r="Q72" s="9"/>
+      <c r="R72" s="9"/>
+      <c r="S72" s="9"/>
+      <c r="T72" s="9"/>
+      <c r="U72" s="9"/>
+      <c r="V72" s="9"/>
+      <c r="W72" s="9"/>
+      <c r="X72" s="9"/>
+      <c r="Y72" s="9"/>
+      <c r="Z72" s="9"/>
+      <c r="AA72" s="9"/>
+      <c r="AB72" s="91"/>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="D73" t="s">
+        <v>26</v>
+      </c>
+      <c r="E73" s="8"/>
+      <c r="F73" s="9"/>
+      <c r="G73" s="9"/>
+      <c r="H73" s="9"/>
+      <c r="I73" s="9"/>
+      <c r="J73" s="9"/>
+      <c r="K73" s="9"/>
+      <c r="L73" s="9"/>
+      <c r="M73" s="9"/>
+      <c r="N73" s="9"/>
+      <c r="O73" s="9"/>
+      <c r="P73" s="9"/>
+      <c r="Q73" s="9"/>
+      <c r="R73" s="9"/>
+      <c r="S73" s="9"/>
+      <c r="T73" s="9"/>
+      <c r="U73" s="9"/>
+      <c r="V73" s="9"/>
+      <c r="W73" s="9"/>
+      <c r="X73" s="9"/>
+      <c r="Y73" s="9"/>
+      <c r="Z73" s="9"/>
+      <c r="AA73" s="9"/>
+      <c r="AB73" s="91"/>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="D74" t="s">
+        <v>27</v>
+      </c>
+      <c r="E74" s="8"/>
+      <c r="F74" s="9"/>
+      <c r="G74" s="9"/>
+      <c r="H74" s="9"/>
+      <c r="I74" s="9"/>
+      <c r="J74" s="9"/>
+      <c r="K74" s="9"/>
+      <c r="L74" s="9"/>
+      <c r="M74" s="9"/>
+      <c r="N74" s="9"/>
+      <c r="O74" s="9"/>
+      <c r="P74" s="9"/>
+      <c r="Q74" s="9"/>
+      <c r="R74" s="9"/>
+      <c r="S74" s="9"/>
+      <c r="T74" s="9"/>
+      <c r="U74" s="9"/>
+      <c r="V74" s="9"/>
+      <c r="W74" s="9"/>
+      <c r="X74" s="9"/>
+      <c r="Y74" s="9"/>
+      <c r="Z74" s="9"/>
+      <c r="AA74" s="9"/>
+      <c r="AB74" s="91"/>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="D75" t="s">
+        <v>28</v>
+      </c>
+      <c r="E75" s="14"/>
+      <c r="F75" s="92"/>
+      <c r="G75" s="92"/>
+      <c r="H75" s="92"/>
+      <c r="I75" s="92"/>
+      <c r="J75" s="92"/>
+      <c r="K75" s="92"/>
+      <c r="L75" s="92"/>
+      <c r="M75" s="92"/>
+      <c r="N75" s="92"/>
+      <c r="O75" s="92"/>
+      <c r="P75" s="92"/>
+      <c r="Q75" s="92"/>
+      <c r="R75" s="92"/>
+      <c r="S75" s="92"/>
+      <c r="T75" s="92"/>
+      <c r="U75" s="92"/>
+      <c r="V75" s="92"/>
+      <c r="W75" s="92"/>
+      <c r="X75" s="92"/>
+      <c r="Y75" s="92"/>
+      <c r="Z75" s="92"/>
+      <c r="AA75" s="92"/>
+      <c r="AB75" s="93"/>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="3"/>
+      <c r="J76" s="3"/>
+      <c r="K76" s="3"/>
+      <c r="L76" s="3"/>
+      <c r="M76" s="3"/>
+      <c r="N76" s="3"/>
+      <c r="O76" s="3"/>
+      <c r="P76" s="3"/>
+      <c r="Q76" s="3"/>
+      <c r="R76" s="3"/>
+      <c r="S76" s="3"/>
+      <c r="T76" s="3"/>
+      <c r="U76" s="3"/>
+      <c r="V76" s="3"/>
+      <c r="W76" s="3"/>
+      <c r="X76" s="3"/>
+      <c r="Y76" s="3"/>
+      <c r="Z76" s="3"/>
+      <c r="AA76" s="3"/>
+      <c r="AB76" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6076,14 +6846,14 @@
     <mergeCell ref="AJ10:AJ11"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A6 A24 A42" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"R,G,B"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ4 AJ10:AJ11" xr:uid="{D33C1792-54B1-0940-9EB2-1FAED54FA887}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE51" xr:uid="{6B1BD937-8499-D14A-A89C-39AB011F1DDC}">
       <formula1>"Condition,QC,Blank,TrueBlank,Library,SystemValidation"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A6 A60" xr:uid="{8029EEAD-587D-F241-B3BD-069D2E6CBB8E}">
+      <formula1>"R,G,B,Y"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6093,15 +6863,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R51"/>
+  <dimension ref="A1:S51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="17" max="17" width="29.33203125" customWidth="1"/>
-    <col min="18" max="18" width="24.6640625" customWidth="1"/>
-    <col min="19" max="19" width="22.83203125" customWidth="1"/>
+    <col min="18" max="18" width="29.33203125" customWidth="1"/>
+    <col min="19" max="19" width="24.6640625" customWidth="1"/>
+    <col min="20" max="20" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -6142,16 +6912,22 @@
         <v>45</v>
       </c>
       <c r="N1" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q1" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="O1" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="11">
         <v>1</v>
       </c>
@@ -6164,28 +6940,28 @@
         <v>D1t0</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E2" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="H2" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="H2" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="I2" s="7" t="s">
+      <c r="J2" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="K2" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="L2" s="24">
         <f>IF(LEN(User!AG2)=0,"",User!AG2)</f>
@@ -6193,16 +6969,17 @@
       </c>
       <c r="M2" s="11"/>
       <c r="N2" s="11"/>
-      <c r="O2" s="10"/>
+      <c r="O2" s="11"/>
       <c r="P2" s="10"/>
-      <c r="Q2" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q2" s="10"/>
+      <c r="R2" s="105" t="s">
+        <v>106</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
         <v>2</v>
       </c>
@@ -6215,28 +6992,28 @@
         <v>D1t1</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E3" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="I3" s="7" t="s">
+      <c r="J3" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="K3" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="L3" s="24">
         <f>IF(LEN(User!AG3)=0,"",User!AG3)</f>
@@ -6244,10 +7021,14 @@
       </c>
       <c r="M3" s="11"/>
       <c r="N3" s="11"/>
-      <c r="O3" s="10"/>
+      <c r="O3" s="11"/>
       <c r="P3" s="10"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q3" s="10"/>
+      <c r="R3" s="94" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="11">
         <v>3</v>
       </c>
@@ -6260,28 +7041,28 @@
         <v>D1t2</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E4" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="G4" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I4" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="H4" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="I4" s="7" t="s">
+      <c r="J4" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="K4" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="L4" s="24">
         <f>IF(LEN(User!AG4)=0,"",User!AG4)</f>
@@ -6289,12 +7070,13 @@
       </c>
       <c r="M4" s="11"/>
       <c r="N4" s="11"/>
-      <c r="O4" s="10"/>
+      <c r="O4" s="11"/>
       <c r="P4" s="10"/>
-      <c r="Q4" s="18"/>
-      <c r="R4" s="19"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q4" s="10"/>
+      <c r="R4" s="18"/>
+      <c r="S4" s="19"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="11">
         <v>4</v>
       </c>
@@ -6307,28 +7089,28 @@
         <v>D1t3</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E5" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="G5" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="H5" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="I5" s="7" t="s">
+      <c r="J5" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="K5" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="L5" s="24">
         <f>IF(LEN(User!AG5)=0,"",User!AG5)</f>
@@ -6336,16 +7118,17 @@
       </c>
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
-      <c r="O5" s="10"/>
+      <c r="O5" s="11"/>
       <c r="P5" s="10"/>
-      <c r="Q5" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="R5" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q5" s="10"/>
+      <c r="R5" s="105" t="s">
+        <v>108</v>
+      </c>
+      <c r="S5" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="11">
         <v>5</v>
       </c>
@@ -6358,28 +7141,28 @@
         <v>D2t0</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E6" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="G6" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="H6" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="H6" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="I6" s="7" t="s">
+      <c r="J6" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="K6" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="L6" s="24">
         <f>IF(LEN(User!AG6)=0,"",User!AG6)</f>
@@ -6387,10 +7170,15 @@
       </c>
       <c r="M6" s="11"/>
       <c r="N6" s="11"/>
-      <c r="O6" s="10"/>
+      <c r="O6" s="11"/>
       <c r="P6" s="10"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q6" s="10"/>
+      <c r="R6" s="106" t="s">
+        <v>109</v>
+      </c>
+      <c r="S6" s="107"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
         <v>6</v>
       </c>
@@ -6403,28 +7191,28 @@
         <v>D2t1</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E7" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="G7" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="H7" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="H7" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="I7" s="7" t="s">
+      <c r="J7" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="K7" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="L7" s="24">
         <f>IF(LEN(User!AG7)=0,"",User!AG7)</f>
@@ -6432,10 +7220,11 @@
       </c>
       <c r="M7" s="11"/>
       <c r="N7" s="11"/>
-      <c r="O7" s="10"/>
+      <c r="O7" s="11"/>
       <c r="P7" s="10"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q7" s="10"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="11">
         <v>7</v>
       </c>
@@ -6448,28 +7237,28 @@
         <v>D2t2</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E8" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="G8" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="H8" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="H8" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="I8" s="7" t="s">
+      <c r="J8" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="K8" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="L8" s="24">
         <f>IF(LEN(User!AG8)=0,"",User!AG8)</f>
@@ -6477,16 +7266,17 @@
       </c>
       <c r="M8" s="11"/>
       <c r="N8" s="11"/>
-      <c r="O8" s="10"/>
+      <c r="O8" s="11"/>
       <c r="P8" s="10"/>
-      <c r="Q8" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="R8" s="25">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q8" s="10"/>
+      <c r="R8" s="108" t="s">
+        <v>97</v>
+      </c>
+      <c r="S8" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <v>8</v>
       </c>
@@ -6499,28 +7289,28 @@
         <v>D2t3</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E9" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="G9" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="H9" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="H9" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="I9" s="7" t="s">
+      <c r="J9" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="K9" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="L9" s="24">
         <f>IF(LEN(User!AG9)=0,"",User!AG9)</f>
@@ -6528,16 +7318,17 @@
       </c>
       <c r="M9" s="11"/>
       <c r="N9" s="11"/>
-      <c r="O9" s="10"/>
+      <c r="O9" s="11"/>
       <c r="P9" s="10"/>
-      <c r="Q9" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="R9" s="6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q9" s="10"/>
+      <c r="R9" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="S9" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="11">
         <v>9</v>
       </c>
@@ -6550,28 +7341,28 @@
         <v>D3t0</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E10" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="G10" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="H10" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="H10" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="I10" s="7" t="s">
+      <c r="J10" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="K10" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="L10" s="24">
         <f>IF(LEN(User!AG10)=0,"",User!AG10)</f>
@@ -6579,10 +7370,15 @@
       </c>
       <c r="M10" s="11"/>
       <c r="N10" s="11"/>
-      <c r="O10" s="10"/>
+      <c r="O10" s="11"/>
       <c r="P10" s="10"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q10" s="10"/>
+      <c r="R10" s="97" t="s">
+        <v>110</v>
+      </c>
+      <c r="S10" s="98"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="11">
         <v>10</v>
       </c>
@@ -6595,28 +7391,28 @@
         <v>D3t1</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E11" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="G11" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="H11" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="I11" s="7" t="s">
+      <c r="J11" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="K11" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="L11" s="24">
         <f>IF(LEN(User!AG11)=0,"",User!AG11)</f>
@@ -6624,10 +7420,11 @@
       </c>
       <c r="M11" s="11"/>
       <c r="N11" s="11"/>
-      <c r="O11" s="10"/>
+      <c r="O11" s="11"/>
       <c r="P11" s="10"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q11" s="10"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="11">
         <v>11</v>
       </c>
@@ -6640,28 +7437,28 @@
         <v>D3t2</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E12" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="G12" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="H12" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I12" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="H12" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="I12" s="7" t="s">
+      <c r="J12" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="K12" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="L12" s="24">
         <f>IF(LEN(User!AG12)=0,"",User!AG12)</f>
@@ -6669,16 +7466,17 @@
       </c>
       <c r="M12" s="11"/>
       <c r="N12" s="11"/>
-      <c r="O12" s="10"/>
+      <c r="O12" s="11"/>
       <c r="P12" s="10"/>
-      <c r="Q12" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="R12" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q12" s="10"/>
+      <c r="R12" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="S12" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="11">
         <v>12</v>
       </c>
@@ -6691,28 +7489,28 @@
         <v>D3t3</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E13" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="G13" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="H13" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="H13" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="I13" s="7" t="s">
+      <c r="J13" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="K13" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="L13" s="24">
         <f>IF(LEN(User!AG13)=0,"",User!AG13)</f>
@@ -6720,14 +7518,15 @@
       </c>
       <c r="M13" s="11"/>
       <c r="N13" s="11"/>
-      <c r="O13" s="10"/>
+      <c r="O13" s="11"/>
       <c r="P13" s="10"/>
-      <c r="Q13" s="93" t="s">
-        <v>103</v>
-      </c>
-      <c r="R13" s="94"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q13" s="10"/>
+      <c r="R13" s="97" t="s">
+        <v>100</v>
+      </c>
+      <c r="S13" s="98"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="11">
         <v>13</v>
       </c>
@@ -6740,45 +7539,52 @@
         <v>QC</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E14" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="G14" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="H14" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I14" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="H14" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="I14" s="7" t="s">
+      <c r="J14" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="K14" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="L14" s="24">
         <f>IF(LEN(User!AG14)=0,"",User!AG14)</f>
         <v>1</v>
       </c>
       <c r="M14" s="11"/>
-      <c r="N14" s="11">
-        <v>2</v>
-      </c>
-      <c r="O14" s="10">
+      <c r="N14" s="11"/>
+      <c r="O14" s="11">
         <v>2</v>
       </c>
       <c r="P14" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="10">
+        <v>1</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="S14" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="11">
         <v>14</v>
       </c>
@@ -6791,45 +7597,50 @@
         <v>digest mix</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E15" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="G15" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="H15" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I15" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="H15" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="I15" s="7" t="s">
+      <c r="J15" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="K15" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="L15" s="24">
         <f>IF(LEN(User!AG15)=0,"",User!AG15)</f>
         <v>1</v>
       </c>
       <c r="M15" s="11"/>
-      <c r="N15" s="11">
-        <v>2</v>
-      </c>
-      <c r="O15" s="10">
+      <c r="N15" s="11"/>
+      <c r="O15" s="11">
         <v>2</v>
       </c>
       <c r="P15" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="10">
+        <v>1</v>
+      </c>
+      <c r="R15" s="95" t="s">
+        <v>112</v>
+      </c>
+      <c r="S15" s="96"/>
+    </row>
+    <row r="16" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="11">
         <v>15</v>
       </c>
@@ -6842,28 +7653,28 @@
         <v>Library</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E16" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="G16" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="H16" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="I16" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="H16" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="I16" s="7" t="s">
+      <c r="J16" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="K16" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="L16" s="24">
         <f>IF(LEN(User!AG16)=0,"",User!AG16)</f>
@@ -6873,10 +7684,11 @@
         <v>5</v>
       </c>
       <c r="N16" s="11"/>
-      <c r="O16" s="10"/>
+      <c r="O16" s="11"/>
       <c r="P16" s="10"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="10"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="11">
         <v>16</v>
       </c>
@@ -6889,28 +7701,28 @@
         <v>sys qc</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E17" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="G17" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="H17" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="I17" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="I17" s="7" t="s">
+      <c r="J17" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J17" s="7" t="s">
+      <c r="K17" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="L17" s="24">
         <f>IF(LEN(User!AG17)=0,"",User!AG17)</f>
@@ -6918,10 +7730,11 @@
       </c>
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
-      <c r="O17" s="10"/>
+      <c r="O17" s="11"/>
       <c r="P17" s="10"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="10"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="11">
         <v>17</v>
       </c>
@@ -6934,45 +7747,46 @@
         <v>true blank</v>
       </c>
       <c r="D18" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="F18" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="G18" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="H18" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="I18" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="H18" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="I18" s="7" t="s">
+      <c r="J18" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J18" s="7" t="s">
+      <c r="K18" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="L18" s="24">
         <f>IF(LEN(User!AG18)=0,"",User!AG18)</f>
         <v>1</v>
       </c>
       <c r="M18" s="11"/>
-      <c r="N18" s="11">
-        <v>1</v>
-      </c>
-      <c r="O18" s="10">
+      <c r="N18" s="11"/>
+      <c r="O18" s="11">
         <v>1</v>
       </c>
       <c r="P18" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="11">
         <v>18</v>
       </c>
@@ -6998,10 +7812,11 @@
       </c>
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
-      <c r="O19" s="10"/>
+      <c r="O19" s="11"/>
       <c r="P19" s="10"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="10"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="11">
         <v>19</v>
       </c>
@@ -7027,10 +7842,11 @@
       </c>
       <c r="M20" s="11"/>
       <c r="N20" s="11"/>
-      <c r="O20" s="10"/>
+      <c r="O20" s="11"/>
       <c r="P20" s="10"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="10"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" s="11">
         <v>20</v>
       </c>
@@ -7056,10 +7872,11 @@
       </c>
       <c r="M21" s="11"/>
       <c r="N21" s="11"/>
-      <c r="O21" s="10"/>
+      <c r="O21" s="11"/>
       <c r="P21" s="10"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="10"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" s="11">
         <v>21</v>
       </c>
@@ -7085,10 +7902,11 @@
       </c>
       <c r="M22" s="11"/>
       <c r="N22" s="11"/>
-      <c r="O22" s="10"/>
+      <c r="O22" s="11"/>
       <c r="P22" s="10"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="10"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="11">
         <v>22</v>
       </c>
@@ -7114,10 +7932,11 @@
       </c>
       <c r="M23" s="11"/>
       <c r="N23" s="11"/>
-      <c r="O23" s="10"/>
+      <c r="O23" s="11"/>
       <c r="P23" s="10"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="10"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="11">
         <v>23</v>
       </c>
@@ -7143,10 +7962,11 @@
       </c>
       <c r="M24" s="11"/>
       <c r="N24" s="11"/>
-      <c r="O24" s="10"/>
+      <c r="O24" s="11"/>
       <c r="P24" s="10"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="10"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" s="11">
         <v>24</v>
       </c>
@@ -7172,10 +7992,11 @@
       </c>
       <c r="M25" s="11"/>
       <c r="N25" s="11"/>
-      <c r="O25" s="10"/>
+      <c r="O25" s="11"/>
       <c r="P25" s="10"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="10"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="11">
         <v>25</v>
       </c>
@@ -7201,10 +8022,11 @@
       </c>
       <c r="M26" s="11"/>
       <c r="N26" s="11"/>
-      <c r="O26" s="10"/>
+      <c r="O26" s="11"/>
       <c r="P26" s="10"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="10"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="11">
         <v>26</v>
       </c>
@@ -7230,10 +8052,11 @@
       </c>
       <c r="M27" s="11"/>
       <c r="N27" s="11"/>
-      <c r="O27" s="10"/>
+      <c r="O27" s="11"/>
       <c r="P27" s="10"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="10"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" s="11">
         <v>27</v>
       </c>
@@ -7259,10 +8082,11 @@
       </c>
       <c r="M28" s="11"/>
       <c r="N28" s="11"/>
-      <c r="O28" s="10"/>
+      <c r="O28" s="11"/>
       <c r="P28" s="10"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="10"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="11">
         <v>28</v>
       </c>
@@ -7288,10 +8112,11 @@
       </c>
       <c r="M29" s="11"/>
       <c r="N29" s="11"/>
-      <c r="O29" s="10"/>
+      <c r="O29" s="11"/>
       <c r="P29" s="10"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="10"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="11">
         <v>29</v>
       </c>
@@ -7317,10 +8142,11 @@
       </c>
       <c r="M30" s="11"/>
       <c r="N30" s="11"/>
-      <c r="O30" s="10"/>
+      <c r="O30" s="11"/>
       <c r="P30" s="10"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="10"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" s="11">
         <v>30</v>
       </c>
@@ -7346,10 +8172,11 @@
       </c>
       <c r="M31" s="11"/>
       <c r="N31" s="11"/>
-      <c r="O31" s="10"/>
+      <c r="O31" s="11"/>
       <c r="P31" s="10"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="10"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="11">
         <v>31</v>
       </c>
@@ -7375,10 +8202,11 @@
       </c>
       <c r="M32" s="11"/>
       <c r="N32" s="11"/>
-      <c r="O32" s="10"/>
+      <c r="O32" s="11"/>
       <c r="P32" s="10"/>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="10"/>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" s="11">
         <v>32</v>
       </c>
@@ -7404,10 +8232,11 @@
       </c>
       <c r="M33" s="11"/>
       <c r="N33" s="11"/>
-      <c r="O33" s="10"/>
+      <c r="O33" s="11"/>
       <c r="P33" s="10"/>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="10"/>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" s="11">
         <v>33</v>
       </c>
@@ -7433,10 +8262,11 @@
       </c>
       <c r="M34" s="11"/>
       <c r="N34" s="11"/>
-      <c r="O34" s="10"/>
+      <c r="O34" s="11"/>
       <c r="P34" s="10"/>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="10"/>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35" s="11">
         <v>34</v>
       </c>
@@ -7462,10 +8292,11 @@
       </c>
       <c r="M35" s="11"/>
       <c r="N35" s="11"/>
-      <c r="O35" s="10"/>
+      <c r="O35" s="11"/>
       <c r="P35" s="10"/>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="10"/>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" s="11">
         <v>35</v>
       </c>
@@ -7489,11 +8320,11 @@
         <f>IF(LEN(User!AG36)=0,"",User!AG36)</f>
         <v/>
       </c>
-      <c r="N36" s="11"/>
-      <c r="O36" s="10"/>
+      <c r="O36" s="11"/>
       <c r="P36" s="10"/>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q36" s="10"/>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" s="11">
         <v>36</v>
       </c>
@@ -7519,10 +8350,11 @@
       </c>
       <c r="M37" s="11"/>
       <c r="N37" s="11"/>
-      <c r="O37" s="10"/>
+      <c r="O37" s="11"/>
       <c r="P37" s="10"/>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q37" s="10"/>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38" s="11">
         <v>37</v>
       </c>
@@ -7548,10 +8380,11 @@
       </c>
       <c r="M38" s="11"/>
       <c r="N38" s="11"/>
-      <c r="O38" s="10"/>
+      <c r="O38" s="11"/>
       <c r="P38" s="10"/>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="10"/>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" s="11">
         <v>38</v>
       </c>
@@ -7577,10 +8410,11 @@
       </c>
       <c r="M39" s="11"/>
       <c r="N39" s="11"/>
-      <c r="O39" s="10"/>
+      <c r="O39" s="11"/>
       <c r="P39" s="10"/>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="10"/>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40" s="11">
         <v>39</v>
       </c>
@@ -7606,10 +8440,11 @@
       </c>
       <c r="M40" s="11"/>
       <c r="N40" s="11"/>
-      <c r="O40" s="10"/>
+      <c r="O40" s="11"/>
       <c r="P40" s="10"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="10"/>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41" s="11">
         <v>40</v>
       </c>
@@ -7635,10 +8470,11 @@
       </c>
       <c r="M41" s="11"/>
       <c r="N41" s="11"/>
-      <c r="O41" s="10"/>
+      <c r="O41" s="11"/>
       <c r="P41" s="10"/>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="10"/>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" s="11">
         <v>41</v>
       </c>
@@ -7664,10 +8500,11 @@
       </c>
       <c r="M42" s="11"/>
       <c r="N42" s="11"/>
-      <c r="O42" s="10"/>
+      <c r="O42" s="11"/>
       <c r="P42" s="10"/>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="10"/>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" s="11">
         <v>42</v>
       </c>
@@ -7693,10 +8530,11 @@
       </c>
       <c r="M43" s="11"/>
       <c r="N43" s="11"/>
-      <c r="O43" s="10"/>
+      <c r="O43" s="11"/>
       <c r="P43" s="10"/>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="10"/>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" s="11">
         <v>43</v>
       </c>
@@ -7722,10 +8560,11 @@
       </c>
       <c r="M44" s="11"/>
       <c r="N44" s="11"/>
-      <c r="O44" s="10"/>
+      <c r="O44" s="11"/>
       <c r="P44" s="10"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="10"/>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" s="11">
         <v>44</v>
       </c>
@@ -7751,10 +8590,11 @@
       </c>
       <c r="M45" s="11"/>
       <c r="N45" s="11"/>
-      <c r="O45" s="10"/>
+      <c r="O45" s="11"/>
       <c r="P45" s="10"/>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="10"/>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" s="11">
         <v>45</v>
       </c>
@@ -7780,10 +8620,11 @@
       </c>
       <c r="M46" s="11"/>
       <c r="N46" s="11"/>
-      <c r="O46" s="10"/>
+      <c r="O46" s="11"/>
       <c r="P46" s="10"/>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="10"/>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" s="11">
         <v>46</v>
       </c>
@@ -7809,10 +8650,11 @@
       </c>
       <c r="M47" s="11"/>
       <c r="N47" s="11"/>
-      <c r="O47" s="10"/>
+      <c r="O47" s="11"/>
       <c r="P47" s="10"/>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="10"/>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" s="11">
         <v>47</v>
       </c>
@@ -7838,10 +8680,11 @@
       </c>
       <c r="M48" s="11"/>
       <c r="N48" s="11"/>
-      <c r="O48" s="10"/>
+      <c r="O48" s="11"/>
       <c r="P48" s="10"/>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="10"/>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="11">
         <v>48</v>
       </c>
@@ -7867,10 +8710,11 @@
       </c>
       <c r="M49" s="11"/>
       <c r="N49" s="11"/>
-      <c r="O49" s="10"/>
+      <c r="O49" s="11"/>
       <c r="P49" s="10"/>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="10"/>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" s="11">
         <v>49</v>
       </c>
@@ -7896,10 +8740,11 @@
       </c>
       <c r="M50" s="11"/>
       <c r="N50" s="11"/>
-      <c r="O50" s="10"/>
+      <c r="O50" s="11"/>
       <c r="P50" s="10"/>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="10"/>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" s="15">
         <v>50</v>
       </c>
@@ -7919,27 +8764,33 @@
       <c r="I51" s="12"/>
       <c r="J51" s="12"/>
       <c r="K51" s="14"/>
-      <c r="L51" s="32"/>
+      <c r="L51" s="29"/>
       <c r="M51" s="15"/>
       <c r="N51" s="15"/>
-      <c r="O51" s="16"/>
+      <c r="O51" s="15"/>
       <c r="P51" s="16"/>
+      <c r="Q51" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="Q13:R13"/>
+  <mergeCells count="3">
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="R10:S10"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:C51" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Condition,QC,Blank,TrueBlank,Lib,SystemValidation,WetQC"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R12" xr:uid="{F57A66E2-7866-AC44-A175-82DCFB34503A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S14" xr:uid="{35D1B678-0652-4F4F-8971-684F534EB0F5}">
+      <formula1>"(choose),Thermo,Bruker"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S12" xr:uid="{0258A78C-5456-8345-B73E-D53683BC6164}">
       <formula1>"(choose),UltiMate3000,Vanquish Neo"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2" xr:uid="{13E9B72B-2F53-8840-AC81-B9DFFE6FA7D9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2" xr:uid="{168385F4-DA21-D349-8FE3-91F42A2C573D}">
       <formula1>"(choose),1 column,2 column"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R5" xr:uid="{2695CDBE-2ABB-464D-953F-EEBE918C0247}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S5" xr:uid="{1C563DEF-F6E4-544E-81D6-01972A3E5160}">
       <formula1>"(choose),Before,After"</formula1>
     </dataValidation>
   </dataValidations>
